--- a/excel/Pliki+Mistrz+Excela/początkowe/Rozdział 01 - Konsolidacja.xlsx
+++ b/excel/Pliki+Mistrz+Excela/początkowe/Rozdział 01 - Konsolidacja.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr codeName="Ten_skoroszyt"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Pliki Mistrz Excela\początkowe - ten otwieramy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huber\Desktop\portf\kursy\learning-practice-path\excel\Pliki+Mistrz+Excela\początkowe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A48D34-707A-4A91-BC28-56EE60704C54}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01EAF7C-9DAE-4C30-ABEF-B7B81ADEA729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="825" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExceliAdam" sheetId="228" r:id="rId1"/>
@@ -10023,17 +10023,28 @@
     <definedName name="aaaa9999">#REF!</definedName>
     <definedName name="aaaaa1">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" iterate="1" iterateCount="10"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="10"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="60">
   <si>
     <t>Produkt</t>
   </si>
@@ -10084,9 +10095,6 @@
   </si>
   <si>
     <t>Suma z Sprzedaż</t>
-  </si>
-  <si>
-    <t>Wszystkie</t>
   </si>
   <si>
     <t>Tęcza</t>
@@ -10330,17 +10338,20 @@
   <si>
     <t>Newsletter (info o webinarach, pliki końcowe po webinarach itp.)</t>
   </si>
+  <si>
+    <t>Rozdział 01 - Konsolidacja</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0,"/>
-    <numFmt numFmtId="166" formatCode="d\-mmm\-yyyy"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00\ &quot;zł&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,##0\ &quot;zł&quot;"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0,"/>
+    <numFmt numFmtId="165" formatCode="d\-mmm\-yyyy"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;zł&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0\ &quot;zł&quot;"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -10569,15 +10580,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyBorder="0">
       <alignment horizontal="centerContinuous" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -10586,12 +10597,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10600,95 +10611,41 @@
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="10" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="10" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="10" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="10" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="10" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="10" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="11" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="12" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="10" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="13" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="12" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="12" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
@@ -10697,6 +10654,63 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="10" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="12" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="13" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="10" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="10" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="15">
     <cellStyle name="Akcent 1" xfId="8" builtinId="29"/>
@@ -11722,18 +11736,18 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="B1:CW95"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="99" width="2.44140625" style="8" customWidth="1"/>
-    <col min="100" max="101" width="2.44140625" customWidth="1"/>
-    <col min="102" max="105" width="9.109375" style="8"/>
-    <col min="106" max="106" width="10.6640625" style="8" customWidth="1"/>
-    <col min="107" max="107" width="73.6640625" style="8" customWidth="1"/>
-    <col min="108" max="108" width="6.33203125" style="8" customWidth="1"/>
-    <col min="109" max="16384" width="9.109375" style="8"/>
+    <col min="1" max="99" width="2.42578125" style="8" customWidth="1"/>
+    <col min="100" max="101" width="2.42578125" customWidth="1"/>
+    <col min="102" max="105" width="9.140625" style="8"/>
+    <col min="106" max="106" width="10.7109375" style="8" customWidth="1"/>
+    <col min="107" max="107" width="73.7109375" style="8" customWidth="1"/>
+    <col min="108" max="108" width="6.28515625" style="8" customWidth="1"/>
+    <col min="109" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R1" s="8"/>
       <c r="S1" s="8"/>
       <c r="T1" s="8"/>
@@ -11817,7 +11831,7 @@
       <c r="CT1" s="8"/>
       <c r="CU1" s="8"/>
     </row>
-    <row r="2" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R2" s="8"/>
       <c r="S2" s="8"/>
       <c r="T2" s="8"/>
@@ -11826,39 +11840,39 @@
       <c r="W2" s="8"/>
       <c r="X2" s="8"/>
       <c r="Y2" s="8"/>
-      <c r="Z2" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA2" s="45"/>
-      <c r="AB2" s="45"/>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="45"/>
-      <c r="AE2" s="45"/>
-      <c r="AF2" s="45"/>
-      <c r="AG2" s="45"/>
-      <c r="AH2" s="45"/>
-      <c r="AI2" s="45"/>
-      <c r="AJ2" s="45"/>
-      <c r="AK2" s="45"/>
-      <c r="AL2" s="45"/>
-      <c r="AM2" s="45"/>
-      <c r="AN2" s="45"/>
-      <c r="AO2" s="45"/>
-      <c r="AP2" s="45"/>
-      <c r="AQ2" s="45"/>
-      <c r="AR2" s="45"/>
-      <c r="AS2" s="45"/>
-      <c r="AT2" s="45"/>
-      <c r="AU2" s="45"/>
-      <c r="AV2" s="45"/>
-      <c r="AW2" s="45"/>
-      <c r="AX2" s="45"/>
-      <c r="AY2" s="45"/>
-      <c r="AZ2" s="45"/>
-      <c r="BA2" s="45"/>
-      <c r="BB2" s="45"/>
-      <c r="BC2" s="45"/>
-      <c r="BD2" s="44"/>
+      <c r="Z2" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA2" s="25"/>
+      <c r="AB2" s="25"/>
+      <c r="AC2" s="25"/>
+      <c r="AD2" s="25"/>
+      <c r="AE2" s="25"/>
+      <c r="AF2" s="25"/>
+      <c r="AG2" s="25"/>
+      <c r="AH2" s="25"/>
+      <c r="AI2" s="25"/>
+      <c r="AJ2" s="25"/>
+      <c r="AK2" s="25"/>
+      <c r="AL2" s="25"/>
+      <c r="AM2" s="25"/>
+      <c r="AN2" s="25"/>
+      <c r="AO2" s="25"/>
+      <c r="AP2" s="25"/>
+      <c r="AQ2" s="25"/>
+      <c r="AR2" s="25"/>
+      <c r="AS2" s="25"/>
+      <c r="AT2" s="25"/>
+      <c r="AU2" s="25"/>
+      <c r="AV2" s="25"/>
+      <c r="AW2" s="25"/>
+      <c r="AX2" s="25"/>
+      <c r="AY2" s="25"/>
+      <c r="AZ2" s="25"/>
+      <c r="BA2" s="25"/>
+      <c r="BB2" s="25"/>
+      <c r="BC2" s="25"/>
+      <c r="BD2" s="24"/>
       <c r="BE2" s="8"/>
       <c r="BF2" s="8"/>
       <c r="BG2" s="8"/>
@@ -11903,7 +11917,7 @@
       <c r="CT2" s="8"/>
       <c r="CU2" s="8"/>
     </row>
-    <row r="3" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
       <c r="T3" s="8"/>
@@ -11912,37 +11926,37 @@
       <c r="W3" s="8"/>
       <c r="X3" s="8"/>
       <c r="Y3" s="8"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="45"/>
-      <c r="AH3" s="45"/>
-      <c r="AI3" s="45"/>
-      <c r="AJ3" s="45"/>
-      <c r="AK3" s="45"/>
-      <c r="AL3" s="45"/>
-      <c r="AM3" s="45"/>
-      <c r="AN3" s="45"/>
-      <c r="AO3" s="45"/>
-      <c r="AP3" s="45"/>
-      <c r="AQ3" s="45"/>
-      <c r="AR3" s="45"/>
-      <c r="AS3" s="45"/>
-      <c r="AT3" s="45"/>
-      <c r="AU3" s="45"/>
-      <c r="AV3" s="45"/>
-      <c r="AW3" s="45"/>
-      <c r="AX3" s="45"/>
-      <c r="AY3" s="45"/>
-      <c r="AZ3" s="45"/>
-      <c r="BA3" s="45"/>
-      <c r="BB3" s="45"/>
-      <c r="BC3" s="45"/>
-      <c r="BD3" s="44"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25"/>
+      <c r="AB3" s="25"/>
+      <c r="AC3" s="25"/>
+      <c r="AD3" s="25"/>
+      <c r="AE3" s="25"/>
+      <c r="AF3" s="25"/>
+      <c r="AG3" s="25"/>
+      <c r="AH3" s="25"/>
+      <c r="AI3" s="25"/>
+      <c r="AJ3" s="25"/>
+      <c r="AK3" s="25"/>
+      <c r="AL3" s="25"/>
+      <c r="AM3" s="25"/>
+      <c r="AN3" s="25"/>
+      <c r="AO3" s="25"/>
+      <c r="AP3" s="25"/>
+      <c r="AQ3" s="25"/>
+      <c r="AR3" s="25"/>
+      <c r="AS3" s="25"/>
+      <c r="AT3" s="25"/>
+      <c r="AU3" s="25"/>
+      <c r="AV3" s="25"/>
+      <c r="AW3" s="25"/>
+      <c r="AX3" s="25"/>
+      <c r="AY3" s="25"/>
+      <c r="AZ3" s="25"/>
+      <c r="BA3" s="25"/>
+      <c r="BB3" s="25"/>
+      <c r="BC3" s="25"/>
+      <c r="BD3" s="24"/>
       <c r="BE3" s="8"/>
       <c r="BF3" s="8"/>
       <c r="BG3" s="8"/>
@@ -11987,7 +12001,7 @@
       <c r="CT3" s="8"/>
       <c r="CU3" s="8"/>
     </row>
-    <row r="4" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R4" s="8"/>
       <c r="S4" s="8"/>
       <c r="T4" s="8"/>
@@ -11996,39 +12010,39 @@
       <c r="W4" s="8"/>
       <c r="X4" s="8"/>
       <c r="Y4" s="8"/>
-      <c r="Z4" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA4" s="32"/>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="32"/>
-      <c r="AD4" s="32"/>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="32"/>
-      <c r="AG4" s="32"/>
-      <c r="AH4" s="32"/>
-      <c r="AI4" s="32"/>
-      <c r="AJ4" s="32"/>
-      <c r="AK4" s="32"/>
-      <c r="AL4" s="32"/>
-      <c r="AM4" s="32"/>
-      <c r="AN4" s="32"/>
-      <c r="AO4" s="32"/>
-      <c r="AP4" s="32"/>
-      <c r="AQ4" s="32"/>
-      <c r="AR4" s="32"/>
-      <c r="AS4" s="32"/>
-      <c r="AT4" s="32"/>
-      <c r="AU4" s="32"/>
-      <c r="AV4" s="32"/>
-      <c r="AW4" s="32"/>
-      <c r="AX4" s="32"/>
-      <c r="AY4" s="32"/>
-      <c r="AZ4" s="32"/>
-      <c r="BA4" s="32"/>
-      <c r="BB4" s="32"/>
-      <c r="BC4" s="32"/>
-      <c r="BD4" s="43"/>
+      <c r="Z4" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA4" s="26"/>
+      <c r="AB4" s="26"/>
+      <c r="AC4" s="26"/>
+      <c r="AD4" s="26"/>
+      <c r="AE4" s="26"/>
+      <c r="AF4" s="26"/>
+      <c r="AG4" s="26"/>
+      <c r="AH4" s="26"/>
+      <c r="AI4" s="26"/>
+      <c r="AJ4" s="26"/>
+      <c r="AK4" s="26"/>
+      <c r="AL4" s="26"/>
+      <c r="AM4" s="26"/>
+      <c r="AN4" s="26"/>
+      <c r="AO4" s="26"/>
+      <c r="AP4" s="26"/>
+      <c r="AQ4" s="26"/>
+      <c r="AR4" s="26"/>
+      <c r="AS4" s="26"/>
+      <c r="AT4" s="26"/>
+      <c r="AU4" s="26"/>
+      <c r="AV4" s="26"/>
+      <c r="AW4" s="26"/>
+      <c r="AX4" s="26"/>
+      <c r="AY4" s="26"/>
+      <c r="AZ4" s="26"/>
+      <c r="BA4" s="26"/>
+      <c r="BB4" s="26"/>
+      <c r="BC4" s="26"/>
+      <c r="BD4" s="19"/>
       <c r="BE4" s="8"/>
       <c r="BF4" s="8"/>
       <c r="BG4" s="8"/>
@@ -12073,57 +12087,57 @@
       <c r="CT4" s="8"/>
       <c r="CU4" s="8"/>
     </row>
-    <row r="5" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R5" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="S5" s="41"/>
-      <c r="T5" s="41"/>
-      <c r="U5" s="41"/>
-      <c r="V5" s="41"/>
-      <c r="W5" s="41"/>
+    <row r="5" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R5" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
       <c r="X5" s="8"/>
       <c r="Y5" s="8"/>
-      <c r="Z5" s="32"/>
-      <c r="AA5" s="32"/>
-      <c r="AB5" s="32"/>
-      <c r="AC5" s="32"/>
-      <c r="AD5" s="32"/>
-      <c r="AE5" s="32"/>
-      <c r="AF5" s="32"/>
-      <c r="AG5" s="32"/>
-      <c r="AH5" s="32"/>
-      <c r="AI5" s="32"/>
-      <c r="AJ5" s="32"/>
-      <c r="AK5" s="32"/>
-      <c r="AL5" s="32"/>
-      <c r="AM5" s="32"/>
-      <c r="AN5" s="32"/>
-      <c r="AO5" s="32"/>
-      <c r="AP5" s="32"/>
-      <c r="AQ5" s="32"/>
-      <c r="AR5" s="32"/>
-      <c r="AS5" s="32"/>
-      <c r="AT5" s="32"/>
-      <c r="AU5" s="32"/>
-      <c r="AV5" s="32"/>
-      <c r="AW5" s="32"/>
-      <c r="AX5" s="32"/>
-      <c r="AY5" s="32"/>
-      <c r="AZ5" s="32"/>
-      <c r="BA5" s="32"/>
-      <c r="BB5" s="32"/>
-      <c r="BC5" s="32"/>
-      <c r="BD5" s="43"/>
+      <c r="Z5" s="26"/>
+      <c r="AA5" s="26"/>
+      <c r="AB5" s="26"/>
+      <c r="AC5" s="26"/>
+      <c r="AD5" s="26"/>
+      <c r="AE5" s="26"/>
+      <c r="AF5" s="26"/>
+      <c r="AG5" s="26"/>
+      <c r="AH5" s="26"/>
+      <c r="AI5" s="26"/>
+      <c r="AJ5" s="26"/>
+      <c r="AK5" s="26"/>
+      <c r="AL5" s="26"/>
+      <c r="AM5" s="26"/>
+      <c r="AN5" s="26"/>
+      <c r="AO5" s="26"/>
+      <c r="AP5" s="26"/>
+      <c r="AQ5" s="26"/>
+      <c r="AR5" s="26"/>
+      <c r="AS5" s="26"/>
+      <c r="AT5" s="26"/>
+      <c r="AU5" s="26"/>
+      <c r="AV5" s="26"/>
+      <c r="AW5" s="26"/>
+      <c r="AX5" s="26"/>
+      <c r="AY5" s="26"/>
+      <c r="AZ5" s="26"/>
+      <c r="BA5" s="26"/>
+      <c r="BB5" s="26"/>
+      <c r="BC5" s="26"/>
+      <c r="BD5" s="19"/>
       <c r="BE5" s="8"/>
-      <c r="BF5" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="BG5" s="41"/>
-      <c r="BH5" s="41"/>
-      <c r="BI5" s="41"/>
-      <c r="BJ5" s="41"/>
-      <c r="BK5" s="41"/>
+      <c r="BF5" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="BG5" s="27"/>
+      <c r="BH5" s="27"/>
+      <c r="BI5" s="27"/>
+      <c r="BJ5" s="27"/>
+      <c r="BK5" s="27"/>
       <c r="BL5" s="8"/>
       <c r="BM5" s="8"/>
       <c r="BN5" s="8"/>
@@ -12161,53 +12175,53 @@
       <c r="CT5" s="8"/>
       <c r="CU5" s="8"/>
     </row>
-    <row r="6" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="41"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="41"/>
+    <row r="6" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27"/>
+      <c r="W6" s="27"/>
       <c r="X6" s="8"/>
       <c r="Y6" s="8"/>
-      <c r="Z6" s="32"/>
-      <c r="AA6" s="32"/>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="32"/>
-      <c r="AD6" s="32"/>
-      <c r="AE6" s="32"/>
-      <c r="AF6" s="32"/>
-      <c r="AG6" s="32"/>
-      <c r="AH6" s="32"/>
-      <c r="AI6" s="32"/>
-      <c r="AJ6" s="32"/>
-      <c r="AK6" s="32"/>
-      <c r="AL6" s="32"/>
-      <c r="AM6" s="32"/>
-      <c r="AN6" s="32"/>
-      <c r="AO6" s="32"/>
-      <c r="AP6" s="32"/>
-      <c r="AQ6" s="32"/>
-      <c r="AR6" s="32"/>
-      <c r="AS6" s="32"/>
-      <c r="AT6" s="32"/>
-      <c r="AU6" s="32"/>
-      <c r="AV6" s="32"/>
-      <c r="AW6" s="32"/>
-      <c r="AX6" s="32"/>
-      <c r="AY6" s="32"/>
-      <c r="AZ6" s="32"/>
-      <c r="BA6" s="32"/>
-      <c r="BB6" s="32"/>
-      <c r="BC6" s="32"/>
-      <c r="BD6" s="43"/>
+      <c r="Z6" s="26"/>
+      <c r="AA6" s="26"/>
+      <c r="AB6" s="26"/>
+      <c r="AC6" s="26"/>
+      <c r="AD6" s="26"/>
+      <c r="AE6" s="26"/>
+      <c r="AF6" s="26"/>
+      <c r="AG6" s="26"/>
+      <c r="AH6" s="26"/>
+      <c r="AI6" s="26"/>
+      <c r="AJ6" s="26"/>
+      <c r="AK6" s="26"/>
+      <c r="AL6" s="26"/>
+      <c r="AM6" s="26"/>
+      <c r="AN6" s="26"/>
+      <c r="AO6" s="26"/>
+      <c r="AP6" s="26"/>
+      <c r="AQ6" s="26"/>
+      <c r="AR6" s="26"/>
+      <c r="AS6" s="26"/>
+      <c r="AT6" s="26"/>
+      <c r="AU6" s="26"/>
+      <c r="AV6" s="26"/>
+      <c r="AW6" s="26"/>
+      <c r="AX6" s="26"/>
+      <c r="AY6" s="26"/>
+      <c r="AZ6" s="26"/>
+      <c r="BA6" s="26"/>
+      <c r="BB6" s="26"/>
+      <c r="BC6" s="26"/>
+      <c r="BD6" s="19"/>
       <c r="BE6" s="8"/>
-      <c r="BF6" s="41"/>
-      <c r="BG6" s="41"/>
-      <c r="BH6" s="41"/>
-      <c r="BI6" s="41"/>
-      <c r="BJ6" s="41"/>
-      <c r="BK6" s="41"/>
+      <c r="BF6" s="27"/>
+      <c r="BG6" s="27"/>
+      <c r="BH6" s="27"/>
+      <c r="BI6" s="27"/>
+      <c r="BJ6" s="27"/>
+      <c r="BK6" s="27"/>
       <c r="BL6" s="8"/>
       <c r="BM6" s="8"/>
       <c r="BN6" s="8"/>
@@ -12245,14 +12259,14 @@
       <c r="CT6" s="8"/>
       <c r="CU6" s="8"/>
     </row>
-    <row r="7" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R7" s="41"/>
-      <c r="S7" s="41"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="41"/>
-      <c r="X7" s="42"/>
+    <row r="7" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="27"/>
+      <c r="X7" s="23"/>
       <c r="Y7" s="8"/>
       <c r="Z7" s="8"/>
       <c r="AA7" s="8"/>
@@ -12286,12 +12300,12 @@
       <c r="BC7" s="8"/>
       <c r="BD7" s="8"/>
       <c r="BE7" s="8"/>
-      <c r="BF7" s="41"/>
-      <c r="BG7" s="41"/>
-      <c r="BH7" s="41"/>
-      <c r="BI7" s="41"/>
-      <c r="BJ7" s="41"/>
-      <c r="BK7" s="41"/>
+      <c r="BF7" s="27"/>
+      <c r="BG7" s="27"/>
+      <c r="BH7" s="27"/>
+      <c r="BI7" s="27"/>
+      <c r="BJ7" s="27"/>
+      <c r="BK7" s="27"/>
       <c r="BL7" s="8"/>
       <c r="BM7" s="8"/>
       <c r="BN7" s="8"/>
@@ -12329,7 +12343,7 @@
       <c r="CT7" s="8"/>
       <c r="CU7" s="8"/>
     </row>
-    <row r="8" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R8" s="8"/>
       <c r="S8" s="8"/>
       <c r="T8" s="8"/>
@@ -12413,95 +12427,95 @@
       <c r="CT8" s="8"/>
       <c r="CU8" s="8"/>
     </row>
-    <row r="9" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R9" s="24"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="24"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="24"/>
-      <c r="X9" s="24"/>
-      <c r="Y9" s="24"/>
-      <c r="Z9" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA9" s="40"/>
-      <c r="AB9" s="40"/>
-      <c r="AC9" s="40"/>
-      <c r="AD9" s="40"/>
-      <c r="AE9" s="40"/>
-      <c r="AF9" s="40"/>
-      <c r="AG9" s="40"/>
-      <c r="AH9" s="40"/>
-      <c r="AI9" s="40"/>
-      <c r="AJ9" s="40"/>
-      <c r="AK9" s="40"/>
-      <c r="AL9" s="40"/>
-      <c r="AM9" s="40"/>
-      <c r="AN9" s="40"/>
-      <c r="AO9" s="40"/>
-      <c r="AP9" s="40"/>
-      <c r="AQ9" s="40"/>
-      <c r="AR9" s="40"/>
-      <c r="AS9" s="40"/>
-      <c r="AT9" s="40"/>
-      <c r="AU9" s="40"/>
-      <c r="AV9" s="40"/>
-      <c r="AW9" s="40"/>
-      <c r="AX9" s="40"/>
-      <c r="AY9" s="40"/>
-      <c r="AZ9" s="40"/>
-      <c r="BA9" s="40"/>
-      <c r="BB9" s="40"/>
-      <c r="BC9" s="40"/>
-      <c r="BD9" s="38"/>
+    <row r="9" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R9" s="18"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="18"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="18"/>
+      <c r="X9" s="18"/>
+      <c r="Y9" s="18"/>
+      <c r="Z9" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
+      <c r="AI9" s="28"/>
+      <c r="AJ9" s="28"/>
+      <c r="AK9" s="28"/>
+      <c r="AL9" s="28"/>
+      <c r="AM9" s="28"/>
+      <c r="AN9" s="28"/>
+      <c r="AO9" s="28"/>
+      <c r="AP9" s="28"/>
+      <c r="AQ9" s="28"/>
+      <c r="AR9" s="28"/>
+      <c r="AS9" s="28"/>
+      <c r="AT9" s="28"/>
+      <c r="AU9" s="28"/>
+      <c r="AV9" s="28"/>
+      <c r="AW9" s="28"/>
+      <c r="AX9" s="28"/>
+      <c r="AY9" s="28"/>
+      <c r="AZ9" s="28"/>
+      <c r="BA9" s="28"/>
+      <c r="BB9" s="28"/>
+      <c r="BC9" s="28"/>
+      <c r="BD9" s="22"/>
       <c r="BE9" s="8"/>
-      <c r="BF9" s="24"/>
-      <c r="BG9" s="24"/>
-      <c r="BH9" s="24"/>
-      <c r="BI9" s="24"/>
-      <c r="BJ9" s="24"/>
-      <c r="BK9" s="24"/>
-      <c r="BL9" s="24"/>
-      <c r="BM9" s="24"/>
-      <c r="BN9" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="BO9" s="29"/>
-      <c r="BP9" s="29"/>
-      <c r="BQ9" s="29"/>
-      <c r="BR9" s="29"/>
-      <c r="BS9" s="29"/>
-      <c r="BT9" s="29"/>
-      <c r="BU9" s="29"/>
-      <c r="BV9" s="29"/>
-      <c r="BW9" s="29"/>
-      <c r="BX9" s="29"/>
-      <c r="BY9" s="29"/>
-      <c r="BZ9" s="29"/>
-      <c r="CA9" s="29"/>
-      <c r="CB9" s="29"/>
-      <c r="CC9" s="29"/>
-      <c r="CD9" s="29"/>
-      <c r="CE9" s="29"/>
-      <c r="CF9" s="29"/>
-      <c r="CG9" s="29"/>
-      <c r="CH9" s="29"/>
-      <c r="CI9" s="29"/>
-      <c r="CJ9" s="29"/>
-      <c r="CK9" s="29"/>
-      <c r="CL9" s="29"/>
-      <c r="CM9" s="29"/>
-      <c r="CN9" s="29"/>
-      <c r="CO9" s="29"/>
-      <c r="CP9" s="29"/>
-      <c r="CQ9" s="29"/>
-      <c r="CR9" s="21"/>
-      <c r="CS9" s="21"/>
-      <c r="CT9" s="21"/>
-      <c r="CU9" s="21"/>
+      <c r="BF9" s="18"/>
+      <c r="BG9" s="18"/>
+      <c r="BH9" s="18"/>
+      <c r="BI9" s="18"/>
+      <c r="BJ9" s="18"/>
+      <c r="BK9" s="18"/>
+      <c r="BL9" s="18"/>
+      <c r="BM9" s="18"/>
+      <c r="BN9" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="BO9" s="30"/>
+      <c r="BP9" s="30"/>
+      <c r="BQ9" s="30"/>
+      <c r="BR9" s="30"/>
+      <c r="BS9" s="30"/>
+      <c r="BT9" s="30"/>
+      <c r="BU9" s="30"/>
+      <c r="BV9" s="30"/>
+      <c r="BW9" s="30"/>
+      <c r="BX9" s="30"/>
+      <c r="BY9" s="30"/>
+      <c r="BZ9" s="30"/>
+      <c r="CA9" s="30"/>
+      <c r="CB9" s="30"/>
+      <c r="CC9" s="30"/>
+      <c r="CD9" s="30"/>
+      <c r="CE9" s="30"/>
+      <c r="CF9" s="30"/>
+      <c r="CG9" s="30"/>
+      <c r="CH9" s="30"/>
+      <c r="CI9" s="30"/>
+      <c r="CJ9" s="30"/>
+      <c r="CK9" s="30"/>
+      <c r="CL9" s="30"/>
+      <c r="CM9" s="30"/>
+      <c r="CN9" s="30"/>
+      <c r="CO9" s="30"/>
+      <c r="CP9" s="30"/>
+      <c r="CQ9" s="30"/>
+      <c r="CR9" s="17"/>
+      <c r="CS9" s="17"/>
+      <c r="CT9" s="17"/>
+      <c r="CU9" s="17"/>
     </row>
-    <row r="10" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R10" s="8"/>
       <c r="S10" s="8"/>
       <c r="T10" s="8"/>
@@ -12510,37 +12524,37 @@
       <c r="W10" s="8"/>
       <c r="X10" s="8"/>
       <c r="Y10" s="8"/>
-      <c r="Z10" s="39"/>
-      <c r="AA10" s="39"/>
-      <c r="AB10" s="39"/>
-      <c r="AC10" s="39"/>
-      <c r="AD10" s="39"/>
-      <c r="AE10" s="39"/>
-      <c r="AF10" s="39"/>
-      <c r="AG10" s="39"/>
-      <c r="AH10" s="39"/>
-      <c r="AI10" s="39"/>
-      <c r="AJ10" s="39"/>
-      <c r="AK10" s="39"/>
-      <c r="AL10" s="39"/>
-      <c r="AM10" s="39"/>
-      <c r="AN10" s="39"/>
-      <c r="AO10" s="39"/>
-      <c r="AP10" s="39"/>
-      <c r="AQ10" s="39"/>
-      <c r="AR10" s="39"/>
-      <c r="AS10" s="39"/>
-      <c r="AT10" s="39"/>
-      <c r="AU10" s="39"/>
-      <c r="AV10" s="39"/>
-      <c r="AW10" s="39"/>
-      <c r="AX10" s="39"/>
-      <c r="AY10" s="39"/>
-      <c r="AZ10" s="39"/>
-      <c r="BA10" s="39"/>
-      <c r="BB10" s="39"/>
-      <c r="BC10" s="39"/>
-      <c r="BD10" s="38"/>
+      <c r="Z10" s="29"/>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="29"/>
+      <c r="AC10" s="29"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="29"/>
+      <c r="AF10" s="29"/>
+      <c r="AG10" s="29"/>
+      <c r="AH10" s="29"/>
+      <c r="AI10" s="29"/>
+      <c r="AJ10" s="29"/>
+      <c r="AK10" s="29"/>
+      <c r="AL10" s="29"/>
+      <c r="AM10" s="29"/>
+      <c r="AN10" s="29"/>
+      <c r="AO10" s="29"/>
+      <c r="AP10" s="29"/>
+      <c r="AQ10" s="29"/>
+      <c r="AR10" s="29"/>
+      <c r="AS10" s="29"/>
+      <c r="AT10" s="29"/>
+      <c r="AU10" s="29"/>
+      <c r="AV10" s="29"/>
+      <c r="AW10" s="29"/>
+      <c r="AX10" s="29"/>
+      <c r="AY10" s="29"/>
+      <c r="AZ10" s="29"/>
+      <c r="BA10" s="29"/>
+      <c r="BB10" s="29"/>
+      <c r="BC10" s="29"/>
+      <c r="BD10" s="22"/>
       <c r="BE10" s="8"/>
       <c r="BF10" s="8"/>
       <c r="BG10" s="8"/>
@@ -12550,42 +12564,42 @@
       <c r="BK10" s="8"/>
       <c r="BL10" s="8"/>
       <c r="BM10" s="8"/>
-      <c r="BN10" s="22"/>
-      <c r="BO10" s="22"/>
-      <c r="BP10" s="22"/>
-      <c r="BQ10" s="22"/>
-      <c r="BR10" s="22"/>
-      <c r="BS10" s="22"/>
-      <c r="BT10" s="22"/>
-      <c r="BU10" s="22"/>
-      <c r="BV10" s="22"/>
-      <c r="BW10" s="22"/>
-      <c r="BX10" s="22"/>
-      <c r="BY10" s="22"/>
-      <c r="BZ10" s="22"/>
-      <c r="CA10" s="22"/>
-      <c r="CB10" s="22"/>
-      <c r="CC10" s="22"/>
-      <c r="CD10" s="22"/>
-      <c r="CE10" s="22"/>
-      <c r="CF10" s="22"/>
-      <c r="CG10" s="22"/>
-      <c r="CH10" s="22"/>
-      <c r="CI10" s="22"/>
-      <c r="CJ10" s="22"/>
-      <c r="CK10" s="22"/>
-      <c r="CL10" s="22"/>
-      <c r="CM10" s="22"/>
-      <c r="CN10" s="22"/>
-      <c r="CO10" s="22"/>
-      <c r="CP10" s="22"/>
-      <c r="CQ10" s="22"/>
-      <c r="CR10" s="21"/>
-      <c r="CS10" s="21"/>
-      <c r="CT10" s="21"/>
-      <c r="CU10" s="21"/>
+      <c r="BN10" s="31"/>
+      <c r="BO10" s="31"/>
+      <c r="BP10" s="31"/>
+      <c r="BQ10" s="31"/>
+      <c r="BR10" s="31"/>
+      <c r="BS10" s="31"/>
+      <c r="BT10" s="31"/>
+      <c r="BU10" s="31"/>
+      <c r="BV10" s="31"/>
+      <c r="BW10" s="31"/>
+      <c r="BX10" s="31"/>
+      <c r="BY10" s="31"/>
+      <c r="BZ10" s="31"/>
+      <c r="CA10" s="31"/>
+      <c r="CB10" s="31"/>
+      <c r="CC10" s="31"/>
+      <c r="CD10" s="31"/>
+      <c r="CE10" s="31"/>
+      <c r="CF10" s="31"/>
+      <c r="CG10" s="31"/>
+      <c r="CH10" s="31"/>
+      <c r="CI10" s="31"/>
+      <c r="CJ10" s="31"/>
+      <c r="CK10" s="31"/>
+      <c r="CL10" s="31"/>
+      <c r="CM10" s="31"/>
+      <c r="CN10" s="31"/>
+      <c r="CO10" s="31"/>
+      <c r="CP10" s="31"/>
+      <c r="CQ10" s="31"/>
+      <c r="CR10" s="17"/>
+      <c r="CS10" s="17"/>
+      <c r="CT10" s="17"/>
+      <c r="CU10" s="17"/>
     </row>
-    <row r="11" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R11" s="8"/>
       <c r="S11" s="8"/>
       <c r="T11" s="8"/>
@@ -12594,37 +12608,37 @@
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
       <c r="Y11" s="8"/>
-      <c r="Z11" s="39"/>
-      <c r="AA11" s="39"/>
-      <c r="AB11" s="39"/>
-      <c r="AC11" s="39"/>
-      <c r="AD11" s="39"/>
-      <c r="AE11" s="39"/>
-      <c r="AF11" s="39"/>
-      <c r="AG11" s="39"/>
-      <c r="AH11" s="39"/>
-      <c r="AI11" s="39"/>
-      <c r="AJ11" s="39"/>
-      <c r="AK11" s="39"/>
-      <c r="AL11" s="39"/>
-      <c r="AM11" s="39"/>
-      <c r="AN11" s="39"/>
-      <c r="AO11" s="39"/>
-      <c r="AP11" s="39"/>
-      <c r="AQ11" s="39"/>
-      <c r="AR11" s="39"/>
-      <c r="AS11" s="39"/>
-      <c r="AT11" s="39"/>
-      <c r="AU11" s="39"/>
-      <c r="AV11" s="39"/>
-      <c r="AW11" s="39"/>
-      <c r="AX11" s="39"/>
-      <c r="AY11" s="39"/>
-      <c r="AZ11" s="39"/>
-      <c r="BA11" s="39"/>
-      <c r="BB11" s="39"/>
-      <c r="BC11" s="39"/>
-      <c r="BD11" s="38"/>
+      <c r="Z11" s="29"/>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="29"/>
+      <c r="AC11" s="29"/>
+      <c r="AD11" s="29"/>
+      <c r="AE11" s="29"/>
+      <c r="AF11" s="29"/>
+      <c r="AG11" s="29"/>
+      <c r="AH11" s="29"/>
+      <c r="AI11" s="29"/>
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="29"/>
+      <c r="AL11" s="29"/>
+      <c r="AM11" s="29"/>
+      <c r="AN11" s="29"/>
+      <c r="AO11" s="29"/>
+      <c r="AP11" s="29"/>
+      <c r="AQ11" s="29"/>
+      <c r="AR11" s="29"/>
+      <c r="AS11" s="29"/>
+      <c r="AT11" s="29"/>
+      <c r="AU11" s="29"/>
+      <c r="AV11" s="29"/>
+      <c r="AW11" s="29"/>
+      <c r="AX11" s="29"/>
+      <c r="AY11" s="29"/>
+      <c r="AZ11" s="29"/>
+      <c r="BA11" s="29"/>
+      <c r="BB11" s="29"/>
+      <c r="BC11" s="29"/>
+      <c r="BD11" s="22"/>
       <c r="BE11" s="8"/>
       <c r="BF11" s="8"/>
       <c r="BG11" s="8"/>
@@ -12634,42 +12648,42 @@
       <c r="BK11" s="8"/>
       <c r="BL11" s="8"/>
       <c r="BM11" s="8"/>
-      <c r="BN11" s="22"/>
-      <c r="BO11" s="22"/>
-      <c r="BP11" s="22"/>
-      <c r="BQ11" s="22"/>
-      <c r="BR11" s="22"/>
-      <c r="BS11" s="22"/>
-      <c r="BT11" s="22"/>
-      <c r="BU11" s="22"/>
-      <c r="BV11" s="22"/>
-      <c r="BW11" s="22"/>
-      <c r="BX11" s="22"/>
-      <c r="BY11" s="22"/>
-      <c r="BZ11" s="22"/>
-      <c r="CA11" s="22"/>
-      <c r="CB11" s="22"/>
-      <c r="CC11" s="22"/>
-      <c r="CD11" s="22"/>
-      <c r="CE11" s="22"/>
-      <c r="CF11" s="22"/>
-      <c r="CG11" s="22"/>
-      <c r="CH11" s="22"/>
-      <c r="CI11" s="22"/>
-      <c r="CJ11" s="22"/>
-      <c r="CK11" s="22"/>
-      <c r="CL11" s="22"/>
-      <c r="CM11" s="22"/>
-      <c r="CN11" s="22"/>
-      <c r="CO11" s="22"/>
-      <c r="CP11" s="22"/>
-      <c r="CQ11" s="22"/>
-      <c r="CR11" s="21"/>
-      <c r="CS11" s="21"/>
-      <c r="CT11" s="21"/>
-      <c r="CU11" s="21"/>
+      <c r="BN11" s="31"/>
+      <c r="BO11" s="31"/>
+      <c r="BP11" s="31"/>
+      <c r="BQ11" s="31"/>
+      <c r="BR11" s="31"/>
+      <c r="BS11" s="31"/>
+      <c r="BT11" s="31"/>
+      <c r="BU11" s="31"/>
+      <c r="BV11" s="31"/>
+      <c r="BW11" s="31"/>
+      <c r="BX11" s="31"/>
+      <c r="BY11" s="31"/>
+      <c r="BZ11" s="31"/>
+      <c r="CA11" s="31"/>
+      <c r="CB11" s="31"/>
+      <c r="CC11" s="31"/>
+      <c r="CD11" s="31"/>
+      <c r="CE11" s="31"/>
+      <c r="CF11" s="31"/>
+      <c r="CG11" s="31"/>
+      <c r="CH11" s="31"/>
+      <c r="CI11" s="31"/>
+      <c r="CJ11" s="31"/>
+      <c r="CK11" s="31"/>
+      <c r="CL11" s="31"/>
+      <c r="CM11" s="31"/>
+      <c r="CN11" s="31"/>
+      <c r="CO11" s="31"/>
+      <c r="CP11" s="31"/>
+      <c r="CQ11" s="31"/>
+      <c r="CR11" s="17"/>
+      <c r="CS11" s="17"/>
+      <c r="CT11" s="17"/>
+      <c r="CU11" s="17"/>
     </row>
-    <row r="12" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R12" s="8"/>
       <c r="S12" s="8"/>
       <c r="T12" s="8"/>
@@ -12678,37 +12692,37 @@
       <c r="W12" s="8"/>
       <c r="X12" s="8"/>
       <c r="Y12" s="8"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="39"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="39"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="39"/>
-      <c r="AK12" s="39"/>
-      <c r="AL12" s="39"/>
-      <c r="AM12" s="39"/>
-      <c r="AN12" s="39"/>
-      <c r="AO12" s="39"/>
-      <c r="AP12" s="39"/>
-      <c r="AQ12" s="39"/>
-      <c r="AR12" s="39"/>
-      <c r="AS12" s="39"/>
-      <c r="AT12" s="39"/>
-      <c r="AU12" s="39"/>
-      <c r="AV12" s="39"/>
-      <c r="AW12" s="39"/>
-      <c r="AX12" s="39"/>
-      <c r="AY12" s="39"/>
-      <c r="AZ12" s="39"/>
-      <c r="BA12" s="39"/>
-      <c r="BB12" s="39"/>
-      <c r="BC12" s="39"/>
-      <c r="BD12" s="38"/>
+      <c r="Z12" s="29"/>
+      <c r="AA12" s="29"/>
+      <c r="AB12" s="29"/>
+      <c r="AC12" s="29"/>
+      <c r="AD12" s="29"/>
+      <c r="AE12" s="29"/>
+      <c r="AF12" s="29"/>
+      <c r="AG12" s="29"/>
+      <c r="AH12" s="29"/>
+      <c r="AI12" s="29"/>
+      <c r="AJ12" s="29"/>
+      <c r="AK12" s="29"/>
+      <c r="AL12" s="29"/>
+      <c r="AM12" s="29"/>
+      <c r="AN12" s="29"/>
+      <c r="AO12" s="29"/>
+      <c r="AP12" s="29"/>
+      <c r="AQ12" s="29"/>
+      <c r="AR12" s="29"/>
+      <c r="AS12" s="29"/>
+      <c r="AT12" s="29"/>
+      <c r="AU12" s="29"/>
+      <c r="AV12" s="29"/>
+      <c r="AW12" s="29"/>
+      <c r="AX12" s="29"/>
+      <c r="AY12" s="29"/>
+      <c r="AZ12" s="29"/>
+      <c r="BA12" s="29"/>
+      <c r="BB12" s="29"/>
+      <c r="BC12" s="29"/>
+      <c r="BD12" s="22"/>
       <c r="BE12" s="8"/>
       <c r="BF12" s="8"/>
       <c r="BG12" s="8"/>
@@ -12718,44 +12732,44 @@
       <c r="BK12" s="8"/>
       <c r="BL12" s="8"/>
       <c r="BM12" s="8"/>
-      <c r="BN12" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="BO12" s="18"/>
-      <c r="BP12" s="18"/>
-      <c r="BQ12" s="18"/>
-      <c r="BR12" s="18"/>
-      <c r="BS12" s="18"/>
-      <c r="BT12" s="18"/>
-      <c r="BU12" s="18"/>
-      <c r="BV12" s="18"/>
-      <c r="BW12" s="18"/>
-      <c r="BX12" s="18"/>
-      <c r="BY12" s="18"/>
-      <c r="BZ12" s="18"/>
-      <c r="CA12" s="18"/>
-      <c r="CB12" s="18"/>
-      <c r="CC12" s="18"/>
-      <c r="CD12" s="18"/>
-      <c r="CE12" s="18"/>
-      <c r="CF12" s="18"/>
-      <c r="CG12" s="18"/>
-      <c r="CH12" s="18"/>
-      <c r="CI12" s="18"/>
-      <c r="CJ12" s="18"/>
-      <c r="CK12" s="18"/>
-      <c r="CL12" s="18"/>
-      <c r="CM12" s="18"/>
-      <c r="CN12" s="18"/>
-      <c r="CO12" s="18"/>
-      <c r="CP12" s="18"/>
-      <c r="CQ12" s="18"/>
-      <c r="CR12" s="17"/>
-      <c r="CS12" s="17"/>
-      <c r="CT12" s="17"/>
-      <c r="CU12" s="17"/>
+      <c r="BN12" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="BO12" s="32"/>
+      <c r="BP12" s="32"/>
+      <c r="BQ12" s="32"/>
+      <c r="BR12" s="32"/>
+      <c r="BS12" s="32"/>
+      <c r="BT12" s="32"/>
+      <c r="BU12" s="32"/>
+      <c r="BV12" s="32"/>
+      <c r="BW12" s="32"/>
+      <c r="BX12" s="32"/>
+      <c r="BY12" s="32"/>
+      <c r="BZ12" s="32"/>
+      <c r="CA12" s="32"/>
+      <c r="CB12" s="32"/>
+      <c r="CC12" s="32"/>
+      <c r="CD12" s="32"/>
+      <c r="CE12" s="32"/>
+      <c r="CF12" s="32"/>
+      <c r="CG12" s="32"/>
+      <c r="CH12" s="32"/>
+      <c r="CI12" s="32"/>
+      <c r="CJ12" s="32"/>
+      <c r="CK12" s="32"/>
+      <c r="CL12" s="32"/>
+      <c r="CM12" s="32"/>
+      <c r="CN12" s="32"/>
+      <c r="CO12" s="32"/>
+      <c r="CP12" s="32"/>
+      <c r="CQ12" s="32"/>
+      <c r="CR12" s="15"/>
+      <c r="CS12" s="15"/>
+      <c r="CT12" s="15"/>
+      <c r="CU12" s="15"/>
     </row>
-    <row r="13" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R13" s="8"/>
       <c r="S13" s="8"/>
       <c r="T13" s="8"/>
@@ -12764,37 +12778,37 @@
       <c r="W13" s="8"/>
       <c r="X13" s="8"/>
       <c r="Y13" s="8"/>
-      <c r="Z13" s="39"/>
-      <c r="AA13" s="39"/>
-      <c r="AB13" s="39"/>
-      <c r="AC13" s="39"/>
-      <c r="AD13" s="39"/>
-      <c r="AE13" s="39"/>
-      <c r="AF13" s="39"/>
-      <c r="AG13" s="39"/>
-      <c r="AH13" s="39"/>
-      <c r="AI13" s="39"/>
-      <c r="AJ13" s="39"/>
-      <c r="AK13" s="39"/>
-      <c r="AL13" s="39"/>
-      <c r="AM13" s="39"/>
-      <c r="AN13" s="39"/>
-      <c r="AO13" s="39"/>
-      <c r="AP13" s="39"/>
-      <c r="AQ13" s="39"/>
-      <c r="AR13" s="39"/>
-      <c r="AS13" s="39"/>
-      <c r="AT13" s="39"/>
-      <c r="AU13" s="39"/>
-      <c r="AV13" s="39"/>
-      <c r="AW13" s="39"/>
-      <c r="AX13" s="39"/>
-      <c r="AY13" s="39"/>
-      <c r="AZ13" s="39"/>
-      <c r="BA13" s="39"/>
-      <c r="BB13" s="39"/>
-      <c r="BC13" s="39"/>
-      <c r="BD13" s="38"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="29"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="29"/>
+      <c r="AF13" s="29"/>
+      <c r="AG13" s="29"/>
+      <c r="AH13" s="29"/>
+      <c r="AI13" s="29"/>
+      <c r="AJ13" s="29"/>
+      <c r="AK13" s="29"/>
+      <c r="AL13" s="29"/>
+      <c r="AM13" s="29"/>
+      <c r="AN13" s="29"/>
+      <c r="AO13" s="29"/>
+      <c r="AP13" s="29"/>
+      <c r="AQ13" s="29"/>
+      <c r="AR13" s="29"/>
+      <c r="AS13" s="29"/>
+      <c r="AT13" s="29"/>
+      <c r="AU13" s="29"/>
+      <c r="AV13" s="29"/>
+      <c r="AW13" s="29"/>
+      <c r="AX13" s="29"/>
+      <c r="AY13" s="29"/>
+      <c r="AZ13" s="29"/>
+      <c r="BA13" s="29"/>
+      <c r="BB13" s="29"/>
+      <c r="BC13" s="29"/>
+      <c r="BD13" s="22"/>
       <c r="BE13" s="8"/>
       <c r="BF13" s="8"/>
       <c r="BG13" s="8"/>
@@ -12804,42 +12818,42 @@
       <c r="BK13" s="8"/>
       <c r="BL13" s="8"/>
       <c r="BM13" s="8"/>
-      <c r="BN13" s="18"/>
-      <c r="BO13" s="18"/>
-      <c r="BP13" s="18"/>
-      <c r="BQ13" s="18"/>
-      <c r="BR13" s="18"/>
-      <c r="BS13" s="18"/>
-      <c r="BT13" s="18"/>
-      <c r="BU13" s="18"/>
-      <c r="BV13" s="18"/>
-      <c r="BW13" s="18"/>
-      <c r="BX13" s="18"/>
-      <c r="BY13" s="18"/>
-      <c r="BZ13" s="18"/>
-      <c r="CA13" s="18"/>
-      <c r="CB13" s="18"/>
-      <c r="CC13" s="18"/>
-      <c r="CD13" s="18"/>
-      <c r="CE13" s="18"/>
-      <c r="CF13" s="18"/>
-      <c r="CG13" s="18"/>
-      <c r="CH13" s="18"/>
-      <c r="CI13" s="18"/>
-      <c r="CJ13" s="18"/>
-      <c r="CK13" s="18"/>
-      <c r="CL13" s="18"/>
-      <c r="CM13" s="18"/>
-      <c r="CN13" s="18"/>
-      <c r="CO13" s="18"/>
-      <c r="CP13" s="18"/>
-      <c r="CQ13" s="18"/>
-      <c r="CR13" s="17"/>
-      <c r="CS13" s="17"/>
-      <c r="CT13" s="17"/>
-      <c r="CU13" s="17"/>
+      <c r="BN13" s="32"/>
+      <c r="BO13" s="32"/>
+      <c r="BP13" s="32"/>
+      <c r="BQ13" s="32"/>
+      <c r="BR13" s="32"/>
+      <c r="BS13" s="32"/>
+      <c r="BT13" s="32"/>
+      <c r="BU13" s="32"/>
+      <c r="BV13" s="32"/>
+      <c r="BW13" s="32"/>
+      <c r="BX13" s="32"/>
+      <c r="BY13" s="32"/>
+      <c r="BZ13" s="32"/>
+      <c r="CA13" s="32"/>
+      <c r="CB13" s="32"/>
+      <c r="CC13" s="32"/>
+      <c r="CD13" s="32"/>
+      <c r="CE13" s="32"/>
+      <c r="CF13" s="32"/>
+      <c r="CG13" s="32"/>
+      <c r="CH13" s="32"/>
+      <c r="CI13" s="32"/>
+      <c r="CJ13" s="32"/>
+      <c r="CK13" s="32"/>
+      <c r="CL13" s="32"/>
+      <c r="CM13" s="32"/>
+      <c r="CN13" s="32"/>
+      <c r="CO13" s="32"/>
+      <c r="CP13" s="32"/>
+      <c r="CQ13" s="32"/>
+      <c r="CR13" s="15"/>
+      <c r="CS13" s="15"/>
+      <c r="CT13" s="15"/>
+      <c r="CU13" s="15"/>
     </row>
-    <row r="14" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R14" s="8"/>
       <c r="S14" s="8"/>
       <c r="T14" s="8"/>
@@ -12848,39 +12862,39 @@
       <c r="W14" s="8"/>
       <c r="X14" s="8"/>
       <c r="Y14" s="8"/>
-      <c r="Z14" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA14" s="28"/>
-      <c r="AB14" s="28"/>
-      <c r="AC14" s="28"/>
-      <c r="AD14" s="28"/>
-      <c r="AE14" s="28"/>
-      <c r="AF14" s="28"/>
-      <c r="AG14" s="28"/>
-      <c r="AH14" s="28"/>
-      <c r="AI14" s="28"/>
-      <c r="AJ14" s="28"/>
-      <c r="AK14" s="28"/>
-      <c r="AL14" s="28"/>
-      <c r="AM14" s="28"/>
-      <c r="AN14" s="28"/>
-      <c r="AO14" s="28"/>
-      <c r="AP14" s="28"/>
-      <c r="AQ14" s="28"/>
-      <c r="AR14" s="28"/>
-      <c r="AS14" s="28"/>
-      <c r="AT14" s="28"/>
-      <c r="AU14" s="28"/>
-      <c r="AV14" s="28"/>
-      <c r="AW14" s="28"/>
-      <c r="AX14" s="28"/>
-      <c r="AY14" s="28"/>
-      <c r="AZ14" s="28"/>
-      <c r="BA14" s="28"/>
-      <c r="BB14" s="28"/>
-      <c r="BC14" s="28"/>
-      <c r="BD14" s="14"/>
+      <c r="Z14" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA14" s="33"/>
+      <c r="AB14" s="33"/>
+      <c r="AC14" s="33"/>
+      <c r="AD14" s="33"/>
+      <c r="AE14" s="33"/>
+      <c r="AF14" s="33"/>
+      <c r="AG14" s="33"/>
+      <c r="AH14" s="33"/>
+      <c r="AI14" s="33"/>
+      <c r="AJ14" s="33"/>
+      <c r="AK14" s="33"/>
+      <c r="AL14" s="33"/>
+      <c r="AM14" s="33"/>
+      <c r="AN14" s="33"/>
+      <c r="AO14" s="33"/>
+      <c r="AP14" s="33"/>
+      <c r="AQ14" s="33"/>
+      <c r="AR14" s="33"/>
+      <c r="AS14" s="33"/>
+      <c r="AT14" s="33"/>
+      <c r="AU14" s="33"/>
+      <c r="AV14" s="33"/>
+      <c r="AW14" s="33"/>
+      <c r="AX14" s="33"/>
+      <c r="AY14" s="33"/>
+      <c r="AZ14" s="33"/>
+      <c r="BA14" s="33"/>
+      <c r="BB14" s="33"/>
+      <c r="BC14" s="33"/>
+      <c r="BD14" s="12"/>
       <c r="BE14" s="8"/>
       <c r="BF14" s="8"/>
       <c r="BG14" s="8"/>
@@ -12925,7 +12939,7 @@
       <c r="CT14" s="8"/>
       <c r="CU14" s="8"/>
     </row>
-    <row r="15" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R15" s="8"/>
       <c r="S15" s="8"/>
       <c r="T15" s="8"/>
@@ -12934,37 +12948,37 @@
       <c r="W15" s="8"/>
       <c r="X15" s="8"/>
       <c r="Y15" s="8"/>
-      <c r="Z15" s="28"/>
-      <c r="AA15" s="28"/>
-      <c r="AB15" s="28"/>
-      <c r="AC15" s="28"/>
-      <c r="AD15" s="28"/>
-      <c r="AE15" s="28"/>
-      <c r="AF15" s="28"/>
-      <c r="AG15" s="28"/>
-      <c r="AH15" s="28"/>
-      <c r="AI15" s="28"/>
-      <c r="AJ15" s="28"/>
-      <c r="AK15" s="28"/>
-      <c r="AL15" s="28"/>
-      <c r="AM15" s="28"/>
-      <c r="AN15" s="28"/>
-      <c r="AO15" s="28"/>
-      <c r="AP15" s="28"/>
-      <c r="AQ15" s="28"/>
-      <c r="AR15" s="28"/>
-      <c r="AS15" s="28"/>
-      <c r="AT15" s="28"/>
-      <c r="AU15" s="28"/>
-      <c r="AV15" s="28"/>
-      <c r="AW15" s="28"/>
-      <c r="AX15" s="28"/>
-      <c r="AY15" s="28"/>
-      <c r="AZ15" s="28"/>
-      <c r="BA15" s="28"/>
-      <c r="BB15" s="28"/>
-      <c r="BC15" s="28"/>
-      <c r="BD15" s="14"/>
+      <c r="Z15" s="33"/>
+      <c r="AA15" s="33"/>
+      <c r="AB15" s="33"/>
+      <c r="AC15" s="33"/>
+      <c r="AD15" s="33"/>
+      <c r="AE15" s="33"/>
+      <c r="AF15" s="33"/>
+      <c r="AG15" s="33"/>
+      <c r="AH15" s="33"/>
+      <c r="AI15" s="33"/>
+      <c r="AJ15" s="33"/>
+      <c r="AK15" s="33"/>
+      <c r="AL15" s="33"/>
+      <c r="AM15" s="33"/>
+      <c r="AN15" s="33"/>
+      <c r="AO15" s="33"/>
+      <c r="AP15" s="33"/>
+      <c r="AQ15" s="33"/>
+      <c r="AR15" s="33"/>
+      <c r="AS15" s="33"/>
+      <c r="AT15" s="33"/>
+      <c r="AU15" s="33"/>
+      <c r="AV15" s="33"/>
+      <c r="AW15" s="33"/>
+      <c r="AX15" s="33"/>
+      <c r="AY15" s="33"/>
+      <c r="AZ15" s="33"/>
+      <c r="BA15" s="33"/>
+      <c r="BB15" s="33"/>
+      <c r="BC15" s="33"/>
+      <c r="BD15" s="12"/>
       <c r="BE15" s="8"/>
       <c r="BF15" s="8"/>
       <c r="BG15" s="8"/>
@@ -13009,7 +13023,7 @@
       <c r="CT15" s="8"/>
       <c r="CU15" s="8"/>
     </row>
-    <row r="16" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R16" s="8"/>
       <c r="S16" s="8"/>
       <c r="T16" s="8"/>
@@ -13018,37 +13032,37 @@
       <c r="W16" s="8"/>
       <c r="X16" s="8"/>
       <c r="Y16" s="8"/>
-      <c r="Z16" s="28"/>
-      <c r="AA16" s="28"/>
-      <c r="AB16" s="28"/>
-      <c r="AC16" s="28"/>
-      <c r="AD16" s="28"/>
-      <c r="AE16" s="28"/>
-      <c r="AF16" s="28"/>
-      <c r="AG16" s="28"/>
-      <c r="AH16" s="28"/>
-      <c r="AI16" s="28"/>
-      <c r="AJ16" s="28"/>
-      <c r="AK16" s="28"/>
-      <c r="AL16" s="28"/>
-      <c r="AM16" s="28"/>
-      <c r="AN16" s="28"/>
-      <c r="AO16" s="28"/>
-      <c r="AP16" s="28"/>
-      <c r="AQ16" s="28"/>
-      <c r="AR16" s="28"/>
-      <c r="AS16" s="28"/>
-      <c r="AT16" s="28"/>
-      <c r="AU16" s="28"/>
-      <c r="AV16" s="28"/>
-      <c r="AW16" s="28"/>
-      <c r="AX16" s="28"/>
-      <c r="AY16" s="28"/>
-      <c r="AZ16" s="28"/>
-      <c r="BA16" s="28"/>
-      <c r="BB16" s="28"/>
-      <c r="BC16" s="28"/>
-      <c r="BD16" s="14"/>
+      <c r="Z16" s="33"/>
+      <c r="AA16" s="33"/>
+      <c r="AB16" s="33"/>
+      <c r="AC16" s="33"/>
+      <c r="AD16" s="33"/>
+      <c r="AE16" s="33"/>
+      <c r="AF16" s="33"/>
+      <c r="AG16" s="33"/>
+      <c r="AH16" s="33"/>
+      <c r="AI16" s="33"/>
+      <c r="AJ16" s="33"/>
+      <c r="AK16" s="33"/>
+      <c r="AL16" s="33"/>
+      <c r="AM16" s="33"/>
+      <c r="AN16" s="33"/>
+      <c r="AO16" s="33"/>
+      <c r="AP16" s="33"/>
+      <c r="AQ16" s="33"/>
+      <c r="AR16" s="33"/>
+      <c r="AS16" s="33"/>
+      <c r="AT16" s="33"/>
+      <c r="AU16" s="33"/>
+      <c r="AV16" s="33"/>
+      <c r="AW16" s="33"/>
+      <c r="AX16" s="33"/>
+      <c r="AY16" s="33"/>
+      <c r="AZ16" s="33"/>
+      <c r="BA16" s="33"/>
+      <c r="BB16" s="33"/>
+      <c r="BC16" s="33"/>
+      <c r="BD16" s="12"/>
       <c r="BE16" s="8"/>
       <c r="BF16" s="8"/>
       <c r="BG16" s="8"/>
@@ -13093,132 +13107,120 @@
       <c r="CT16" s="8"/>
       <c r="CU16" s="8"/>
     </row>
-    <row r="17" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z17" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA17" s="16"/>
-      <c r="AB17" s="16"/>
-      <c r="AC17" s="16"/>
-      <c r="AD17" s="16"/>
-      <c r="AE17" s="16"/>
-      <c r="AF17" s="16"/>
-      <c r="AG17" s="16"/>
-      <c r="AH17" s="16"/>
-      <c r="AI17" s="16"/>
-      <c r="AJ17" s="16"/>
-      <c r="AK17" s="16"/>
-      <c r="AL17" s="16"/>
-      <c r="AM17" s="16"/>
-      <c r="AN17" s="16"/>
-      <c r="AO17" s="16"/>
-      <c r="AP17" s="16"/>
-      <c r="AQ17" s="16"/>
-      <c r="AR17" s="16"/>
-      <c r="AS17" s="16"/>
-      <c r="AT17" s="16"/>
-      <c r="AU17" s="16"/>
-      <c r="AV17" s="16"/>
-      <c r="AW17" s="16"/>
-      <c r="AX17" s="16"/>
-      <c r="AY17" s="16"/>
-      <c r="AZ17" s="16"/>
-      <c r="BA17" s="16"/>
-      <c r="BB17" s="16"/>
-      <c r="BC17" s="16"/>
-      <c r="BD17" s="26"/>
-      <c r="CV17"/>
-      <c r="CW17"/>
+    <row r="17" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z17" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA17" s="34"/>
+      <c r="AB17" s="34"/>
+      <c r="AC17" s="34"/>
+      <c r="AD17" s="34"/>
+      <c r="AE17" s="34"/>
+      <c r="AF17" s="34"/>
+      <c r="AG17" s="34"/>
+      <c r="AH17" s="34"/>
+      <c r="AI17" s="34"/>
+      <c r="AJ17" s="34"/>
+      <c r="AK17" s="34"/>
+      <c r="AL17" s="34"/>
+      <c r="AM17" s="34"/>
+      <c r="AN17" s="34"/>
+      <c r="AO17" s="34"/>
+      <c r="AP17" s="34"/>
+      <c r="AQ17" s="34"/>
+      <c r="AR17" s="34"/>
+      <c r="AS17" s="34"/>
+      <c r="AT17" s="34"/>
+      <c r="AU17" s="34"/>
+      <c r="AV17" s="34"/>
+      <c r="AW17" s="34"/>
+      <c r="AX17" s="34"/>
+      <c r="AY17" s="34"/>
+      <c r="AZ17" s="34"/>
+      <c r="BA17" s="34"/>
+      <c r="BB17" s="34"/>
+      <c r="BC17" s="34"/>
+      <c r="BD17" s="14"/>
     </row>
-    <row r="18" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z18" s="16"/>
-      <c r="AA18" s="16"/>
-      <c r="AB18" s="16"/>
-      <c r="AC18" s="16"/>
-      <c r="AD18" s="16"/>
-      <c r="AE18" s="16"/>
-      <c r="AF18" s="16"/>
-      <c r="AG18" s="16"/>
-      <c r="AH18" s="16"/>
-      <c r="AI18" s="16"/>
-      <c r="AJ18" s="16"/>
-      <c r="AK18" s="16"/>
-      <c r="AL18" s="16"/>
-      <c r="AM18" s="16"/>
-      <c r="AN18" s="16"/>
-      <c r="AO18" s="16"/>
-      <c r="AP18" s="16"/>
-      <c r="AQ18" s="16"/>
-      <c r="AR18" s="16"/>
-      <c r="AS18" s="16"/>
-      <c r="AT18" s="16"/>
-      <c r="AU18" s="16"/>
-      <c r="AV18" s="16"/>
-      <c r="AW18" s="16"/>
-      <c r="AX18" s="16"/>
-      <c r="AY18" s="16"/>
-      <c r="AZ18" s="16"/>
-      <c r="BA18" s="16"/>
-      <c r="BB18" s="16"/>
-      <c r="BC18" s="16"/>
-      <c r="BD18" s="26"/>
-      <c r="CV18"/>
-      <c r="CW18"/>
+    <row r="18" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z18" s="34"/>
+      <c r="AA18" s="34"/>
+      <c r="AB18" s="34"/>
+      <c r="AC18" s="34"/>
+      <c r="AD18" s="34"/>
+      <c r="AE18" s="34"/>
+      <c r="AF18" s="34"/>
+      <c r="AG18" s="34"/>
+      <c r="AH18" s="34"/>
+      <c r="AI18" s="34"/>
+      <c r="AJ18" s="34"/>
+      <c r="AK18" s="34"/>
+      <c r="AL18" s="34"/>
+      <c r="AM18" s="34"/>
+      <c r="AN18" s="34"/>
+      <c r="AO18" s="34"/>
+      <c r="AP18" s="34"/>
+      <c r="AQ18" s="34"/>
+      <c r="AR18" s="34"/>
+      <c r="AS18" s="34"/>
+      <c r="AT18" s="34"/>
+      <c r="AU18" s="34"/>
+      <c r="AV18" s="34"/>
+      <c r="AW18" s="34"/>
+      <c r="AX18" s="34"/>
+      <c r="AY18" s="34"/>
+      <c r="AZ18" s="34"/>
+      <c r="BA18" s="34"/>
+      <c r="BB18" s="34"/>
+      <c r="BC18" s="34"/>
+      <c r="BD18" s="14"/>
     </row>
-    <row r="19" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CV19"/>
-      <c r="CW19"/>
+    <row r="19" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R21" s="18"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="18"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA21" s="35"/>
+      <c r="AB21" s="35"/>
+      <c r="AC21" s="35"/>
+      <c r="AD21" s="35"/>
+      <c r="AE21" s="35"/>
+      <c r="AF21" s="35"/>
+      <c r="AG21" s="35"/>
+      <c r="AH21" s="35"/>
+      <c r="AI21" s="35"/>
+      <c r="AJ21" s="35"/>
+      <c r="AK21" s="35"/>
+      <c r="AL21" s="35"/>
+      <c r="AM21" s="35"/>
+      <c r="AN21" s="35"/>
+      <c r="AO21" s="35"/>
+      <c r="AP21" s="35"/>
+      <c r="AQ21" s="35"/>
+      <c r="AR21" s="35"/>
+      <c r="AS21" s="35"/>
+      <c r="AT21" s="35"/>
+      <c r="AU21" s="35"/>
+      <c r="AV21" s="35"/>
+      <c r="AW21" s="35"/>
+      <c r="AX21" s="35"/>
+      <c r="AY21" s="35"/>
+      <c r="AZ21" s="35"/>
+      <c r="BA21" s="35"/>
+      <c r="BB21" s="35"/>
+      <c r="BC21" s="35"/>
+      <c r="BD21" s="21"/>
     </row>
-    <row r="20" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CV20"/>
-      <c r="CW20"/>
-    </row>
-    <row r="21" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="24"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="24"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA21" s="37"/>
-      <c r="AB21" s="37"/>
-      <c r="AC21" s="37"/>
-      <c r="AD21" s="37"/>
-      <c r="AE21" s="37"/>
-      <c r="AF21" s="37"/>
-      <c r="AG21" s="37"/>
-      <c r="AH21" s="37"/>
-      <c r="AI21" s="37"/>
-      <c r="AJ21" s="37"/>
-      <c r="AK21" s="37"/>
-      <c r="AL21" s="37"/>
-      <c r="AM21" s="37"/>
-      <c r="AN21" s="37"/>
-      <c r="AO21" s="37"/>
-      <c r="AP21" s="37"/>
-      <c r="AQ21" s="37"/>
-      <c r="AR21" s="37"/>
-      <c r="AS21" s="37"/>
-      <c r="AT21" s="37"/>
-      <c r="AU21" s="37"/>
-      <c r="AV21" s="37"/>
-      <c r="AW21" s="37"/>
-      <c r="AX21" s="37"/>
-      <c r="AY21" s="37"/>
-      <c r="AZ21" s="37"/>
-      <c r="BA21" s="37"/>
-      <c r="BB21" s="37"/>
-      <c r="BC21" s="37"/>
-      <c r="BD21" s="35"/>
-      <c r="CV21"/>
-      <c r="CW21"/>
-    </row>
-    <row r="22" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Z22" s="36"/>
       <c r="AA22" s="36"/>
       <c r="AB22" s="36"/>
@@ -13249,251 +13251,225 @@
       <c r="BA22" s="36"/>
       <c r="BB22" s="36"/>
       <c r="BC22" s="36"/>
-      <c r="BD22" s="35"/>
-      <c r="CV22"/>
-      <c r="CW22"/>
+      <c r="BD22" s="21"/>
     </row>
-    <row r="23" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z23" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA23" s="34"/>
-      <c r="AB23" s="34"/>
-      <c r="AC23" s="34"/>
-      <c r="AD23" s="34"/>
-      <c r="AE23" s="34"/>
-      <c r="AF23" s="34"/>
-      <c r="AG23" s="34"/>
-      <c r="AH23" s="34"/>
-      <c r="AI23" s="34"/>
-      <c r="AJ23" s="34"/>
-      <c r="AK23" s="34"/>
-      <c r="AL23" s="34"/>
-      <c r="AM23" s="34"/>
-      <c r="AN23" s="34"/>
-      <c r="AO23" s="34"/>
-      <c r="AP23" s="34"/>
-      <c r="AQ23" s="34"/>
-      <c r="AR23" s="34"/>
-      <c r="AS23" s="34"/>
-      <c r="AT23" s="34"/>
-      <c r="AU23" s="34"/>
-      <c r="AV23" s="34"/>
-      <c r="AW23" s="34"/>
-      <c r="AX23" s="34"/>
-      <c r="AY23" s="34"/>
-      <c r="AZ23" s="34"/>
-      <c r="BA23" s="34"/>
-      <c r="BB23" s="34"/>
-      <c r="BC23" s="34"/>
-      <c r="BD23" s="33"/>
-      <c r="CV23"/>
-      <c r="CW23"/>
+    <row r="23" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z23" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA23" s="37"/>
+      <c r="AB23" s="37"/>
+      <c r="AC23" s="37"/>
+      <c r="AD23" s="37"/>
+      <c r="AE23" s="37"/>
+      <c r="AF23" s="37"/>
+      <c r="AG23" s="37"/>
+      <c r="AH23" s="37"/>
+      <c r="AI23" s="37"/>
+      <c r="AJ23" s="37"/>
+      <c r="AK23" s="37"/>
+      <c r="AL23" s="37"/>
+      <c r="AM23" s="37"/>
+      <c r="AN23" s="37"/>
+      <c r="AO23" s="37"/>
+      <c r="AP23" s="37"/>
+      <c r="AQ23" s="37"/>
+      <c r="AR23" s="37"/>
+      <c r="AS23" s="37"/>
+      <c r="AT23" s="37"/>
+      <c r="AU23" s="37"/>
+      <c r="AV23" s="37"/>
+      <c r="AW23" s="37"/>
+      <c r="AX23" s="37"/>
+      <c r="AY23" s="37"/>
+      <c r="AZ23" s="37"/>
+      <c r="BA23" s="37"/>
+      <c r="BB23" s="37"/>
+      <c r="BC23" s="37"/>
+      <c r="BD23" s="20"/>
     </row>
-    <row r="24" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z24" s="34"/>
-      <c r="AA24" s="34"/>
-      <c r="AB24" s="34"/>
-      <c r="AC24" s="34"/>
-      <c r="AD24" s="34"/>
-      <c r="AE24" s="34"/>
-      <c r="AF24" s="34"/>
-      <c r="AG24" s="34"/>
-      <c r="AH24" s="34"/>
-      <c r="AI24" s="34"/>
-      <c r="AJ24" s="34"/>
-      <c r="AK24" s="34"/>
-      <c r="AL24" s="34"/>
-      <c r="AM24" s="34"/>
-      <c r="AN24" s="34"/>
-      <c r="AO24" s="34"/>
-      <c r="AP24" s="34"/>
-      <c r="AQ24" s="34"/>
-      <c r="AR24" s="34"/>
-      <c r="AS24" s="34"/>
-      <c r="AT24" s="34"/>
-      <c r="AU24" s="34"/>
-      <c r="AV24" s="34"/>
-      <c r="AW24" s="34"/>
-      <c r="AX24" s="34"/>
-      <c r="AY24" s="34"/>
-      <c r="AZ24" s="34"/>
-      <c r="BA24" s="34"/>
-      <c r="BB24" s="34"/>
-      <c r="BC24" s="34"/>
-      <c r="BD24" s="33"/>
-      <c r="CV24"/>
-      <c r="CW24"/>
+    <row r="24" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z24" s="37"/>
+      <c r="AA24" s="37"/>
+      <c r="AB24" s="37"/>
+      <c r="AC24" s="37"/>
+      <c r="AD24" s="37"/>
+      <c r="AE24" s="37"/>
+      <c r="AF24" s="37"/>
+      <c r="AG24" s="37"/>
+      <c r="AH24" s="37"/>
+      <c r="AI24" s="37"/>
+      <c r="AJ24" s="37"/>
+      <c r="AK24" s="37"/>
+      <c r="AL24" s="37"/>
+      <c r="AM24" s="37"/>
+      <c r="AN24" s="37"/>
+      <c r="AO24" s="37"/>
+      <c r="AP24" s="37"/>
+      <c r="AQ24" s="37"/>
+      <c r="AR24" s="37"/>
+      <c r="AS24" s="37"/>
+      <c r="AT24" s="37"/>
+      <c r="AU24" s="37"/>
+      <c r="AV24" s="37"/>
+      <c r="AW24" s="37"/>
+      <c r="AX24" s="37"/>
+      <c r="AY24" s="37"/>
+      <c r="AZ24" s="37"/>
+      <c r="BA24" s="37"/>
+      <c r="BB24" s="37"/>
+      <c r="BC24" s="37"/>
+      <c r="BD24" s="20"/>
     </row>
-    <row r="25" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CV25"/>
-      <c r="CW25"/>
+    <row r="25" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z26" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA26" s="34"/>
+      <c r="AB26" s="34"/>
+      <c r="AC26" s="34"/>
+      <c r="AD26" s="34"/>
+      <c r="AE26" s="34"/>
+      <c r="AF26" s="34"/>
+      <c r="AG26" s="34"/>
+      <c r="AH26" s="34"/>
+      <c r="AI26" s="34"/>
+      <c r="AJ26" s="34"/>
+      <c r="AK26" s="34"/>
+      <c r="AL26" s="34"/>
+      <c r="AM26" s="34"/>
+      <c r="AN26" s="34"/>
+      <c r="AO26" s="34"/>
+      <c r="AP26" s="34"/>
+      <c r="AQ26" s="34"/>
+      <c r="AR26" s="34"/>
+      <c r="AS26" s="34"/>
+      <c r="AT26" s="34"/>
+      <c r="AU26" s="34"/>
+      <c r="AV26" s="34"/>
+      <c r="AW26" s="34"/>
+      <c r="AX26" s="34"/>
+      <c r="AY26" s="34"/>
+      <c r="AZ26" s="34"/>
+      <c r="BA26" s="34"/>
+      <c r="BB26" s="34"/>
+      <c r="BC26" s="34"/>
+      <c r="BD26" s="14"/>
     </row>
-    <row r="26" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z26" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA26" s="16"/>
-      <c r="AB26" s="16"/>
-      <c r="AC26" s="16"/>
-      <c r="AD26" s="16"/>
-      <c r="AE26" s="16"/>
-      <c r="AF26" s="16"/>
-      <c r="AG26" s="16"/>
-      <c r="AH26" s="16"/>
-      <c r="AI26" s="16"/>
-      <c r="AJ26" s="16"/>
-      <c r="AK26" s="16"/>
-      <c r="AL26" s="16"/>
-      <c r="AM26" s="16"/>
-      <c r="AN26" s="16"/>
-      <c r="AO26" s="16"/>
-      <c r="AP26" s="16"/>
-      <c r="AQ26" s="16"/>
-      <c r="AR26" s="16"/>
-      <c r="AS26" s="16"/>
-      <c r="AT26" s="16"/>
-      <c r="AU26" s="16"/>
-      <c r="AV26" s="16"/>
-      <c r="AW26" s="16"/>
-      <c r="AX26" s="16"/>
-      <c r="AY26" s="16"/>
-      <c r="AZ26" s="16"/>
-      <c r="BA26" s="16"/>
-      <c r="BB26" s="16"/>
-      <c r="BC26" s="16"/>
-      <c r="BD26" s="26"/>
-      <c r="CV26"/>
-      <c r="CW26"/>
+    <row r="27" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z27" s="34"/>
+      <c r="AA27" s="34"/>
+      <c r="AB27" s="34"/>
+      <c r="AC27" s="34"/>
+      <c r="AD27" s="34"/>
+      <c r="AE27" s="34"/>
+      <c r="AF27" s="34"/>
+      <c r="AG27" s="34"/>
+      <c r="AH27" s="34"/>
+      <c r="AI27" s="34"/>
+      <c r="AJ27" s="34"/>
+      <c r="AK27" s="34"/>
+      <c r="AL27" s="34"/>
+      <c r="AM27" s="34"/>
+      <c r="AN27" s="34"/>
+      <c r="AO27" s="34"/>
+      <c r="AP27" s="34"/>
+      <c r="AQ27" s="34"/>
+      <c r="AR27" s="34"/>
+      <c r="AS27" s="34"/>
+      <c r="AT27" s="34"/>
+      <c r="AU27" s="34"/>
+      <c r="AV27" s="34"/>
+      <c r="AW27" s="34"/>
+      <c r="AX27" s="34"/>
+      <c r="AY27" s="34"/>
+      <c r="AZ27" s="34"/>
+      <c r="BA27" s="34"/>
+      <c r="BB27" s="34"/>
+      <c r="BC27" s="34"/>
+      <c r="BD27" s="14"/>
     </row>
-    <row r="27" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z27" s="16"/>
-      <c r="AA27" s="16"/>
-      <c r="AB27" s="16"/>
-      <c r="AC27" s="16"/>
-      <c r="AD27" s="16"/>
-      <c r="AE27" s="16"/>
-      <c r="AF27" s="16"/>
-      <c r="AG27" s="16"/>
-      <c r="AH27" s="16"/>
-      <c r="AI27" s="16"/>
-      <c r="AJ27" s="16"/>
-      <c r="AK27" s="16"/>
-      <c r="AL27" s="16"/>
-      <c r="AM27" s="16"/>
-      <c r="AN27" s="16"/>
-      <c r="AO27" s="16"/>
-      <c r="AP27" s="16"/>
-      <c r="AQ27" s="16"/>
-      <c r="AR27" s="16"/>
-      <c r="AS27" s="16"/>
-      <c r="AT27" s="16"/>
-      <c r="AU27" s="16"/>
-      <c r="AV27" s="16"/>
-      <c r="AW27" s="16"/>
-      <c r="AX27" s="16"/>
-      <c r="AY27" s="16"/>
-      <c r="AZ27" s="16"/>
-      <c r="BA27" s="16"/>
-      <c r="BB27" s="16"/>
-      <c r="BC27" s="16"/>
-      <c r="BD27" s="26"/>
-      <c r="CV27"/>
-      <c r="CW27"/>
+    <row r="28" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="13"/>
+      <c r="AC28" s="13"/>
+      <c r="AD28" s="13"/>
+      <c r="AE28" s="13"/>
+      <c r="AF28" s="13"/>
+      <c r="AG28" s="13"/>
+      <c r="AH28" s="13"/>
+      <c r="AI28" s="13"/>
+      <c r="AJ28" s="13"/>
+      <c r="AK28" s="13"/>
+      <c r="AL28" s="13"/>
+      <c r="AM28" s="13"/>
+      <c r="AN28" s="13"/>
+      <c r="AO28" s="13"/>
+      <c r="AP28" s="13"/>
+      <c r="AQ28" s="13"/>
+      <c r="AR28" s="13"/>
+      <c r="AS28" s="13"/>
+      <c r="AT28" s="13"/>
+      <c r="AU28" s="13"/>
+      <c r="AV28" s="13"/>
+      <c r="AW28" s="13"/>
+      <c r="AX28" s="13"/>
+      <c r="AY28" s="13"/>
+      <c r="AZ28" s="13"/>
+      <c r="BA28" s="13"/>
+      <c r="BB28" s="13"/>
+      <c r="BC28" s="13"/>
+      <c r="BD28" s="13"/>
     </row>
-    <row r="28" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z28" s="15"/>
-      <c r="AA28" s="15"/>
-      <c r="AB28" s="15"/>
-      <c r="AC28" s="15"/>
-      <c r="AD28" s="15"/>
-      <c r="AE28" s="15"/>
-      <c r="AF28" s="15"/>
-      <c r="AG28" s="15"/>
-      <c r="AH28" s="15"/>
-      <c r="AI28" s="15"/>
-      <c r="AJ28" s="15"/>
-      <c r="AK28" s="15"/>
-      <c r="AL28" s="15"/>
-      <c r="AM28" s="15"/>
-      <c r="AN28" s="15"/>
-      <c r="AO28" s="15"/>
-      <c r="AP28" s="15"/>
-      <c r="AQ28" s="15"/>
-      <c r="AR28" s="15"/>
-      <c r="AS28" s="15"/>
-      <c r="AT28" s="15"/>
-      <c r="AU28" s="15"/>
-      <c r="AV28" s="15"/>
-      <c r="AW28" s="15"/>
-      <c r="AX28" s="15"/>
-      <c r="AY28" s="15"/>
-      <c r="AZ28" s="15"/>
-      <c r="BA28" s="15"/>
-      <c r="BB28" s="15"/>
-      <c r="BC28" s="15"/>
-      <c r="BD28" s="15"/>
-      <c r="CV28"/>
-      <c r="CW28"/>
+    <row r="29" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="18:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R32" s="18"/>
+      <c r="S32" s="18"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="18"/>
+      <c r="V32" s="18"/>
+      <c r="W32" s="18"/>
+      <c r="X32" s="18"/>
+      <c r="Y32" s="18"/>
+      <c r="Z32" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA32" s="38"/>
+      <c r="AB32" s="38"/>
+      <c r="AC32" s="38"/>
+      <c r="AD32" s="38"/>
+      <c r="AE32" s="38"/>
+      <c r="AF32" s="38"/>
+      <c r="AG32" s="38"/>
+      <c r="AH32" s="38"/>
+      <c r="AI32" s="38"/>
+      <c r="AJ32" s="38"/>
+      <c r="AK32" s="38"/>
+      <c r="AL32" s="38"/>
+      <c r="AM32" s="38"/>
+      <c r="AN32" s="38"/>
+      <c r="AO32" s="38"/>
+      <c r="AP32" s="38"/>
+      <c r="AQ32" s="38"/>
+      <c r="AR32" s="38"/>
+      <c r="AS32" s="38"/>
+      <c r="AT32" s="38"/>
+      <c r="AU32" s="38"/>
+      <c r="AV32" s="38"/>
+      <c r="AW32" s="38"/>
+      <c r="AX32" s="38"/>
+      <c r="AY32" s="38"/>
+      <c r="AZ32" s="38"/>
+      <c r="BA32" s="38"/>
+      <c r="BB32" s="38"/>
+      <c r="BC32" s="38"/>
+      <c r="BD32" s="16"/>
     </row>
-    <row r="29" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CV29"/>
-      <c r="CW29"/>
-    </row>
-    <row r="30" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CV30"/>
-      <c r="CW30"/>
-    </row>
-    <row r="31" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CV31"/>
-      <c r="CW31"/>
-    </row>
-    <row r="32" spans="18:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R32" s="24"/>
-      <c r="S32" s="24"/>
-      <c r="T32" s="24"/>
-      <c r="U32" s="24"/>
-      <c r="V32" s="24"/>
-      <c r="W32" s="24"/>
-      <c r="X32" s="24"/>
-      <c r="Y32" s="24"/>
-      <c r="Z32" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA32" s="23"/>
-      <c r="AB32" s="23"/>
-      <c r="AC32" s="23"/>
-      <c r="AD32" s="23"/>
-      <c r="AE32" s="23"/>
-      <c r="AF32" s="23"/>
-      <c r="AG32" s="23"/>
-      <c r="AH32" s="23"/>
-      <c r="AI32" s="23"/>
-      <c r="AJ32" s="23"/>
-      <c r="AK32" s="23"/>
-      <c r="AL32" s="23"/>
-      <c r="AM32" s="23"/>
-      <c r="AN32" s="23"/>
-      <c r="AO32" s="23"/>
-      <c r="AP32" s="23"/>
-      <c r="AQ32" s="23"/>
-      <c r="AR32" s="23"/>
-      <c r="AS32" s="23"/>
-      <c r="AT32" s="23"/>
-      <c r="AU32" s="23"/>
-      <c r="AV32" s="23"/>
-      <c r="AW32" s="23"/>
-      <c r="AX32" s="23"/>
-      <c r="AY32" s="23"/>
-      <c r="AZ32" s="23"/>
-      <c r="BA32" s="23"/>
-      <c r="BB32" s="23"/>
-      <c r="BC32" s="23"/>
-      <c r="BD32" s="19"/>
-      <c r="CV32"/>
-      <c r="CW32"/>
-    </row>
-    <row r="33" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R33" s="8"/>
       <c r="S33" s="8"/>
       <c r="T33" s="8"/>
@@ -13502,37 +13478,37 @@
       <c r="W33" s="8"/>
       <c r="X33" s="8"/>
       <c r="Y33" s="8"/>
-      <c r="Z33" s="20"/>
-      <c r="AA33" s="20"/>
-      <c r="AB33" s="20"/>
-      <c r="AC33" s="20"/>
-      <c r="AD33" s="20"/>
-      <c r="AE33" s="20"/>
-      <c r="AF33" s="20"/>
-      <c r="AG33" s="20"/>
-      <c r="AH33" s="20"/>
-      <c r="AI33" s="20"/>
-      <c r="AJ33" s="20"/>
-      <c r="AK33" s="20"/>
-      <c r="AL33" s="20"/>
-      <c r="AM33" s="20"/>
-      <c r="AN33" s="20"/>
-      <c r="AO33" s="20"/>
-      <c r="AP33" s="20"/>
-      <c r="AQ33" s="20"/>
-      <c r="AR33" s="20"/>
-      <c r="AS33" s="20"/>
-      <c r="AT33" s="20"/>
-      <c r="AU33" s="20"/>
-      <c r="AV33" s="20"/>
-      <c r="AW33" s="20"/>
-      <c r="AX33" s="20"/>
-      <c r="AY33" s="20"/>
-      <c r="AZ33" s="20"/>
-      <c r="BA33" s="20"/>
-      <c r="BB33" s="20"/>
-      <c r="BC33" s="20"/>
-      <c r="BD33" s="19"/>
+      <c r="Z33" s="39"/>
+      <c r="AA33" s="39"/>
+      <c r="AB33" s="39"/>
+      <c r="AC33" s="39"/>
+      <c r="AD33" s="39"/>
+      <c r="AE33" s="39"/>
+      <c r="AF33" s="39"/>
+      <c r="AG33" s="39"/>
+      <c r="AH33" s="39"/>
+      <c r="AI33" s="39"/>
+      <c r="AJ33" s="39"/>
+      <c r="AK33" s="39"/>
+      <c r="AL33" s="39"/>
+      <c r="AM33" s="39"/>
+      <c r="AN33" s="39"/>
+      <c r="AO33" s="39"/>
+      <c r="AP33" s="39"/>
+      <c r="AQ33" s="39"/>
+      <c r="AR33" s="39"/>
+      <c r="AS33" s="39"/>
+      <c r="AT33" s="39"/>
+      <c r="AU33" s="39"/>
+      <c r="AV33" s="39"/>
+      <c r="AW33" s="39"/>
+      <c r="AX33" s="39"/>
+      <c r="AY33" s="39"/>
+      <c r="AZ33" s="39"/>
+      <c r="BA33" s="39"/>
+      <c r="BB33" s="39"/>
+      <c r="BC33" s="39"/>
+      <c r="BD33" s="16"/>
       <c r="BE33" s="8"/>
       <c r="BF33" s="8"/>
       <c r="BG33" s="8"/>
@@ -13577,7 +13553,7 @@
       <c r="CT33" s="8"/>
       <c r="CU33" s="8"/>
     </row>
-    <row r="34" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R34" s="8"/>
       <c r="S34" s="8"/>
       <c r="T34" s="8"/>
@@ -13586,84 +13562,84 @@
       <c r="W34" s="8"/>
       <c r="X34" s="8"/>
       <c r="Y34" s="8"/>
-      <c r="Z34" s="20"/>
-      <c r="AA34" s="20"/>
-      <c r="AB34" s="20"/>
-      <c r="AC34" s="20"/>
-      <c r="AD34" s="20"/>
-      <c r="AE34" s="20"/>
-      <c r="AF34" s="20"/>
-      <c r="AG34" s="20"/>
-      <c r="AH34" s="20"/>
-      <c r="AI34" s="20"/>
-      <c r="AJ34" s="20"/>
-      <c r="AK34" s="20"/>
-      <c r="AL34" s="20"/>
-      <c r="AM34" s="20"/>
-      <c r="AN34" s="20"/>
-      <c r="AO34" s="20"/>
-      <c r="AP34" s="20"/>
-      <c r="AQ34" s="20"/>
-      <c r="AR34" s="20"/>
-      <c r="AS34" s="20"/>
-      <c r="AT34" s="20"/>
-      <c r="AU34" s="20"/>
-      <c r="AV34" s="20"/>
-      <c r="AW34" s="20"/>
-      <c r="AX34" s="20"/>
-      <c r="AY34" s="20"/>
-      <c r="AZ34" s="20"/>
-      <c r="BA34" s="20"/>
-      <c r="BB34" s="20"/>
-      <c r="BC34" s="20"/>
-      <c r="BD34" s="19"/>
+      <c r="Z34" s="39"/>
+      <c r="AA34" s="39"/>
+      <c r="AB34" s="39"/>
+      <c r="AC34" s="39"/>
+      <c r="AD34" s="39"/>
+      <c r="AE34" s="39"/>
+      <c r="AF34" s="39"/>
+      <c r="AG34" s="39"/>
+      <c r="AH34" s="39"/>
+      <c r="AI34" s="39"/>
+      <c r="AJ34" s="39"/>
+      <c r="AK34" s="39"/>
+      <c r="AL34" s="39"/>
+      <c r="AM34" s="39"/>
+      <c r="AN34" s="39"/>
+      <c r="AO34" s="39"/>
+      <c r="AP34" s="39"/>
+      <c r="AQ34" s="39"/>
+      <c r="AR34" s="39"/>
+      <c r="AS34" s="39"/>
+      <c r="AT34" s="39"/>
+      <c r="AU34" s="39"/>
+      <c r="AV34" s="39"/>
+      <c r="AW34" s="39"/>
+      <c r="AX34" s="39"/>
+      <c r="AY34" s="39"/>
+      <c r="AZ34" s="39"/>
+      <c r="BA34" s="39"/>
+      <c r="BB34" s="39"/>
+      <c r="BC34" s="39"/>
+      <c r="BD34" s="16"/>
       <c r="BE34" s="8"/>
-      <c r="BF34" s="24"/>
-      <c r="BG34" s="24"/>
-      <c r="BH34" s="24"/>
-      <c r="BI34" s="24"/>
-      <c r="BJ34" s="24"/>
-      <c r="BK34" s="24"/>
-      <c r="BL34" s="24"/>
-      <c r="BM34" s="24"/>
-      <c r="BN34" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="BO34" s="29"/>
-      <c r="BP34" s="29"/>
-      <c r="BQ34" s="29"/>
-      <c r="BR34" s="29"/>
-      <c r="BS34" s="29"/>
-      <c r="BT34" s="29"/>
-      <c r="BU34" s="29"/>
-      <c r="BV34" s="29"/>
-      <c r="BW34" s="29"/>
-      <c r="BX34" s="29"/>
-      <c r="BY34" s="29"/>
-      <c r="BZ34" s="29"/>
-      <c r="CA34" s="29"/>
-      <c r="CB34" s="29"/>
-      <c r="CC34" s="29"/>
-      <c r="CD34" s="29"/>
-      <c r="CE34" s="29"/>
-      <c r="CF34" s="29"/>
-      <c r="CG34" s="29"/>
-      <c r="CH34" s="29"/>
-      <c r="CI34" s="29"/>
-      <c r="CJ34" s="29"/>
-      <c r="CK34" s="29"/>
-      <c r="CL34" s="29"/>
-      <c r="CM34" s="29"/>
-      <c r="CN34" s="29"/>
-      <c r="CO34" s="29"/>
-      <c r="CP34" s="29"/>
-      <c r="CQ34" s="29"/>
-      <c r="CR34" s="21"/>
-      <c r="CS34" s="21"/>
-      <c r="CT34" s="21"/>
-      <c r="CU34" s="21"/>
+      <c r="BF34" s="18"/>
+      <c r="BG34" s="18"/>
+      <c r="BH34" s="18"/>
+      <c r="BI34" s="18"/>
+      <c r="BJ34" s="18"/>
+      <c r="BK34" s="18"/>
+      <c r="BL34" s="18"/>
+      <c r="BM34" s="18"/>
+      <c r="BN34" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="BO34" s="30"/>
+      <c r="BP34" s="30"/>
+      <c r="BQ34" s="30"/>
+      <c r="BR34" s="30"/>
+      <c r="BS34" s="30"/>
+      <c r="BT34" s="30"/>
+      <c r="BU34" s="30"/>
+      <c r="BV34" s="30"/>
+      <c r="BW34" s="30"/>
+      <c r="BX34" s="30"/>
+      <c r="BY34" s="30"/>
+      <c r="BZ34" s="30"/>
+      <c r="CA34" s="30"/>
+      <c r="CB34" s="30"/>
+      <c r="CC34" s="30"/>
+      <c r="CD34" s="30"/>
+      <c r="CE34" s="30"/>
+      <c r="CF34" s="30"/>
+      <c r="CG34" s="30"/>
+      <c r="CH34" s="30"/>
+      <c r="CI34" s="30"/>
+      <c r="CJ34" s="30"/>
+      <c r="CK34" s="30"/>
+      <c r="CL34" s="30"/>
+      <c r="CM34" s="30"/>
+      <c r="CN34" s="30"/>
+      <c r="CO34" s="30"/>
+      <c r="CP34" s="30"/>
+      <c r="CQ34" s="30"/>
+      <c r="CR34" s="17"/>
+      <c r="CS34" s="17"/>
+      <c r="CT34" s="17"/>
+      <c r="CU34" s="17"/>
     </row>
-    <row r="35" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R35" s="8"/>
       <c r="S35" s="8"/>
       <c r="T35" s="8"/>
@@ -13672,37 +13648,37 @@
       <c r="W35" s="8"/>
       <c r="X35" s="8"/>
       <c r="Y35" s="8"/>
-      <c r="Z35" s="20"/>
-      <c r="AA35" s="20"/>
-      <c r="AB35" s="20"/>
-      <c r="AC35" s="20"/>
-      <c r="AD35" s="20"/>
-      <c r="AE35" s="20"/>
-      <c r="AF35" s="20"/>
-      <c r="AG35" s="20"/>
-      <c r="AH35" s="20"/>
-      <c r="AI35" s="20"/>
-      <c r="AJ35" s="20"/>
-      <c r="AK35" s="20"/>
-      <c r="AL35" s="20"/>
-      <c r="AM35" s="20"/>
-      <c r="AN35" s="20"/>
-      <c r="AO35" s="20"/>
-      <c r="AP35" s="20"/>
-      <c r="AQ35" s="20"/>
-      <c r="AR35" s="20"/>
-      <c r="AS35" s="20"/>
-      <c r="AT35" s="20"/>
-      <c r="AU35" s="20"/>
-      <c r="AV35" s="20"/>
-      <c r="AW35" s="20"/>
-      <c r="AX35" s="20"/>
-      <c r="AY35" s="20"/>
-      <c r="AZ35" s="20"/>
-      <c r="BA35" s="20"/>
-      <c r="BB35" s="20"/>
-      <c r="BC35" s="20"/>
-      <c r="BD35" s="19"/>
+      <c r="Z35" s="39"/>
+      <c r="AA35" s="39"/>
+      <c r="AB35" s="39"/>
+      <c r="AC35" s="39"/>
+      <c r="AD35" s="39"/>
+      <c r="AE35" s="39"/>
+      <c r="AF35" s="39"/>
+      <c r="AG35" s="39"/>
+      <c r="AH35" s="39"/>
+      <c r="AI35" s="39"/>
+      <c r="AJ35" s="39"/>
+      <c r="AK35" s="39"/>
+      <c r="AL35" s="39"/>
+      <c r="AM35" s="39"/>
+      <c r="AN35" s="39"/>
+      <c r="AO35" s="39"/>
+      <c r="AP35" s="39"/>
+      <c r="AQ35" s="39"/>
+      <c r="AR35" s="39"/>
+      <c r="AS35" s="39"/>
+      <c r="AT35" s="39"/>
+      <c r="AU35" s="39"/>
+      <c r="AV35" s="39"/>
+      <c r="AW35" s="39"/>
+      <c r="AX35" s="39"/>
+      <c r="AY35" s="39"/>
+      <c r="AZ35" s="39"/>
+      <c r="BA35" s="39"/>
+      <c r="BB35" s="39"/>
+      <c r="BC35" s="39"/>
+      <c r="BD35" s="16"/>
       <c r="BE35" s="8"/>
       <c r="BF35" s="8"/>
       <c r="BG35" s="8"/>
@@ -13712,42 +13688,42 @@
       <c r="BK35" s="8"/>
       <c r="BL35" s="8"/>
       <c r="BM35" s="8"/>
-      <c r="BN35" s="22"/>
-      <c r="BO35" s="22"/>
-      <c r="BP35" s="22"/>
-      <c r="BQ35" s="22"/>
-      <c r="BR35" s="22"/>
-      <c r="BS35" s="22"/>
-      <c r="BT35" s="22"/>
-      <c r="BU35" s="22"/>
-      <c r="BV35" s="22"/>
-      <c r="BW35" s="22"/>
-      <c r="BX35" s="22"/>
-      <c r="BY35" s="22"/>
-      <c r="BZ35" s="22"/>
-      <c r="CA35" s="22"/>
-      <c r="CB35" s="22"/>
-      <c r="CC35" s="22"/>
-      <c r="CD35" s="22"/>
-      <c r="CE35" s="22"/>
-      <c r="CF35" s="22"/>
-      <c r="CG35" s="22"/>
-      <c r="CH35" s="22"/>
-      <c r="CI35" s="22"/>
-      <c r="CJ35" s="22"/>
-      <c r="CK35" s="22"/>
-      <c r="CL35" s="22"/>
-      <c r="CM35" s="22"/>
-      <c r="CN35" s="22"/>
-      <c r="CO35" s="22"/>
-      <c r="CP35" s="22"/>
-      <c r="CQ35" s="22"/>
-      <c r="CR35" s="21"/>
-      <c r="CS35" s="21"/>
-      <c r="CT35" s="21"/>
-      <c r="CU35" s="21"/>
+      <c r="BN35" s="31"/>
+      <c r="BO35" s="31"/>
+      <c r="BP35" s="31"/>
+      <c r="BQ35" s="31"/>
+      <c r="BR35" s="31"/>
+      <c r="BS35" s="31"/>
+      <c r="BT35" s="31"/>
+      <c r="BU35" s="31"/>
+      <c r="BV35" s="31"/>
+      <c r="BW35" s="31"/>
+      <c r="BX35" s="31"/>
+      <c r="BY35" s="31"/>
+      <c r="BZ35" s="31"/>
+      <c r="CA35" s="31"/>
+      <c r="CB35" s="31"/>
+      <c r="CC35" s="31"/>
+      <c r="CD35" s="31"/>
+      <c r="CE35" s="31"/>
+      <c r="CF35" s="31"/>
+      <c r="CG35" s="31"/>
+      <c r="CH35" s="31"/>
+      <c r="CI35" s="31"/>
+      <c r="CJ35" s="31"/>
+      <c r="CK35" s="31"/>
+      <c r="CL35" s="31"/>
+      <c r="CM35" s="31"/>
+      <c r="CN35" s="31"/>
+      <c r="CO35" s="31"/>
+      <c r="CP35" s="31"/>
+      <c r="CQ35" s="31"/>
+      <c r="CR35" s="17"/>
+      <c r="CS35" s="17"/>
+      <c r="CT35" s="17"/>
+      <c r="CU35" s="17"/>
     </row>
-    <row r="36" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R36" s="8"/>
       <c r="S36" s="8"/>
       <c r="T36" s="8"/>
@@ -13756,37 +13732,37 @@
       <c r="W36" s="8"/>
       <c r="X36" s="8"/>
       <c r="Y36" s="8"/>
-      <c r="Z36" s="20"/>
-      <c r="AA36" s="20"/>
-      <c r="AB36" s="20"/>
-      <c r="AC36" s="20"/>
-      <c r="AD36" s="20"/>
-      <c r="AE36" s="20"/>
-      <c r="AF36" s="20"/>
-      <c r="AG36" s="20"/>
-      <c r="AH36" s="20"/>
-      <c r="AI36" s="20"/>
-      <c r="AJ36" s="20"/>
-      <c r="AK36" s="20"/>
-      <c r="AL36" s="20"/>
-      <c r="AM36" s="20"/>
-      <c r="AN36" s="20"/>
-      <c r="AO36" s="20"/>
-      <c r="AP36" s="20"/>
-      <c r="AQ36" s="20"/>
-      <c r="AR36" s="20"/>
-      <c r="AS36" s="20"/>
-      <c r="AT36" s="20"/>
-      <c r="AU36" s="20"/>
-      <c r="AV36" s="20"/>
-      <c r="AW36" s="20"/>
-      <c r="AX36" s="20"/>
-      <c r="AY36" s="20"/>
-      <c r="AZ36" s="20"/>
-      <c r="BA36" s="20"/>
-      <c r="BB36" s="20"/>
-      <c r="BC36" s="20"/>
-      <c r="BD36" s="19"/>
+      <c r="Z36" s="39"/>
+      <c r="AA36" s="39"/>
+      <c r="AB36" s="39"/>
+      <c r="AC36" s="39"/>
+      <c r="AD36" s="39"/>
+      <c r="AE36" s="39"/>
+      <c r="AF36" s="39"/>
+      <c r="AG36" s="39"/>
+      <c r="AH36" s="39"/>
+      <c r="AI36" s="39"/>
+      <c r="AJ36" s="39"/>
+      <c r="AK36" s="39"/>
+      <c r="AL36" s="39"/>
+      <c r="AM36" s="39"/>
+      <c r="AN36" s="39"/>
+      <c r="AO36" s="39"/>
+      <c r="AP36" s="39"/>
+      <c r="AQ36" s="39"/>
+      <c r="AR36" s="39"/>
+      <c r="AS36" s="39"/>
+      <c r="AT36" s="39"/>
+      <c r="AU36" s="39"/>
+      <c r="AV36" s="39"/>
+      <c r="AW36" s="39"/>
+      <c r="AX36" s="39"/>
+      <c r="AY36" s="39"/>
+      <c r="AZ36" s="39"/>
+      <c r="BA36" s="39"/>
+      <c r="BB36" s="39"/>
+      <c r="BC36" s="39"/>
+      <c r="BD36" s="16"/>
       <c r="BE36" s="8"/>
       <c r="BF36" s="8"/>
       <c r="BG36" s="8"/>
@@ -13796,42 +13772,42 @@
       <c r="BK36" s="8"/>
       <c r="BL36" s="8"/>
       <c r="BM36" s="8"/>
-      <c r="BN36" s="22"/>
-      <c r="BO36" s="22"/>
-      <c r="BP36" s="22"/>
-      <c r="BQ36" s="22"/>
-      <c r="BR36" s="22"/>
-      <c r="BS36" s="22"/>
-      <c r="BT36" s="22"/>
-      <c r="BU36" s="22"/>
-      <c r="BV36" s="22"/>
-      <c r="BW36" s="22"/>
-      <c r="BX36" s="22"/>
-      <c r="BY36" s="22"/>
-      <c r="BZ36" s="22"/>
-      <c r="CA36" s="22"/>
-      <c r="CB36" s="22"/>
-      <c r="CC36" s="22"/>
-      <c r="CD36" s="22"/>
-      <c r="CE36" s="22"/>
-      <c r="CF36" s="22"/>
-      <c r="CG36" s="22"/>
-      <c r="CH36" s="22"/>
-      <c r="CI36" s="22"/>
-      <c r="CJ36" s="22"/>
-      <c r="CK36" s="22"/>
-      <c r="CL36" s="22"/>
-      <c r="CM36" s="22"/>
-      <c r="CN36" s="22"/>
-      <c r="CO36" s="22"/>
-      <c r="CP36" s="22"/>
-      <c r="CQ36" s="22"/>
-      <c r="CR36" s="21"/>
-      <c r="CS36" s="21"/>
-      <c r="CT36" s="21"/>
-      <c r="CU36" s="21"/>
+      <c r="BN36" s="31"/>
+      <c r="BO36" s="31"/>
+      <c r="BP36" s="31"/>
+      <c r="BQ36" s="31"/>
+      <c r="BR36" s="31"/>
+      <c r="BS36" s="31"/>
+      <c r="BT36" s="31"/>
+      <c r="BU36" s="31"/>
+      <c r="BV36" s="31"/>
+      <c r="BW36" s="31"/>
+      <c r="BX36" s="31"/>
+      <c r="BY36" s="31"/>
+      <c r="BZ36" s="31"/>
+      <c r="CA36" s="31"/>
+      <c r="CB36" s="31"/>
+      <c r="CC36" s="31"/>
+      <c r="CD36" s="31"/>
+      <c r="CE36" s="31"/>
+      <c r="CF36" s="31"/>
+      <c r="CG36" s="31"/>
+      <c r="CH36" s="31"/>
+      <c r="CI36" s="31"/>
+      <c r="CJ36" s="31"/>
+      <c r="CK36" s="31"/>
+      <c r="CL36" s="31"/>
+      <c r="CM36" s="31"/>
+      <c r="CN36" s="31"/>
+      <c r="CO36" s="31"/>
+      <c r="CP36" s="31"/>
+      <c r="CQ36" s="31"/>
+      <c r="CR36" s="17"/>
+      <c r="CS36" s="17"/>
+      <c r="CT36" s="17"/>
+      <c r="CU36" s="17"/>
     </row>
-    <row r="37" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R37" s="8"/>
       <c r="S37" s="8"/>
       <c r="T37" s="8"/>
@@ -13840,39 +13816,39 @@
       <c r="W37" s="8"/>
       <c r="X37" s="8"/>
       <c r="Y37" s="8"/>
-      <c r="Z37" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA37" s="28"/>
-      <c r="AB37" s="28"/>
-      <c r="AC37" s="28"/>
-      <c r="AD37" s="28"/>
-      <c r="AE37" s="28"/>
-      <c r="AF37" s="28"/>
-      <c r="AG37" s="28"/>
-      <c r="AH37" s="28"/>
-      <c r="AI37" s="28"/>
-      <c r="AJ37" s="28"/>
-      <c r="AK37" s="28"/>
-      <c r="AL37" s="28"/>
-      <c r="AM37" s="28"/>
-      <c r="AN37" s="28"/>
-      <c r="AO37" s="28"/>
-      <c r="AP37" s="28"/>
-      <c r="AQ37" s="28"/>
-      <c r="AR37" s="28"/>
-      <c r="AS37" s="28"/>
-      <c r="AT37" s="28"/>
-      <c r="AU37" s="28"/>
-      <c r="AV37" s="28"/>
-      <c r="AW37" s="28"/>
-      <c r="AX37" s="28"/>
-      <c r="AY37" s="28"/>
-      <c r="AZ37" s="28"/>
-      <c r="BA37" s="28"/>
-      <c r="BB37" s="28"/>
-      <c r="BC37" s="28"/>
-      <c r="BD37" s="14"/>
+      <c r="Z37" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA37" s="33"/>
+      <c r="AB37" s="33"/>
+      <c r="AC37" s="33"/>
+      <c r="AD37" s="33"/>
+      <c r="AE37" s="33"/>
+      <c r="AF37" s="33"/>
+      <c r="AG37" s="33"/>
+      <c r="AH37" s="33"/>
+      <c r="AI37" s="33"/>
+      <c r="AJ37" s="33"/>
+      <c r="AK37" s="33"/>
+      <c r="AL37" s="33"/>
+      <c r="AM37" s="33"/>
+      <c r="AN37" s="33"/>
+      <c r="AO37" s="33"/>
+      <c r="AP37" s="33"/>
+      <c r="AQ37" s="33"/>
+      <c r="AR37" s="33"/>
+      <c r="AS37" s="33"/>
+      <c r="AT37" s="33"/>
+      <c r="AU37" s="33"/>
+      <c r="AV37" s="33"/>
+      <c r="AW37" s="33"/>
+      <c r="AX37" s="33"/>
+      <c r="AY37" s="33"/>
+      <c r="AZ37" s="33"/>
+      <c r="BA37" s="33"/>
+      <c r="BB37" s="33"/>
+      <c r="BC37" s="33"/>
+      <c r="BD37" s="12"/>
       <c r="BE37" s="8"/>
       <c r="BF37" s="8"/>
       <c r="BG37" s="8"/>
@@ -13882,44 +13858,44 @@
       <c r="BK37" s="8"/>
       <c r="BL37" s="8"/>
       <c r="BM37" s="8"/>
-      <c r="BN37" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="BO37" s="18"/>
-      <c r="BP37" s="18"/>
-      <c r="BQ37" s="18"/>
-      <c r="BR37" s="18"/>
-      <c r="BS37" s="18"/>
-      <c r="BT37" s="18"/>
-      <c r="BU37" s="18"/>
-      <c r="BV37" s="18"/>
-      <c r="BW37" s="18"/>
-      <c r="BX37" s="18"/>
-      <c r="BY37" s="18"/>
-      <c r="BZ37" s="18"/>
-      <c r="CA37" s="18"/>
-      <c r="CB37" s="18"/>
-      <c r="CC37" s="18"/>
-      <c r="CD37" s="18"/>
-      <c r="CE37" s="18"/>
-      <c r="CF37" s="18"/>
-      <c r="CG37" s="18"/>
-      <c r="CH37" s="18"/>
-      <c r="CI37" s="18"/>
-      <c r="CJ37" s="18"/>
-      <c r="CK37" s="18"/>
-      <c r="CL37" s="18"/>
-      <c r="CM37" s="18"/>
-      <c r="CN37" s="18"/>
-      <c r="CO37" s="18"/>
-      <c r="CP37" s="18"/>
-      <c r="CQ37" s="18"/>
-      <c r="CR37" s="17"/>
-      <c r="CS37" s="17"/>
-      <c r="CT37" s="17"/>
-      <c r="CU37" s="17"/>
+      <c r="BN37" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="BO37" s="32"/>
+      <c r="BP37" s="32"/>
+      <c r="BQ37" s="32"/>
+      <c r="BR37" s="32"/>
+      <c r="BS37" s="32"/>
+      <c r="BT37" s="32"/>
+      <c r="BU37" s="32"/>
+      <c r="BV37" s="32"/>
+      <c r="BW37" s="32"/>
+      <c r="BX37" s="32"/>
+      <c r="BY37" s="32"/>
+      <c r="BZ37" s="32"/>
+      <c r="CA37" s="32"/>
+      <c r="CB37" s="32"/>
+      <c r="CC37" s="32"/>
+      <c r="CD37" s="32"/>
+      <c r="CE37" s="32"/>
+      <c r="CF37" s="32"/>
+      <c r="CG37" s="32"/>
+      <c r="CH37" s="32"/>
+      <c r="CI37" s="32"/>
+      <c r="CJ37" s="32"/>
+      <c r="CK37" s="32"/>
+      <c r="CL37" s="32"/>
+      <c r="CM37" s="32"/>
+      <c r="CN37" s="32"/>
+      <c r="CO37" s="32"/>
+      <c r="CP37" s="32"/>
+      <c r="CQ37" s="32"/>
+      <c r="CR37" s="15"/>
+      <c r="CS37" s="15"/>
+      <c r="CT37" s="15"/>
+      <c r="CU37" s="15"/>
     </row>
-    <row r="38" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R38" s="8"/>
       <c r="S38" s="8"/>
       <c r="T38" s="8"/>
@@ -13928,37 +13904,37 @@
       <c r="W38" s="8"/>
       <c r="X38" s="8"/>
       <c r="Y38" s="8"/>
-      <c r="Z38" s="28"/>
-      <c r="AA38" s="28"/>
-      <c r="AB38" s="28"/>
-      <c r="AC38" s="28"/>
-      <c r="AD38" s="28"/>
-      <c r="AE38" s="28"/>
-      <c r="AF38" s="28"/>
-      <c r="AG38" s="28"/>
-      <c r="AH38" s="28"/>
-      <c r="AI38" s="28"/>
-      <c r="AJ38" s="28"/>
-      <c r="AK38" s="28"/>
-      <c r="AL38" s="28"/>
-      <c r="AM38" s="28"/>
-      <c r="AN38" s="28"/>
-      <c r="AO38" s="28"/>
-      <c r="AP38" s="28"/>
-      <c r="AQ38" s="28"/>
-      <c r="AR38" s="28"/>
-      <c r="AS38" s="28"/>
-      <c r="AT38" s="28"/>
-      <c r="AU38" s="28"/>
-      <c r="AV38" s="28"/>
-      <c r="AW38" s="28"/>
-      <c r="AX38" s="28"/>
-      <c r="AY38" s="28"/>
-      <c r="AZ38" s="28"/>
-      <c r="BA38" s="28"/>
-      <c r="BB38" s="28"/>
-      <c r="BC38" s="28"/>
-      <c r="BD38" s="14"/>
+      <c r="Z38" s="33"/>
+      <c r="AA38" s="33"/>
+      <c r="AB38" s="33"/>
+      <c r="AC38" s="33"/>
+      <c r="AD38" s="33"/>
+      <c r="AE38" s="33"/>
+      <c r="AF38" s="33"/>
+      <c r="AG38" s="33"/>
+      <c r="AH38" s="33"/>
+      <c r="AI38" s="33"/>
+      <c r="AJ38" s="33"/>
+      <c r="AK38" s="33"/>
+      <c r="AL38" s="33"/>
+      <c r="AM38" s="33"/>
+      <c r="AN38" s="33"/>
+      <c r="AO38" s="33"/>
+      <c r="AP38" s="33"/>
+      <c r="AQ38" s="33"/>
+      <c r="AR38" s="33"/>
+      <c r="AS38" s="33"/>
+      <c r="AT38" s="33"/>
+      <c r="AU38" s="33"/>
+      <c r="AV38" s="33"/>
+      <c r="AW38" s="33"/>
+      <c r="AX38" s="33"/>
+      <c r="AY38" s="33"/>
+      <c r="AZ38" s="33"/>
+      <c r="BA38" s="33"/>
+      <c r="BB38" s="33"/>
+      <c r="BC38" s="33"/>
+      <c r="BD38" s="12"/>
       <c r="BE38" s="8"/>
       <c r="BF38" s="8"/>
       <c r="BG38" s="8"/>
@@ -13968,42 +13944,42 @@
       <c r="BK38" s="8"/>
       <c r="BL38" s="8"/>
       <c r="BM38" s="8"/>
-      <c r="BN38" s="18"/>
-      <c r="BO38" s="18"/>
-      <c r="BP38" s="18"/>
-      <c r="BQ38" s="18"/>
-      <c r="BR38" s="18"/>
-      <c r="BS38" s="18"/>
-      <c r="BT38" s="18"/>
-      <c r="BU38" s="18"/>
-      <c r="BV38" s="18"/>
-      <c r="BW38" s="18"/>
-      <c r="BX38" s="18"/>
-      <c r="BY38" s="18"/>
-      <c r="BZ38" s="18"/>
-      <c r="CA38" s="18"/>
-      <c r="CB38" s="18"/>
-      <c r="CC38" s="18"/>
-      <c r="CD38" s="18"/>
-      <c r="CE38" s="18"/>
-      <c r="CF38" s="18"/>
-      <c r="CG38" s="18"/>
-      <c r="CH38" s="18"/>
-      <c r="CI38" s="18"/>
-      <c r="CJ38" s="18"/>
-      <c r="CK38" s="18"/>
-      <c r="CL38" s="18"/>
-      <c r="CM38" s="18"/>
-      <c r="CN38" s="18"/>
-      <c r="CO38" s="18"/>
-      <c r="CP38" s="18"/>
-      <c r="CQ38" s="18"/>
-      <c r="CR38" s="17"/>
-      <c r="CS38" s="17"/>
-      <c r="CT38" s="17"/>
-      <c r="CU38" s="17"/>
+      <c r="BN38" s="32"/>
+      <c r="BO38" s="32"/>
+      <c r="BP38" s="32"/>
+      <c r="BQ38" s="32"/>
+      <c r="BR38" s="32"/>
+      <c r="BS38" s="32"/>
+      <c r="BT38" s="32"/>
+      <c r="BU38" s="32"/>
+      <c r="BV38" s="32"/>
+      <c r="BW38" s="32"/>
+      <c r="BX38" s="32"/>
+      <c r="BY38" s="32"/>
+      <c r="BZ38" s="32"/>
+      <c r="CA38" s="32"/>
+      <c r="CB38" s="32"/>
+      <c r="CC38" s="32"/>
+      <c r="CD38" s="32"/>
+      <c r="CE38" s="32"/>
+      <c r="CF38" s="32"/>
+      <c r="CG38" s="32"/>
+      <c r="CH38" s="32"/>
+      <c r="CI38" s="32"/>
+      <c r="CJ38" s="32"/>
+      <c r="CK38" s="32"/>
+      <c r="CL38" s="32"/>
+      <c r="CM38" s="32"/>
+      <c r="CN38" s="32"/>
+      <c r="CO38" s="32"/>
+      <c r="CP38" s="32"/>
+      <c r="CQ38" s="32"/>
+      <c r="CR38" s="15"/>
+      <c r="CS38" s="15"/>
+      <c r="CT38" s="15"/>
+      <c r="CU38" s="15"/>
     </row>
-    <row r="39" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R39" s="8"/>
       <c r="S39" s="8"/>
       <c r="T39" s="8"/>
@@ -14012,37 +13988,37 @@
       <c r="W39" s="8"/>
       <c r="X39" s="8"/>
       <c r="Y39" s="8"/>
-      <c r="Z39" s="28"/>
-      <c r="AA39" s="28"/>
-      <c r="AB39" s="28"/>
-      <c r="AC39" s="28"/>
-      <c r="AD39" s="28"/>
-      <c r="AE39" s="28"/>
-      <c r="AF39" s="28"/>
-      <c r="AG39" s="28"/>
-      <c r="AH39" s="28"/>
-      <c r="AI39" s="28"/>
-      <c r="AJ39" s="28"/>
-      <c r="AK39" s="28"/>
-      <c r="AL39" s="28"/>
-      <c r="AM39" s="28"/>
-      <c r="AN39" s="28"/>
-      <c r="AO39" s="28"/>
-      <c r="AP39" s="28"/>
-      <c r="AQ39" s="28"/>
-      <c r="AR39" s="28"/>
-      <c r="AS39" s="28"/>
-      <c r="AT39" s="28"/>
-      <c r="AU39" s="28"/>
-      <c r="AV39" s="28"/>
-      <c r="AW39" s="28"/>
-      <c r="AX39" s="28"/>
-      <c r="AY39" s="28"/>
-      <c r="AZ39" s="28"/>
-      <c r="BA39" s="28"/>
-      <c r="BB39" s="28"/>
-      <c r="BC39" s="28"/>
-      <c r="BD39" s="14"/>
+      <c r="Z39" s="33"/>
+      <c r="AA39" s="33"/>
+      <c r="AB39" s="33"/>
+      <c r="AC39" s="33"/>
+      <c r="AD39" s="33"/>
+      <c r="AE39" s="33"/>
+      <c r="AF39" s="33"/>
+      <c r="AG39" s="33"/>
+      <c r="AH39" s="33"/>
+      <c r="AI39" s="33"/>
+      <c r="AJ39" s="33"/>
+      <c r="AK39" s="33"/>
+      <c r="AL39" s="33"/>
+      <c r="AM39" s="33"/>
+      <c r="AN39" s="33"/>
+      <c r="AO39" s="33"/>
+      <c r="AP39" s="33"/>
+      <c r="AQ39" s="33"/>
+      <c r="AR39" s="33"/>
+      <c r="AS39" s="33"/>
+      <c r="AT39" s="33"/>
+      <c r="AU39" s="33"/>
+      <c r="AV39" s="33"/>
+      <c r="AW39" s="33"/>
+      <c r="AX39" s="33"/>
+      <c r="AY39" s="33"/>
+      <c r="AZ39" s="33"/>
+      <c r="BA39" s="33"/>
+      <c r="BB39" s="33"/>
+      <c r="BC39" s="33"/>
+      <c r="BD39" s="12"/>
       <c r="BE39" s="8"/>
       <c r="BF39" s="8"/>
       <c r="BG39" s="8"/>
@@ -14087,7 +14063,7 @@
       <c r="CT39" s="8"/>
       <c r="CU39" s="8"/>
     </row>
-    <row r="40" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R40" s="8"/>
       <c r="S40" s="8"/>
       <c r="T40" s="8"/>
@@ -14096,39 +14072,39 @@
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
       <c r="Y40" s="8"/>
-      <c r="Z40" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA40" s="16"/>
-      <c r="AB40" s="16"/>
-      <c r="AC40" s="16"/>
-      <c r="AD40" s="16"/>
-      <c r="AE40" s="16"/>
-      <c r="AF40" s="16"/>
-      <c r="AG40" s="16"/>
-      <c r="AH40" s="16"/>
-      <c r="AI40" s="16"/>
-      <c r="AJ40" s="16"/>
-      <c r="AK40" s="16"/>
-      <c r="AL40" s="16"/>
-      <c r="AM40" s="16"/>
-      <c r="AN40" s="16"/>
-      <c r="AO40" s="16"/>
-      <c r="AP40" s="16"/>
-      <c r="AQ40" s="16"/>
-      <c r="AR40" s="16"/>
-      <c r="AS40" s="16"/>
-      <c r="AT40" s="16"/>
-      <c r="AU40" s="16"/>
-      <c r="AV40" s="16"/>
-      <c r="AW40" s="16"/>
-      <c r="AX40" s="16"/>
-      <c r="AY40" s="16"/>
-      <c r="AZ40" s="16"/>
-      <c r="BA40" s="16"/>
-      <c r="BB40" s="16"/>
-      <c r="BC40" s="16"/>
-      <c r="BD40" s="26"/>
+      <c r="Z40" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA40" s="34"/>
+      <c r="AB40" s="34"/>
+      <c r="AC40" s="34"/>
+      <c r="AD40" s="34"/>
+      <c r="AE40" s="34"/>
+      <c r="AF40" s="34"/>
+      <c r="AG40" s="34"/>
+      <c r="AH40" s="34"/>
+      <c r="AI40" s="34"/>
+      <c r="AJ40" s="34"/>
+      <c r="AK40" s="34"/>
+      <c r="AL40" s="34"/>
+      <c r="AM40" s="34"/>
+      <c r="AN40" s="34"/>
+      <c r="AO40" s="34"/>
+      <c r="AP40" s="34"/>
+      <c r="AQ40" s="34"/>
+      <c r="AR40" s="34"/>
+      <c r="AS40" s="34"/>
+      <c r="AT40" s="34"/>
+      <c r="AU40" s="34"/>
+      <c r="AV40" s="34"/>
+      <c r="AW40" s="34"/>
+      <c r="AX40" s="34"/>
+      <c r="AY40" s="34"/>
+      <c r="AZ40" s="34"/>
+      <c r="BA40" s="34"/>
+      <c r="BB40" s="34"/>
+      <c r="BC40" s="34"/>
+      <c r="BD40" s="14"/>
       <c r="BE40" s="8"/>
       <c r="BF40" s="8"/>
       <c r="BG40" s="8"/>
@@ -14138,44 +14114,44 @@
       <c r="BK40" s="8"/>
       <c r="BL40" s="8"/>
       <c r="BM40" s="8"/>
-      <c r="BN40" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="BO40" s="22"/>
-      <c r="BP40" s="22"/>
-      <c r="BQ40" s="22"/>
-      <c r="BR40" s="22"/>
-      <c r="BS40" s="22"/>
-      <c r="BT40" s="22"/>
-      <c r="BU40" s="22"/>
-      <c r="BV40" s="22"/>
-      <c r="BW40" s="22"/>
-      <c r="BX40" s="22"/>
-      <c r="BY40" s="22"/>
-      <c r="BZ40" s="22"/>
-      <c r="CA40" s="22"/>
-      <c r="CB40" s="22"/>
-      <c r="CC40" s="22"/>
-      <c r="CD40" s="22"/>
-      <c r="CE40" s="22"/>
-      <c r="CF40" s="22"/>
-      <c r="CG40" s="22"/>
-      <c r="CH40" s="22"/>
-      <c r="CI40" s="22"/>
-      <c r="CJ40" s="22"/>
-      <c r="CK40" s="22"/>
-      <c r="CL40" s="22"/>
-      <c r="CM40" s="22"/>
-      <c r="CN40" s="22"/>
-      <c r="CO40" s="22"/>
-      <c r="CP40" s="22"/>
-      <c r="CQ40" s="22"/>
-      <c r="CR40" s="21"/>
-      <c r="CS40" s="21"/>
-      <c r="CT40" s="21"/>
-      <c r="CU40" s="21"/>
+      <c r="BN40" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO40" s="31"/>
+      <c r="BP40" s="31"/>
+      <c r="BQ40" s="31"/>
+      <c r="BR40" s="31"/>
+      <c r="BS40" s="31"/>
+      <c r="BT40" s="31"/>
+      <c r="BU40" s="31"/>
+      <c r="BV40" s="31"/>
+      <c r="BW40" s="31"/>
+      <c r="BX40" s="31"/>
+      <c r="BY40" s="31"/>
+      <c r="BZ40" s="31"/>
+      <c r="CA40" s="31"/>
+      <c r="CB40" s="31"/>
+      <c r="CC40" s="31"/>
+      <c r="CD40" s="31"/>
+      <c r="CE40" s="31"/>
+      <c r="CF40" s="31"/>
+      <c r="CG40" s="31"/>
+      <c r="CH40" s="31"/>
+      <c r="CI40" s="31"/>
+      <c r="CJ40" s="31"/>
+      <c r="CK40" s="31"/>
+      <c r="CL40" s="31"/>
+      <c r="CM40" s="31"/>
+      <c r="CN40" s="31"/>
+      <c r="CO40" s="31"/>
+      <c r="CP40" s="31"/>
+      <c r="CQ40" s="31"/>
+      <c r="CR40" s="17"/>
+      <c r="CS40" s="17"/>
+      <c r="CT40" s="17"/>
+      <c r="CU40" s="17"/>
     </row>
-    <row r="41" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R41" s="8"/>
       <c r="S41" s="8"/>
       <c r="T41" s="8"/>
@@ -14184,37 +14160,37 @@
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
       <c r="Y41" s="8"/>
-      <c r="Z41" s="16"/>
-      <c r="AA41" s="16"/>
-      <c r="AB41" s="16"/>
-      <c r="AC41" s="16"/>
-      <c r="AD41" s="16"/>
-      <c r="AE41" s="16"/>
-      <c r="AF41" s="16"/>
-      <c r="AG41" s="16"/>
-      <c r="AH41" s="16"/>
-      <c r="AI41" s="16"/>
-      <c r="AJ41" s="16"/>
-      <c r="AK41" s="16"/>
-      <c r="AL41" s="16"/>
-      <c r="AM41" s="16"/>
-      <c r="AN41" s="16"/>
-      <c r="AO41" s="16"/>
-      <c r="AP41" s="16"/>
-      <c r="AQ41" s="16"/>
-      <c r="AR41" s="16"/>
-      <c r="AS41" s="16"/>
-      <c r="AT41" s="16"/>
-      <c r="AU41" s="16"/>
-      <c r="AV41" s="16"/>
-      <c r="AW41" s="16"/>
-      <c r="AX41" s="16"/>
-      <c r="AY41" s="16"/>
-      <c r="AZ41" s="16"/>
-      <c r="BA41" s="16"/>
-      <c r="BB41" s="16"/>
-      <c r="BC41" s="16"/>
-      <c r="BD41" s="26"/>
+      <c r="Z41" s="34"/>
+      <c r="AA41" s="34"/>
+      <c r="AB41" s="34"/>
+      <c r="AC41" s="34"/>
+      <c r="AD41" s="34"/>
+      <c r="AE41" s="34"/>
+      <c r="AF41" s="34"/>
+      <c r="AG41" s="34"/>
+      <c r="AH41" s="34"/>
+      <c r="AI41" s="34"/>
+      <c r="AJ41" s="34"/>
+      <c r="AK41" s="34"/>
+      <c r="AL41" s="34"/>
+      <c r="AM41" s="34"/>
+      <c r="AN41" s="34"/>
+      <c r="AO41" s="34"/>
+      <c r="AP41" s="34"/>
+      <c r="AQ41" s="34"/>
+      <c r="AR41" s="34"/>
+      <c r="AS41" s="34"/>
+      <c r="AT41" s="34"/>
+      <c r="AU41" s="34"/>
+      <c r="AV41" s="34"/>
+      <c r="AW41" s="34"/>
+      <c r="AX41" s="34"/>
+      <c r="AY41" s="34"/>
+      <c r="AZ41" s="34"/>
+      <c r="BA41" s="34"/>
+      <c r="BB41" s="34"/>
+      <c r="BC41" s="34"/>
+      <c r="BD41" s="14"/>
       <c r="BE41" s="8"/>
       <c r="BF41" s="8"/>
       <c r="BG41" s="8"/>
@@ -14224,42 +14200,42 @@
       <c r="BK41" s="8"/>
       <c r="BL41" s="8"/>
       <c r="BM41" s="8"/>
-      <c r="BN41" s="22"/>
-      <c r="BO41" s="22"/>
-      <c r="BP41" s="22"/>
-      <c r="BQ41" s="22"/>
-      <c r="BR41" s="22"/>
-      <c r="BS41" s="22"/>
-      <c r="BT41" s="22"/>
-      <c r="BU41" s="22"/>
-      <c r="BV41" s="22"/>
-      <c r="BW41" s="22"/>
-      <c r="BX41" s="22"/>
-      <c r="BY41" s="22"/>
-      <c r="BZ41" s="22"/>
-      <c r="CA41" s="22"/>
-      <c r="CB41" s="22"/>
-      <c r="CC41" s="22"/>
-      <c r="CD41" s="22"/>
-      <c r="CE41" s="22"/>
-      <c r="CF41" s="22"/>
-      <c r="CG41" s="22"/>
-      <c r="CH41" s="22"/>
-      <c r="CI41" s="22"/>
-      <c r="CJ41" s="22"/>
-      <c r="CK41" s="22"/>
-      <c r="CL41" s="22"/>
-      <c r="CM41" s="22"/>
-      <c r="CN41" s="22"/>
-      <c r="CO41" s="22"/>
-      <c r="CP41" s="22"/>
-      <c r="CQ41" s="22"/>
-      <c r="CR41" s="21"/>
-      <c r="CS41" s="21"/>
-      <c r="CT41" s="21"/>
-      <c r="CU41" s="21"/>
+      <c r="BN41" s="31"/>
+      <c r="BO41" s="31"/>
+      <c r="BP41" s="31"/>
+      <c r="BQ41" s="31"/>
+      <c r="BR41" s="31"/>
+      <c r="BS41" s="31"/>
+      <c r="BT41" s="31"/>
+      <c r="BU41" s="31"/>
+      <c r="BV41" s="31"/>
+      <c r="BW41" s="31"/>
+      <c r="BX41" s="31"/>
+      <c r="BY41" s="31"/>
+      <c r="BZ41" s="31"/>
+      <c r="CA41" s="31"/>
+      <c r="CB41" s="31"/>
+      <c r="CC41" s="31"/>
+      <c r="CD41" s="31"/>
+      <c r="CE41" s="31"/>
+      <c r="CF41" s="31"/>
+      <c r="CG41" s="31"/>
+      <c r="CH41" s="31"/>
+      <c r="CI41" s="31"/>
+      <c r="CJ41" s="31"/>
+      <c r="CK41" s="31"/>
+      <c r="CL41" s="31"/>
+      <c r="CM41" s="31"/>
+      <c r="CN41" s="31"/>
+      <c r="CO41" s="31"/>
+      <c r="CP41" s="31"/>
+      <c r="CQ41" s="31"/>
+      <c r="CR41" s="17"/>
+      <c r="CS41" s="17"/>
+      <c r="CT41" s="17"/>
+      <c r="CU41" s="17"/>
     </row>
-    <row r="42" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R42" s="8"/>
       <c r="S42" s="8"/>
       <c r="T42" s="8"/>
@@ -14308,83 +14284,83 @@
       <c r="BK42" s="8"/>
       <c r="BL42" s="8"/>
       <c r="BM42" s="8"/>
-      <c r="BN42" s="22"/>
-      <c r="BO42" s="22"/>
-      <c r="BP42" s="22"/>
-      <c r="BQ42" s="22"/>
-      <c r="BR42" s="22"/>
-      <c r="BS42" s="22"/>
-      <c r="BT42" s="22"/>
-      <c r="BU42" s="22"/>
-      <c r="BV42" s="22"/>
-      <c r="BW42" s="22"/>
-      <c r="BX42" s="22"/>
-      <c r="BY42" s="22"/>
-      <c r="BZ42" s="22"/>
-      <c r="CA42" s="22"/>
-      <c r="CB42" s="22"/>
-      <c r="CC42" s="22"/>
-      <c r="CD42" s="22"/>
-      <c r="CE42" s="22"/>
-      <c r="CF42" s="22"/>
-      <c r="CG42" s="22"/>
-      <c r="CH42" s="22"/>
-      <c r="CI42" s="22"/>
-      <c r="CJ42" s="22"/>
-      <c r="CK42" s="22"/>
-      <c r="CL42" s="22"/>
-      <c r="CM42" s="22"/>
-      <c r="CN42" s="22"/>
-      <c r="CO42" s="22"/>
-      <c r="CP42" s="22"/>
-      <c r="CQ42" s="22"/>
-      <c r="CR42" s="21"/>
-      <c r="CS42" s="21"/>
-      <c r="CT42" s="21"/>
-      <c r="CU42" s="21"/>
+      <c r="BN42" s="31"/>
+      <c r="BO42" s="31"/>
+      <c r="BP42" s="31"/>
+      <c r="BQ42" s="31"/>
+      <c r="BR42" s="31"/>
+      <c r="BS42" s="31"/>
+      <c r="BT42" s="31"/>
+      <c r="BU42" s="31"/>
+      <c r="BV42" s="31"/>
+      <c r="BW42" s="31"/>
+      <c r="BX42" s="31"/>
+      <c r="BY42" s="31"/>
+      <c r="BZ42" s="31"/>
+      <c r="CA42" s="31"/>
+      <c r="CB42" s="31"/>
+      <c r="CC42" s="31"/>
+      <c r="CD42" s="31"/>
+      <c r="CE42" s="31"/>
+      <c r="CF42" s="31"/>
+      <c r="CG42" s="31"/>
+      <c r="CH42" s="31"/>
+      <c r="CI42" s="31"/>
+      <c r="CJ42" s="31"/>
+      <c r="CK42" s="31"/>
+      <c r="CL42" s="31"/>
+      <c r="CM42" s="31"/>
+      <c r="CN42" s="31"/>
+      <c r="CO42" s="31"/>
+      <c r="CP42" s="31"/>
+      <c r="CQ42" s="31"/>
+      <c r="CR42" s="17"/>
+      <c r="CS42" s="17"/>
+      <c r="CT42" s="17"/>
+      <c r="CU42" s="17"/>
     </row>
-    <row r="43" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R43" s="24"/>
-      <c r="S43" s="24"/>
-      <c r="T43" s="24"/>
-      <c r="U43" s="24"/>
-      <c r="V43" s="24"/>
-      <c r="W43" s="24"/>
-      <c r="X43" s="24"/>
-      <c r="Y43" s="24"/>
-      <c r="Z43" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA43" s="23"/>
-      <c r="AB43" s="23"/>
-      <c r="AC43" s="23"/>
-      <c r="AD43" s="23"/>
-      <c r="AE43" s="23"/>
-      <c r="AF43" s="23"/>
-      <c r="AG43" s="23"/>
-      <c r="AH43" s="23"/>
-      <c r="AI43" s="23"/>
-      <c r="AJ43" s="23"/>
-      <c r="AK43" s="23"/>
-      <c r="AL43" s="23"/>
-      <c r="AM43" s="23"/>
-      <c r="AN43" s="23"/>
-      <c r="AO43" s="23"/>
-      <c r="AP43" s="23"/>
-      <c r="AQ43" s="23"/>
-      <c r="AR43" s="23"/>
-      <c r="AS43" s="23"/>
-      <c r="AT43" s="23"/>
-      <c r="AU43" s="23"/>
-      <c r="AV43" s="23"/>
-      <c r="AW43" s="23"/>
-      <c r="AX43" s="23"/>
-      <c r="AY43" s="23"/>
-      <c r="AZ43" s="23"/>
-      <c r="BA43" s="23"/>
-      <c r="BB43" s="23"/>
-      <c r="BC43" s="23"/>
-      <c r="BD43" s="19"/>
+    <row r="43" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R43" s="18"/>
+      <c r="S43" s="18"/>
+      <c r="T43" s="18"/>
+      <c r="U43" s="18"/>
+      <c r="V43" s="18"/>
+      <c r="W43" s="18"/>
+      <c r="X43" s="18"/>
+      <c r="Y43" s="18"/>
+      <c r="Z43" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA43" s="38"/>
+      <c r="AB43" s="38"/>
+      <c r="AC43" s="38"/>
+      <c r="AD43" s="38"/>
+      <c r="AE43" s="38"/>
+      <c r="AF43" s="38"/>
+      <c r="AG43" s="38"/>
+      <c r="AH43" s="38"/>
+      <c r="AI43" s="38"/>
+      <c r="AJ43" s="38"/>
+      <c r="AK43" s="38"/>
+      <c r="AL43" s="38"/>
+      <c r="AM43" s="38"/>
+      <c r="AN43" s="38"/>
+      <c r="AO43" s="38"/>
+      <c r="AP43" s="38"/>
+      <c r="AQ43" s="38"/>
+      <c r="AR43" s="38"/>
+      <c r="AS43" s="38"/>
+      <c r="AT43" s="38"/>
+      <c r="AU43" s="38"/>
+      <c r="AV43" s="38"/>
+      <c r="AW43" s="38"/>
+      <c r="AX43" s="38"/>
+      <c r="AY43" s="38"/>
+      <c r="AZ43" s="38"/>
+      <c r="BA43" s="38"/>
+      <c r="BB43" s="38"/>
+      <c r="BC43" s="38"/>
+      <c r="BD43" s="16"/>
       <c r="BE43" s="8"/>
       <c r="BF43" s="8"/>
       <c r="BG43" s="8"/>
@@ -14394,44 +14370,44 @@
       <c r="BK43" s="8"/>
       <c r="BL43" s="8"/>
       <c r="BM43" s="8"/>
-      <c r="BN43" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="BO43" s="18"/>
-      <c r="BP43" s="18"/>
-      <c r="BQ43" s="18"/>
-      <c r="BR43" s="18"/>
-      <c r="BS43" s="18"/>
-      <c r="BT43" s="18"/>
-      <c r="BU43" s="18"/>
-      <c r="BV43" s="18"/>
-      <c r="BW43" s="18"/>
-      <c r="BX43" s="18"/>
-      <c r="BY43" s="18"/>
-      <c r="BZ43" s="18"/>
-      <c r="CA43" s="18"/>
-      <c r="CB43" s="18"/>
-      <c r="CC43" s="18"/>
-      <c r="CD43" s="18"/>
-      <c r="CE43" s="18"/>
-      <c r="CF43" s="18"/>
-      <c r="CG43" s="18"/>
-      <c r="CH43" s="18"/>
-      <c r="CI43" s="18"/>
-      <c r="CJ43" s="18"/>
-      <c r="CK43" s="18"/>
-      <c r="CL43" s="18"/>
-      <c r="CM43" s="18"/>
-      <c r="CN43" s="18"/>
-      <c r="CO43" s="18"/>
-      <c r="CP43" s="18"/>
-      <c r="CQ43" s="18"/>
-      <c r="CR43" s="17"/>
-      <c r="CS43" s="17"/>
-      <c r="CT43" s="17"/>
-      <c r="CU43" s="17"/>
+      <c r="BN43" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="BO43" s="32"/>
+      <c r="BP43" s="32"/>
+      <c r="BQ43" s="32"/>
+      <c r="BR43" s="32"/>
+      <c r="BS43" s="32"/>
+      <c r="BT43" s="32"/>
+      <c r="BU43" s="32"/>
+      <c r="BV43" s="32"/>
+      <c r="BW43" s="32"/>
+      <c r="BX43" s="32"/>
+      <c r="BY43" s="32"/>
+      <c r="BZ43" s="32"/>
+      <c r="CA43" s="32"/>
+      <c r="CB43" s="32"/>
+      <c r="CC43" s="32"/>
+      <c r="CD43" s="32"/>
+      <c r="CE43" s="32"/>
+      <c r="CF43" s="32"/>
+      <c r="CG43" s="32"/>
+      <c r="CH43" s="32"/>
+      <c r="CI43" s="32"/>
+      <c r="CJ43" s="32"/>
+      <c r="CK43" s="32"/>
+      <c r="CL43" s="32"/>
+      <c r="CM43" s="32"/>
+      <c r="CN43" s="32"/>
+      <c r="CO43" s="32"/>
+      <c r="CP43" s="32"/>
+      <c r="CQ43" s="32"/>
+      <c r="CR43" s="15"/>
+      <c r="CS43" s="15"/>
+      <c r="CT43" s="15"/>
+      <c r="CU43" s="15"/>
     </row>
-    <row r="44" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R44" s="8"/>
       <c r="S44" s="8"/>
       <c r="T44" s="8"/>
@@ -14440,37 +14416,37 @@
       <c r="W44" s="8"/>
       <c r="X44" s="8"/>
       <c r="Y44" s="8"/>
-      <c r="Z44" s="20"/>
-      <c r="AA44" s="20"/>
-      <c r="AB44" s="20"/>
-      <c r="AC44" s="20"/>
-      <c r="AD44" s="20"/>
-      <c r="AE44" s="20"/>
-      <c r="AF44" s="20"/>
-      <c r="AG44" s="20"/>
-      <c r="AH44" s="20"/>
-      <c r="AI44" s="20"/>
-      <c r="AJ44" s="20"/>
-      <c r="AK44" s="20"/>
-      <c r="AL44" s="20"/>
-      <c r="AM44" s="20"/>
-      <c r="AN44" s="20"/>
-      <c r="AO44" s="20"/>
-      <c r="AP44" s="20"/>
-      <c r="AQ44" s="20"/>
-      <c r="AR44" s="20"/>
-      <c r="AS44" s="20"/>
-      <c r="AT44" s="20"/>
-      <c r="AU44" s="20"/>
-      <c r="AV44" s="20"/>
-      <c r="AW44" s="20"/>
-      <c r="AX44" s="20"/>
-      <c r="AY44" s="20"/>
-      <c r="AZ44" s="20"/>
-      <c r="BA44" s="20"/>
-      <c r="BB44" s="20"/>
-      <c r="BC44" s="20"/>
-      <c r="BD44" s="19"/>
+      <c r="Z44" s="39"/>
+      <c r="AA44" s="39"/>
+      <c r="AB44" s="39"/>
+      <c r="AC44" s="39"/>
+      <c r="AD44" s="39"/>
+      <c r="AE44" s="39"/>
+      <c r="AF44" s="39"/>
+      <c r="AG44" s="39"/>
+      <c r="AH44" s="39"/>
+      <c r="AI44" s="39"/>
+      <c r="AJ44" s="39"/>
+      <c r="AK44" s="39"/>
+      <c r="AL44" s="39"/>
+      <c r="AM44" s="39"/>
+      <c r="AN44" s="39"/>
+      <c r="AO44" s="39"/>
+      <c r="AP44" s="39"/>
+      <c r="AQ44" s="39"/>
+      <c r="AR44" s="39"/>
+      <c r="AS44" s="39"/>
+      <c r="AT44" s="39"/>
+      <c r="AU44" s="39"/>
+      <c r="AV44" s="39"/>
+      <c r="AW44" s="39"/>
+      <c r="AX44" s="39"/>
+      <c r="AY44" s="39"/>
+      <c r="AZ44" s="39"/>
+      <c r="BA44" s="39"/>
+      <c r="BB44" s="39"/>
+      <c r="BC44" s="39"/>
+      <c r="BD44" s="16"/>
       <c r="BE44" s="8"/>
       <c r="BF44" s="8"/>
       <c r="BG44" s="8"/>
@@ -14480,42 +14456,42 @@
       <c r="BK44" s="8"/>
       <c r="BL44" s="8"/>
       <c r="BM44" s="8"/>
-      <c r="BN44" s="18"/>
-      <c r="BO44" s="18"/>
-      <c r="BP44" s="18"/>
-      <c r="BQ44" s="18"/>
-      <c r="BR44" s="18"/>
-      <c r="BS44" s="18"/>
-      <c r="BT44" s="18"/>
-      <c r="BU44" s="18"/>
-      <c r="BV44" s="18"/>
-      <c r="BW44" s="18"/>
-      <c r="BX44" s="18"/>
-      <c r="BY44" s="18"/>
-      <c r="BZ44" s="18"/>
-      <c r="CA44" s="18"/>
-      <c r="CB44" s="18"/>
-      <c r="CC44" s="18"/>
-      <c r="CD44" s="18"/>
-      <c r="CE44" s="18"/>
-      <c r="CF44" s="18"/>
-      <c r="CG44" s="18"/>
-      <c r="CH44" s="18"/>
-      <c r="CI44" s="18"/>
-      <c r="CJ44" s="18"/>
-      <c r="CK44" s="18"/>
-      <c r="CL44" s="18"/>
-      <c r="CM44" s="18"/>
-      <c r="CN44" s="18"/>
-      <c r="CO44" s="18"/>
-      <c r="CP44" s="18"/>
-      <c r="CQ44" s="18"/>
-      <c r="CR44" s="17"/>
-      <c r="CS44" s="17"/>
-      <c r="CT44" s="17"/>
-      <c r="CU44" s="17"/>
+      <c r="BN44" s="32"/>
+      <c r="BO44" s="32"/>
+      <c r="BP44" s="32"/>
+      <c r="BQ44" s="32"/>
+      <c r="BR44" s="32"/>
+      <c r="BS44" s="32"/>
+      <c r="BT44" s="32"/>
+      <c r="BU44" s="32"/>
+      <c r="BV44" s="32"/>
+      <c r="BW44" s="32"/>
+      <c r="BX44" s="32"/>
+      <c r="BY44" s="32"/>
+      <c r="BZ44" s="32"/>
+      <c r="CA44" s="32"/>
+      <c r="CB44" s="32"/>
+      <c r="CC44" s="32"/>
+      <c r="CD44" s="32"/>
+      <c r="CE44" s="32"/>
+      <c r="CF44" s="32"/>
+      <c r="CG44" s="32"/>
+      <c r="CH44" s="32"/>
+      <c r="CI44" s="32"/>
+      <c r="CJ44" s="32"/>
+      <c r="CK44" s="32"/>
+      <c r="CL44" s="32"/>
+      <c r="CM44" s="32"/>
+      <c r="CN44" s="32"/>
+      <c r="CO44" s="32"/>
+      <c r="CP44" s="32"/>
+      <c r="CQ44" s="32"/>
+      <c r="CR44" s="15"/>
+      <c r="CS44" s="15"/>
+      <c r="CT44" s="15"/>
+      <c r="CU44" s="15"/>
     </row>
-    <row r="45" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R45" s="8"/>
       <c r="S45" s="8"/>
       <c r="T45" s="8"/>
@@ -14524,37 +14500,37 @@
       <c r="W45" s="8"/>
       <c r="X45" s="8"/>
       <c r="Y45" s="8"/>
-      <c r="Z45" s="20"/>
-      <c r="AA45" s="20"/>
-      <c r="AB45" s="20"/>
-      <c r="AC45" s="20"/>
-      <c r="AD45" s="20"/>
-      <c r="AE45" s="20"/>
-      <c r="AF45" s="20"/>
-      <c r="AG45" s="20"/>
-      <c r="AH45" s="20"/>
-      <c r="AI45" s="20"/>
-      <c r="AJ45" s="20"/>
-      <c r="AK45" s="20"/>
-      <c r="AL45" s="20"/>
-      <c r="AM45" s="20"/>
-      <c r="AN45" s="20"/>
-      <c r="AO45" s="20"/>
-      <c r="AP45" s="20"/>
-      <c r="AQ45" s="20"/>
-      <c r="AR45" s="20"/>
-      <c r="AS45" s="20"/>
-      <c r="AT45" s="20"/>
-      <c r="AU45" s="20"/>
-      <c r="AV45" s="20"/>
-      <c r="AW45" s="20"/>
-      <c r="AX45" s="20"/>
-      <c r="AY45" s="20"/>
-      <c r="AZ45" s="20"/>
-      <c r="BA45" s="20"/>
-      <c r="BB45" s="20"/>
-      <c r="BC45" s="20"/>
-      <c r="BD45" s="19"/>
+      <c r="Z45" s="39"/>
+      <c r="AA45" s="39"/>
+      <c r="AB45" s="39"/>
+      <c r="AC45" s="39"/>
+      <c r="AD45" s="39"/>
+      <c r="AE45" s="39"/>
+      <c r="AF45" s="39"/>
+      <c r="AG45" s="39"/>
+      <c r="AH45" s="39"/>
+      <c r="AI45" s="39"/>
+      <c r="AJ45" s="39"/>
+      <c r="AK45" s="39"/>
+      <c r="AL45" s="39"/>
+      <c r="AM45" s="39"/>
+      <c r="AN45" s="39"/>
+      <c r="AO45" s="39"/>
+      <c r="AP45" s="39"/>
+      <c r="AQ45" s="39"/>
+      <c r="AR45" s="39"/>
+      <c r="AS45" s="39"/>
+      <c r="AT45" s="39"/>
+      <c r="AU45" s="39"/>
+      <c r="AV45" s="39"/>
+      <c r="AW45" s="39"/>
+      <c r="AX45" s="39"/>
+      <c r="AY45" s="39"/>
+      <c r="AZ45" s="39"/>
+      <c r="BA45" s="39"/>
+      <c r="BB45" s="39"/>
+      <c r="BC45" s="39"/>
+      <c r="BD45" s="16"/>
       <c r="BE45" s="8"/>
       <c r="BF45" s="8"/>
       <c r="BG45" s="8"/>
@@ -14599,7 +14575,7 @@
       <c r="CT45" s="8"/>
       <c r="CU45" s="8"/>
     </row>
-    <row r="46" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R46" s="8"/>
       <c r="S46" s="8"/>
       <c r="T46" s="8"/>
@@ -14608,37 +14584,37 @@
       <c r="W46" s="8"/>
       <c r="X46" s="8"/>
       <c r="Y46" s="8"/>
-      <c r="Z46" s="20"/>
-      <c r="AA46" s="20"/>
-      <c r="AB46" s="20"/>
-      <c r="AC46" s="20"/>
-      <c r="AD46" s="20"/>
-      <c r="AE46" s="20"/>
-      <c r="AF46" s="20"/>
-      <c r="AG46" s="20"/>
-      <c r="AH46" s="20"/>
-      <c r="AI46" s="20"/>
-      <c r="AJ46" s="20"/>
-      <c r="AK46" s="20"/>
-      <c r="AL46" s="20"/>
-      <c r="AM46" s="20"/>
-      <c r="AN46" s="20"/>
-      <c r="AO46" s="20"/>
-      <c r="AP46" s="20"/>
-      <c r="AQ46" s="20"/>
-      <c r="AR46" s="20"/>
-      <c r="AS46" s="20"/>
-      <c r="AT46" s="20"/>
-      <c r="AU46" s="20"/>
-      <c r="AV46" s="20"/>
-      <c r="AW46" s="20"/>
-      <c r="AX46" s="20"/>
-      <c r="AY46" s="20"/>
-      <c r="AZ46" s="20"/>
-      <c r="BA46" s="20"/>
-      <c r="BB46" s="20"/>
-      <c r="BC46" s="20"/>
-      <c r="BD46" s="19"/>
+      <c r="Z46" s="39"/>
+      <c r="AA46" s="39"/>
+      <c r="AB46" s="39"/>
+      <c r="AC46" s="39"/>
+      <c r="AD46" s="39"/>
+      <c r="AE46" s="39"/>
+      <c r="AF46" s="39"/>
+      <c r="AG46" s="39"/>
+      <c r="AH46" s="39"/>
+      <c r="AI46" s="39"/>
+      <c r="AJ46" s="39"/>
+      <c r="AK46" s="39"/>
+      <c r="AL46" s="39"/>
+      <c r="AM46" s="39"/>
+      <c r="AN46" s="39"/>
+      <c r="AO46" s="39"/>
+      <c r="AP46" s="39"/>
+      <c r="AQ46" s="39"/>
+      <c r="AR46" s="39"/>
+      <c r="AS46" s="39"/>
+      <c r="AT46" s="39"/>
+      <c r="AU46" s="39"/>
+      <c r="AV46" s="39"/>
+      <c r="AW46" s="39"/>
+      <c r="AX46" s="39"/>
+      <c r="AY46" s="39"/>
+      <c r="AZ46" s="39"/>
+      <c r="BA46" s="39"/>
+      <c r="BB46" s="39"/>
+      <c r="BC46" s="39"/>
+      <c r="BD46" s="16"/>
       <c r="BE46" s="8"/>
       <c r="BF46" s="8"/>
       <c r="BG46" s="8"/>
@@ -14683,7 +14659,7 @@
       <c r="CT46" s="8"/>
       <c r="CU46" s="8"/>
     </row>
-    <row r="47" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R47" s="8"/>
       <c r="S47" s="8"/>
       <c r="T47" s="8"/>
@@ -14692,37 +14668,37 @@
       <c r="W47" s="8"/>
       <c r="X47" s="8"/>
       <c r="Y47" s="8"/>
-      <c r="Z47" s="20"/>
-      <c r="AA47" s="20"/>
-      <c r="AB47" s="20"/>
-      <c r="AC47" s="20"/>
-      <c r="AD47" s="20"/>
-      <c r="AE47" s="20"/>
-      <c r="AF47" s="20"/>
-      <c r="AG47" s="20"/>
-      <c r="AH47" s="20"/>
-      <c r="AI47" s="20"/>
-      <c r="AJ47" s="20"/>
-      <c r="AK47" s="20"/>
-      <c r="AL47" s="20"/>
-      <c r="AM47" s="20"/>
-      <c r="AN47" s="20"/>
-      <c r="AO47" s="20"/>
-      <c r="AP47" s="20"/>
-      <c r="AQ47" s="20"/>
-      <c r="AR47" s="20"/>
-      <c r="AS47" s="20"/>
-      <c r="AT47" s="20"/>
-      <c r="AU47" s="20"/>
-      <c r="AV47" s="20"/>
-      <c r="AW47" s="20"/>
-      <c r="AX47" s="20"/>
-      <c r="AY47" s="20"/>
-      <c r="AZ47" s="20"/>
-      <c r="BA47" s="20"/>
-      <c r="BB47" s="20"/>
-      <c r="BC47" s="20"/>
-      <c r="BD47" s="19"/>
+      <c r="Z47" s="39"/>
+      <c r="AA47" s="39"/>
+      <c r="AB47" s="39"/>
+      <c r="AC47" s="39"/>
+      <c r="AD47" s="39"/>
+      <c r="AE47" s="39"/>
+      <c r="AF47" s="39"/>
+      <c r="AG47" s="39"/>
+      <c r="AH47" s="39"/>
+      <c r="AI47" s="39"/>
+      <c r="AJ47" s="39"/>
+      <c r="AK47" s="39"/>
+      <c r="AL47" s="39"/>
+      <c r="AM47" s="39"/>
+      <c r="AN47" s="39"/>
+      <c r="AO47" s="39"/>
+      <c r="AP47" s="39"/>
+      <c r="AQ47" s="39"/>
+      <c r="AR47" s="39"/>
+      <c r="AS47" s="39"/>
+      <c r="AT47" s="39"/>
+      <c r="AU47" s="39"/>
+      <c r="AV47" s="39"/>
+      <c r="AW47" s="39"/>
+      <c r="AX47" s="39"/>
+      <c r="AY47" s="39"/>
+      <c r="AZ47" s="39"/>
+      <c r="BA47" s="39"/>
+      <c r="BB47" s="39"/>
+      <c r="BC47" s="39"/>
+      <c r="BD47" s="16"/>
       <c r="BE47" s="8"/>
       <c r="BF47" s="8"/>
       <c r="BG47" s="8"/>
@@ -14767,7 +14743,7 @@
       <c r="CT47" s="8"/>
       <c r="CU47" s="8"/>
     </row>
-    <row r="48" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R48" s="8"/>
       <c r="S48" s="8"/>
       <c r="T48" s="8"/>
@@ -14776,39 +14752,39 @@
       <c r="W48" s="8"/>
       <c r="X48" s="8"/>
       <c r="Y48" s="8"/>
-      <c r="Z48" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA48" s="28"/>
-      <c r="AB48" s="28"/>
-      <c r="AC48" s="28"/>
-      <c r="AD48" s="28"/>
-      <c r="AE48" s="28"/>
-      <c r="AF48" s="28"/>
-      <c r="AG48" s="28"/>
-      <c r="AH48" s="28"/>
-      <c r="AI48" s="28"/>
-      <c r="AJ48" s="28"/>
-      <c r="AK48" s="28"/>
-      <c r="AL48" s="28"/>
-      <c r="AM48" s="28"/>
-      <c r="AN48" s="28"/>
-      <c r="AO48" s="28"/>
-      <c r="AP48" s="28"/>
-      <c r="AQ48" s="28"/>
-      <c r="AR48" s="28"/>
-      <c r="AS48" s="28"/>
-      <c r="AT48" s="28"/>
-      <c r="AU48" s="28"/>
-      <c r="AV48" s="28"/>
-      <c r="AW48" s="28"/>
-      <c r="AX48" s="28"/>
-      <c r="AY48" s="28"/>
-      <c r="AZ48" s="28"/>
-      <c r="BA48" s="28"/>
-      <c r="BB48" s="28"/>
-      <c r="BC48" s="28"/>
-      <c r="BD48" s="14"/>
+      <c r="Z48" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA48" s="33"/>
+      <c r="AB48" s="33"/>
+      <c r="AC48" s="33"/>
+      <c r="AD48" s="33"/>
+      <c r="AE48" s="33"/>
+      <c r="AF48" s="33"/>
+      <c r="AG48" s="33"/>
+      <c r="AH48" s="33"/>
+      <c r="AI48" s="33"/>
+      <c r="AJ48" s="33"/>
+      <c r="AK48" s="33"/>
+      <c r="AL48" s="33"/>
+      <c r="AM48" s="33"/>
+      <c r="AN48" s="33"/>
+      <c r="AO48" s="33"/>
+      <c r="AP48" s="33"/>
+      <c r="AQ48" s="33"/>
+      <c r="AR48" s="33"/>
+      <c r="AS48" s="33"/>
+      <c r="AT48" s="33"/>
+      <c r="AU48" s="33"/>
+      <c r="AV48" s="33"/>
+      <c r="AW48" s="33"/>
+      <c r="AX48" s="33"/>
+      <c r="AY48" s="33"/>
+      <c r="AZ48" s="33"/>
+      <c r="BA48" s="33"/>
+      <c r="BB48" s="33"/>
+      <c r="BC48" s="33"/>
+      <c r="BD48" s="12"/>
       <c r="BE48" s="8"/>
       <c r="BF48" s="8"/>
       <c r="BG48" s="8"/>
@@ -14853,7 +14829,7 @@
       <c r="CT48" s="8"/>
       <c r="CU48" s="8"/>
     </row>
-    <row r="49" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
@@ -14878,37 +14854,37 @@
       <c r="W49" s="8"/>
       <c r="X49" s="8"/>
       <c r="Y49" s="8"/>
-      <c r="Z49" s="28"/>
-      <c r="AA49" s="28"/>
-      <c r="AB49" s="28"/>
-      <c r="AC49" s="28"/>
-      <c r="AD49" s="28"/>
-      <c r="AE49" s="28"/>
-      <c r="AF49" s="28"/>
-      <c r="AG49" s="28"/>
-      <c r="AH49" s="28"/>
-      <c r="AI49" s="28"/>
-      <c r="AJ49" s="28"/>
-      <c r="AK49" s="28"/>
-      <c r="AL49" s="28"/>
-      <c r="AM49" s="28"/>
-      <c r="AN49" s="28"/>
-      <c r="AO49" s="28"/>
-      <c r="AP49" s="28"/>
-      <c r="AQ49" s="28"/>
-      <c r="AR49" s="28"/>
-      <c r="AS49" s="28"/>
-      <c r="AT49" s="28"/>
-      <c r="AU49" s="28"/>
-      <c r="AV49" s="28"/>
-      <c r="AW49" s="28"/>
-      <c r="AX49" s="28"/>
-      <c r="AY49" s="28"/>
-      <c r="AZ49" s="28"/>
-      <c r="BA49" s="28"/>
-      <c r="BB49" s="28"/>
-      <c r="BC49" s="28"/>
-      <c r="BD49" s="14"/>
+      <c r="Z49" s="33"/>
+      <c r="AA49" s="33"/>
+      <c r="AB49" s="33"/>
+      <c r="AC49" s="33"/>
+      <c r="AD49" s="33"/>
+      <c r="AE49" s="33"/>
+      <c r="AF49" s="33"/>
+      <c r="AG49" s="33"/>
+      <c r="AH49" s="33"/>
+      <c r="AI49" s="33"/>
+      <c r="AJ49" s="33"/>
+      <c r="AK49" s="33"/>
+      <c r="AL49" s="33"/>
+      <c r="AM49" s="33"/>
+      <c r="AN49" s="33"/>
+      <c r="AO49" s="33"/>
+      <c r="AP49" s="33"/>
+      <c r="AQ49" s="33"/>
+      <c r="AR49" s="33"/>
+      <c r="AS49" s="33"/>
+      <c r="AT49" s="33"/>
+      <c r="AU49" s="33"/>
+      <c r="AV49" s="33"/>
+      <c r="AW49" s="33"/>
+      <c r="AX49" s="33"/>
+      <c r="AY49" s="33"/>
+      <c r="AZ49" s="33"/>
+      <c r="BA49" s="33"/>
+      <c r="BB49" s="33"/>
+      <c r="BC49" s="33"/>
+      <c r="BD49" s="12"/>
       <c r="BE49" s="8"/>
       <c r="BF49" s="8"/>
       <c r="BG49" s="8"/>
@@ -14953,7 +14929,7 @@
       <c r="CT49" s="8"/>
       <c r="CU49" s="8"/>
     </row>
-    <row r="50" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
@@ -14978,37 +14954,37 @@
       <c r="W50" s="8"/>
       <c r="X50" s="8"/>
       <c r="Y50" s="8"/>
-      <c r="Z50" s="28"/>
-      <c r="AA50" s="28"/>
-      <c r="AB50" s="28"/>
-      <c r="AC50" s="28"/>
-      <c r="AD50" s="28"/>
-      <c r="AE50" s="28"/>
-      <c r="AF50" s="28"/>
-      <c r="AG50" s="28"/>
-      <c r="AH50" s="28"/>
-      <c r="AI50" s="28"/>
-      <c r="AJ50" s="28"/>
-      <c r="AK50" s="28"/>
-      <c r="AL50" s="28"/>
-      <c r="AM50" s="28"/>
-      <c r="AN50" s="28"/>
-      <c r="AO50" s="28"/>
-      <c r="AP50" s="28"/>
-      <c r="AQ50" s="28"/>
-      <c r="AR50" s="28"/>
-      <c r="AS50" s="28"/>
-      <c r="AT50" s="28"/>
-      <c r="AU50" s="28"/>
-      <c r="AV50" s="28"/>
-      <c r="AW50" s="28"/>
-      <c r="AX50" s="28"/>
-      <c r="AY50" s="28"/>
-      <c r="AZ50" s="28"/>
-      <c r="BA50" s="28"/>
-      <c r="BB50" s="28"/>
-      <c r="BC50" s="28"/>
-      <c r="BD50" s="14"/>
+      <c r="Z50" s="33"/>
+      <c r="AA50" s="33"/>
+      <c r="AB50" s="33"/>
+      <c r="AC50" s="33"/>
+      <c r="AD50" s="33"/>
+      <c r="AE50" s="33"/>
+      <c r="AF50" s="33"/>
+      <c r="AG50" s="33"/>
+      <c r="AH50" s="33"/>
+      <c r="AI50" s="33"/>
+      <c r="AJ50" s="33"/>
+      <c r="AK50" s="33"/>
+      <c r="AL50" s="33"/>
+      <c r="AM50" s="33"/>
+      <c r="AN50" s="33"/>
+      <c r="AO50" s="33"/>
+      <c r="AP50" s="33"/>
+      <c r="AQ50" s="33"/>
+      <c r="AR50" s="33"/>
+      <c r="AS50" s="33"/>
+      <c r="AT50" s="33"/>
+      <c r="AU50" s="33"/>
+      <c r="AV50" s="33"/>
+      <c r="AW50" s="33"/>
+      <c r="AX50" s="33"/>
+      <c r="AY50" s="33"/>
+      <c r="AZ50" s="33"/>
+      <c r="BA50" s="33"/>
+      <c r="BB50" s="33"/>
+      <c r="BC50" s="33"/>
+      <c r="BD50" s="12"/>
       <c r="BE50" s="8"/>
       <c r="BF50" s="8"/>
       <c r="BG50" s="8"/>
@@ -15053,24 +15029,24 @@
       <c r="CT50" s="8"/>
       <c r="CU50" s="8"/>
     </row>
-    <row r="51" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="32"/>
-      <c r="L51" s="32"/>
-      <c r="M51" s="32"/>
-      <c r="N51" s="32"/>
-      <c r="O51" s="32"/>
-      <c r="P51" s="32"/>
+    <row r="51" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="26"/>
+      <c r="J51" s="26"/>
+      <c r="K51" s="26"/>
+      <c r="L51" s="26"/>
+      <c r="M51" s="26"/>
+      <c r="N51" s="26"/>
+      <c r="O51" s="26"/>
+      <c r="P51" s="26"/>
       <c r="Q51" s="8"/>
       <c r="R51" s="8"/>
       <c r="S51" s="8"/>
@@ -15080,39 +15056,39 @@
       <c r="W51" s="8"/>
       <c r="X51" s="8"/>
       <c r="Y51" s="8"/>
-      <c r="Z51" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA51" s="16"/>
-      <c r="AB51" s="16"/>
-      <c r="AC51" s="16"/>
-      <c r="AD51" s="16"/>
-      <c r="AE51" s="16"/>
-      <c r="AF51" s="16"/>
-      <c r="AG51" s="16"/>
-      <c r="AH51" s="16"/>
-      <c r="AI51" s="16"/>
-      <c r="AJ51" s="16"/>
-      <c r="AK51" s="16"/>
-      <c r="AL51" s="16"/>
-      <c r="AM51" s="16"/>
-      <c r="AN51" s="16"/>
-      <c r="AO51" s="16"/>
-      <c r="AP51" s="16"/>
-      <c r="AQ51" s="16"/>
-      <c r="AR51" s="16"/>
-      <c r="AS51" s="16"/>
-      <c r="AT51" s="16"/>
-      <c r="AU51" s="16"/>
-      <c r="AV51" s="16"/>
-      <c r="AW51" s="16"/>
-      <c r="AX51" s="16"/>
-      <c r="AY51" s="16"/>
-      <c r="AZ51" s="16"/>
-      <c r="BA51" s="16"/>
-      <c r="BB51" s="16"/>
-      <c r="BC51" s="16"/>
-      <c r="BD51" s="26"/>
+      <c r="Z51" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA51" s="34"/>
+      <c r="AB51" s="34"/>
+      <c r="AC51" s="34"/>
+      <c r="AD51" s="34"/>
+      <c r="AE51" s="34"/>
+      <c r="AF51" s="34"/>
+      <c r="AG51" s="34"/>
+      <c r="AH51" s="34"/>
+      <c r="AI51" s="34"/>
+      <c r="AJ51" s="34"/>
+      <c r="AK51" s="34"/>
+      <c r="AL51" s="34"/>
+      <c r="AM51" s="34"/>
+      <c r="AN51" s="34"/>
+      <c r="AO51" s="34"/>
+      <c r="AP51" s="34"/>
+      <c r="AQ51" s="34"/>
+      <c r="AR51" s="34"/>
+      <c r="AS51" s="34"/>
+      <c r="AT51" s="34"/>
+      <c r="AU51" s="34"/>
+      <c r="AV51" s="34"/>
+      <c r="AW51" s="34"/>
+      <c r="AX51" s="34"/>
+      <c r="AY51" s="34"/>
+      <c r="AZ51" s="34"/>
+      <c r="BA51" s="34"/>
+      <c r="BB51" s="34"/>
+      <c r="BC51" s="34"/>
+      <c r="BD51" s="14"/>
       <c r="BE51" s="8"/>
       <c r="BF51" s="8"/>
       <c r="BG51" s="8"/>
@@ -15157,22 +15133,22 @@
       <c r="CT51" s="8"/>
       <c r="CU51" s="8"/>
     </row>
-    <row r="52" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="32"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="32"/>
-      <c r="L52" s="32"/>
-      <c r="M52" s="32"/>
-      <c r="N52" s="32"/>
-      <c r="O52" s="32"/>
-      <c r="P52" s="32"/>
+    <row r="52" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="26"/>
+      <c r="K52" s="26"/>
+      <c r="L52" s="26"/>
+      <c r="M52" s="26"/>
+      <c r="N52" s="26"/>
+      <c r="O52" s="26"/>
+      <c r="P52" s="26"/>
       <c r="Q52" s="8"/>
       <c r="R52" s="8"/>
       <c r="S52" s="8"/>
@@ -15182,37 +15158,37 @@
       <c r="W52" s="8"/>
       <c r="X52" s="8"/>
       <c r="Y52" s="8"/>
-      <c r="Z52" s="16"/>
-      <c r="AA52" s="16"/>
-      <c r="AB52" s="16"/>
-      <c r="AC52" s="16"/>
-      <c r="AD52" s="16"/>
-      <c r="AE52" s="16"/>
-      <c r="AF52" s="16"/>
-      <c r="AG52" s="16"/>
-      <c r="AH52" s="16"/>
-      <c r="AI52" s="16"/>
-      <c r="AJ52" s="16"/>
-      <c r="AK52" s="16"/>
-      <c r="AL52" s="16"/>
-      <c r="AM52" s="16"/>
-      <c r="AN52" s="16"/>
-      <c r="AO52" s="16"/>
-      <c r="AP52" s="16"/>
-      <c r="AQ52" s="16"/>
-      <c r="AR52" s="16"/>
-      <c r="AS52" s="16"/>
-      <c r="AT52" s="16"/>
-      <c r="AU52" s="16"/>
-      <c r="AV52" s="16"/>
-      <c r="AW52" s="16"/>
-      <c r="AX52" s="16"/>
-      <c r="AY52" s="16"/>
-      <c r="AZ52" s="16"/>
-      <c r="BA52" s="16"/>
-      <c r="BB52" s="16"/>
-      <c r="BC52" s="16"/>
-      <c r="BD52" s="26"/>
+      <c r="Z52" s="34"/>
+      <c r="AA52" s="34"/>
+      <c r="AB52" s="34"/>
+      <c r="AC52" s="34"/>
+      <c r="AD52" s="34"/>
+      <c r="AE52" s="34"/>
+      <c r="AF52" s="34"/>
+      <c r="AG52" s="34"/>
+      <c r="AH52" s="34"/>
+      <c r="AI52" s="34"/>
+      <c r="AJ52" s="34"/>
+      <c r="AK52" s="34"/>
+      <c r="AL52" s="34"/>
+      <c r="AM52" s="34"/>
+      <c r="AN52" s="34"/>
+      <c r="AO52" s="34"/>
+      <c r="AP52" s="34"/>
+      <c r="AQ52" s="34"/>
+      <c r="AR52" s="34"/>
+      <c r="AS52" s="34"/>
+      <c r="AT52" s="34"/>
+      <c r="AU52" s="34"/>
+      <c r="AV52" s="34"/>
+      <c r="AW52" s="34"/>
+      <c r="AX52" s="34"/>
+      <c r="AY52" s="34"/>
+      <c r="AZ52" s="34"/>
+      <c r="BA52" s="34"/>
+      <c r="BB52" s="34"/>
+      <c r="BC52" s="34"/>
+      <c r="BD52" s="14"/>
       <c r="BE52" s="8"/>
       <c r="BF52" s="8"/>
       <c r="BG52" s="8"/>
@@ -15257,22 +15233,22 @@
       <c r="CT52" s="8"/>
       <c r="CU52" s="8"/>
     </row>
-    <row r="53" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
-      <c r="N53" s="31"/>
-      <c r="O53" s="31"/>
-      <c r="P53" s="31"/>
+    <row r="53" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="19"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="19"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="19"/>
+      <c r="K53" s="19"/>
+      <c r="L53" s="19"/>
+      <c r="M53" s="19"/>
+      <c r="N53" s="19"/>
+      <c r="O53" s="19"/>
+      <c r="P53" s="19"/>
       <c r="Q53" s="8"/>
       <c r="R53" s="8"/>
       <c r="S53" s="8"/>
@@ -15357,66 +15333,66 @@
       <c r="CT53" s="8"/>
       <c r="CU53" s="8"/>
     </row>
-    <row r="54" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="27"/>
-      <c r="J54" s="27"/>
-      <c r="K54" s="27"/>
-      <c r="L54" s="27"/>
-      <c r="M54" s="27"/>
-      <c r="N54" s="27"/>
-      <c r="O54" s="27"/>
-      <c r="P54" s="27"/>
+    <row r="54" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" s="40"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="40"/>
+      <c r="I54" s="40"/>
+      <c r="J54" s="40"/>
+      <c r="K54" s="40"/>
+      <c r="L54" s="40"/>
+      <c r="M54" s="40"/>
+      <c r="N54" s="40"/>
+      <c r="O54" s="40"/>
+      <c r="P54" s="40"/>
       <c r="Q54" s="8"/>
-      <c r="R54" s="24"/>
-      <c r="S54" s="24"/>
-      <c r="T54" s="24"/>
-      <c r="U54" s="24"/>
-      <c r="V54" s="24"/>
-      <c r="W54" s="24"/>
-      <c r="X54" s="24"/>
-      <c r="Y54" s="24"/>
-      <c r="Z54" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA54" s="23"/>
-      <c r="AB54" s="23"/>
-      <c r="AC54" s="23"/>
-      <c r="AD54" s="23"/>
-      <c r="AE54" s="23"/>
-      <c r="AF54" s="23"/>
-      <c r="AG54" s="23"/>
-      <c r="AH54" s="23"/>
-      <c r="AI54" s="23"/>
-      <c r="AJ54" s="23"/>
-      <c r="AK54" s="23"/>
-      <c r="AL54" s="23"/>
-      <c r="AM54" s="23"/>
-      <c r="AN54" s="23"/>
-      <c r="AO54" s="23"/>
-      <c r="AP54" s="23"/>
-      <c r="AQ54" s="23"/>
-      <c r="AR54" s="23"/>
-      <c r="AS54" s="23"/>
-      <c r="AT54" s="23"/>
-      <c r="AU54" s="23"/>
-      <c r="AV54" s="23"/>
-      <c r="AW54" s="23"/>
-      <c r="AX54" s="23"/>
-      <c r="AY54" s="23"/>
-      <c r="AZ54" s="23"/>
-      <c r="BA54" s="23"/>
-      <c r="BB54" s="23"/>
-      <c r="BC54" s="23"/>
-      <c r="BD54" s="19"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="18"/>
+      <c r="T54" s="18"/>
+      <c r="U54" s="18"/>
+      <c r="V54" s="18"/>
+      <c r="W54" s="18"/>
+      <c r="X54" s="18"/>
+      <c r="Y54" s="18"/>
+      <c r="Z54" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA54" s="38"/>
+      <c r="AB54" s="38"/>
+      <c r="AC54" s="38"/>
+      <c r="AD54" s="38"/>
+      <c r="AE54" s="38"/>
+      <c r="AF54" s="38"/>
+      <c r="AG54" s="38"/>
+      <c r="AH54" s="38"/>
+      <c r="AI54" s="38"/>
+      <c r="AJ54" s="38"/>
+      <c r="AK54" s="38"/>
+      <c r="AL54" s="38"/>
+      <c r="AM54" s="38"/>
+      <c r="AN54" s="38"/>
+      <c r="AO54" s="38"/>
+      <c r="AP54" s="38"/>
+      <c r="AQ54" s="38"/>
+      <c r="AR54" s="38"/>
+      <c r="AS54" s="38"/>
+      <c r="AT54" s="38"/>
+      <c r="AU54" s="38"/>
+      <c r="AV54" s="38"/>
+      <c r="AW54" s="38"/>
+      <c r="AX54" s="38"/>
+      <c r="AY54" s="38"/>
+      <c r="AZ54" s="38"/>
+      <c r="BA54" s="38"/>
+      <c r="BB54" s="38"/>
+      <c r="BC54" s="38"/>
+      <c r="BD54" s="16"/>
       <c r="BE54" s="8"/>
       <c r="BF54" s="8"/>
       <c r="BG54" s="8"/>
@@ -15461,22 +15437,22 @@
       <c r="CT54" s="8"/>
       <c r="CU54" s="8"/>
     </row>
-    <row r="55" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="27"/>
-      <c r="N55" s="27"/>
-      <c r="O55" s="27"/>
-      <c r="P55" s="27"/>
+    <row r="55" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="40"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="40"/>
+      <c r="I55" s="40"/>
+      <c r="J55" s="40"/>
+      <c r="K55" s="40"/>
+      <c r="L55" s="40"/>
+      <c r="M55" s="40"/>
+      <c r="N55" s="40"/>
+      <c r="O55" s="40"/>
+      <c r="P55" s="40"/>
       <c r="Q55" s="8"/>
       <c r="R55" s="8"/>
       <c r="S55" s="8"/>
@@ -15486,37 +15462,37 @@
       <c r="W55" s="8"/>
       <c r="X55" s="8"/>
       <c r="Y55" s="8"/>
-      <c r="Z55" s="20"/>
-      <c r="AA55" s="20"/>
-      <c r="AB55" s="20"/>
-      <c r="AC55" s="20"/>
-      <c r="AD55" s="20"/>
-      <c r="AE55" s="20"/>
-      <c r="AF55" s="20"/>
-      <c r="AG55" s="20"/>
-      <c r="AH55" s="20"/>
-      <c r="AI55" s="20"/>
-      <c r="AJ55" s="20"/>
-      <c r="AK55" s="20"/>
-      <c r="AL55" s="20"/>
-      <c r="AM55" s="20"/>
-      <c r="AN55" s="20"/>
-      <c r="AO55" s="20"/>
-      <c r="AP55" s="20"/>
-      <c r="AQ55" s="20"/>
-      <c r="AR55" s="20"/>
-      <c r="AS55" s="20"/>
-      <c r="AT55" s="20"/>
-      <c r="AU55" s="20"/>
-      <c r="AV55" s="20"/>
-      <c r="AW55" s="20"/>
-      <c r="AX55" s="20"/>
-      <c r="AY55" s="20"/>
-      <c r="AZ55" s="20"/>
-      <c r="BA55" s="20"/>
-      <c r="BB55" s="20"/>
-      <c r="BC55" s="20"/>
-      <c r="BD55" s="19"/>
+      <c r="Z55" s="39"/>
+      <c r="AA55" s="39"/>
+      <c r="AB55" s="39"/>
+      <c r="AC55" s="39"/>
+      <c r="AD55" s="39"/>
+      <c r="AE55" s="39"/>
+      <c r="AF55" s="39"/>
+      <c r="AG55" s="39"/>
+      <c r="AH55" s="39"/>
+      <c r="AI55" s="39"/>
+      <c r="AJ55" s="39"/>
+      <c r="AK55" s="39"/>
+      <c r="AL55" s="39"/>
+      <c r="AM55" s="39"/>
+      <c r="AN55" s="39"/>
+      <c r="AO55" s="39"/>
+      <c r="AP55" s="39"/>
+      <c r="AQ55" s="39"/>
+      <c r="AR55" s="39"/>
+      <c r="AS55" s="39"/>
+      <c r="AT55" s="39"/>
+      <c r="AU55" s="39"/>
+      <c r="AV55" s="39"/>
+      <c r="AW55" s="39"/>
+      <c r="AX55" s="39"/>
+      <c r="AY55" s="39"/>
+      <c r="AZ55" s="39"/>
+      <c r="BA55" s="39"/>
+      <c r="BB55" s="39"/>
+      <c r="BC55" s="39"/>
+      <c r="BD55" s="16"/>
       <c r="BE55" s="8"/>
       <c r="BF55" s="8"/>
       <c r="BG55" s="8"/>
@@ -15561,22 +15537,22 @@
       <c r="CT55" s="8"/>
       <c r="CU55" s="8"/>
     </row>
-    <row r="56" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="27"/>
-      <c r="C56" s="27"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="27"/>
-      <c r="H56" s="27"/>
-      <c r="I56" s="27"/>
-      <c r="J56" s="27"/>
-      <c r="K56" s="27"/>
-      <c r="L56" s="27"/>
-      <c r="M56" s="27"/>
-      <c r="N56" s="27"/>
-      <c r="O56" s="27"/>
-      <c r="P56" s="27"/>
+    <row r="56" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="40"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="40"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="40"/>
+      <c r="I56" s="40"/>
+      <c r="J56" s="40"/>
+      <c r="K56" s="40"/>
+      <c r="L56" s="40"/>
+      <c r="M56" s="40"/>
+      <c r="N56" s="40"/>
+      <c r="O56" s="40"/>
+      <c r="P56" s="40"/>
       <c r="Q56" s="8"/>
       <c r="R56" s="8"/>
       <c r="S56" s="8"/>
@@ -15586,37 +15562,37 @@
       <c r="W56" s="8"/>
       <c r="X56" s="8"/>
       <c r="Y56" s="8"/>
-      <c r="Z56" s="20"/>
-      <c r="AA56" s="20"/>
-      <c r="AB56" s="20"/>
-      <c r="AC56" s="20"/>
-      <c r="AD56" s="20"/>
-      <c r="AE56" s="20"/>
-      <c r="AF56" s="20"/>
-      <c r="AG56" s="20"/>
-      <c r="AH56" s="20"/>
-      <c r="AI56" s="20"/>
-      <c r="AJ56" s="20"/>
-      <c r="AK56" s="20"/>
-      <c r="AL56" s="20"/>
-      <c r="AM56" s="20"/>
-      <c r="AN56" s="20"/>
-      <c r="AO56" s="20"/>
-      <c r="AP56" s="20"/>
-      <c r="AQ56" s="20"/>
-      <c r="AR56" s="20"/>
-      <c r="AS56" s="20"/>
-      <c r="AT56" s="20"/>
-      <c r="AU56" s="20"/>
-      <c r="AV56" s="20"/>
-      <c r="AW56" s="20"/>
-      <c r="AX56" s="20"/>
-      <c r="AY56" s="20"/>
-      <c r="AZ56" s="20"/>
-      <c r="BA56" s="20"/>
-      <c r="BB56" s="20"/>
-      <c r="BC56" s="20"/>
-      <c r="BD56" s="19"/>
+      <c r="Z56" s="39"/>
+      <c r="AA56" s="39"/>
+      <c r="AB56" s="39"/>
+      <c r="AC56" s="39"/>
+      <c r="AD56" s="39"/>
+      <c r="AE56" s="39"/>
+      <c r="AF56" s="39"/>
+      <c r="AG56" s="39"/>
+      <c r="AH56" s="39"/>
+      <c r="AI56" s="39"/>
+      <c r="AJ56" s="39"/>
+      <c r="AK56" s="39"/>
+      <c r="AL56" s="39"/>
+      <c r="AM56" s="39"/>
+      <c r="AN56" s="39"/>
+      <c r="AO56" s="39"/>
+      <c r="AP56" s="39"/>
+      <c r="AQ56" s="39"/>
+      <c r="AR56" s="39"/>
+      <c r="AS56" s="39"/>
+      <c r="AT56" s="39"/>
+      <c r="AU56" s="39"/>
+      <c r="AV56" s="39"/>
+      <c r="AW56" s="39"/>
+      <c r="AX56" s="39"/>
+      <c r="AY56" s="39"/>
+      <c r="AZ56" s="39"/>
+      <c r="BA56" s="39"/>
+      <c r="BB56" s="39"/>
+      <c r="BC56" s="39"/>
+      <c r="BD56" s="16"/>
       <c r="BE56" s="8"/>
       <c r="BF56" s="8"/>
       <c r="BG56" s="8"/>
@@ -15661,24 +15637,24 @@
       <c r="CT56" s="8"/>
       <c r="CU56" s="8"/>
     </row>
-    <row r="57" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="30"/>
-      <c r="J57" s="30"/>
-      <c r="K57" s="30"/>
-      <c r="L57" s="30"/>
-      <c r="M57" s="30"/>
-      <c r="N57" s="30"/>
-      <c r="O57" s="30"/>
-      <c r="P57" s="30"/>
+    <row r="57" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C57" s="41"/>
+      <c r="D57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="41"/>
+      <c r="J57" s="41"/>
+      <c r="K57" s="41"/>
+      <c r="L57" s="41"/>
+      <c r="M57" s="41"/>
+      <c r="N57" s="41"/>
+      <c r="O57" s="41"/>
+      <c r="P57" s="41"/>
       <c r="Q57" s="8"/>
       <c r="R57" s="8"/>
       <c r="S57" s="8"/>
@@ -15688,37 +15664,37 @@
       <c r="W57" s="8"/>
       <c r="X57" s="8"/>
       <c r="Y57" s="8"/>
-      <c r="Z57" s="20"/>
-      <c r="AA57" s="20"/>
-      <c r="AB57" s="20"/>
-      <c r="AC57" s="20"/>
-      <c r="AD57" s="20"/>
-      <c r="AE57" s="20"/>
-      <c r="AF57" s="20"/>
-      <c r="AG57" s="20"/>
-      <c r="AH57" s="20"/>
-      <c r="AI57" s="20"/>
-      <c r="AJ57" s="20"/>
-      <c r="AK57" s="20"/>
-      <c r="AL57" s="20"/>
-      <c r="AM57" s="20"/>
-      <c r="AN57" s="20"/>
-      <c r="AO57" s="20"/>
-      <c r="AP57" s="20"/>
-      <c r="AQ57" s="20"/>
-      <c r="AR57" s="20"/>
-      <c r="AS57" s="20"/>
-      <c r="AT57" s="20"/>
-      <c r="AU57" s="20"/>
-      <c r="AV57" s="20"/>
-      <c r="AW57" s="20"/>
-      <c r="AX57" s="20"/>
-      <c r="AY57" s="20"/>
-      <c r="AZ57" s="20"/>
-      <c r="BA57" s="20"/>
-      <c r="BB57" s="20"/>
-      <c r="BC57" s="20"/>
-      <c r="BD57" s="19"/>
+      <c r="Z57" s="39"/>
+      <c r="AA57" s="39"/>
+      <c r="AB57" s="39"/>
+      <c r="AC57" s="39"/>
+      <c r="AD57" s="39"/>
+      <c r="AE57" s="39"/>
+      <c r="AF57" s="39"/>
+      <c r="AG57" s="39"/>
+      <c r="AH57" s="39"/>
+      <c r="AI57" s="39"/>
+      <c r="AJ57" s="39"/>
+      <c r="AK57" s="39"/>
+      <c r="AL57" s="39"/>
+      <c r="AM57" s="39"/>
+      <c r="AN57" s="39"/>
+      <c r="AO57" s="39"/>
+      <c r="AP57" s="39"/>
+      <c r="AQ57" s="39"/>
+      <c r="AR57" s="39"/>
+      <c r="AS57" s="39"/>
+      <c r="AT57" s="39"/>
+      <c r="AU57" s="39"/>
+      <c r="AV57" s="39"/>
+      <c r="AW57" s="39"/>
+      <c r="AX57" s="39"/>
+      <c r="AY57" s="39"/>
+      <c r="AZ57" s="39"/>
+      <c r="BA57" s="39"/>
+      <c r="BB57" s="39"/>
+      <c r="BC57" s="39"/>
+      <c r="BD57" s="16"/>
       <c r="BE57" s="8"/>
       <c r="BF57" s="8"/>
       <c r="BG57" s="8"/>
@@ -15763,22 +15739,22 @@
       <c r="CT57" s="8"/>
       <c r="CU57" s="8"/>
     </row>
-    <row r="58" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="30"/>
-      <c r="K58" s="30"/>
-      <c r="L58" s="30"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="30"/>
-      <c r="O58" s="30"/>
-      <c r="P58" s="30"/>
+    <row r="58" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="41"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="41"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="41"/>
+      <c r="G58" s="41"/>
+      <c r="H58" s="41"/>
+      <c r="I58" s="41"/>
+      <c r="J58" s="41"/>
+      <c r="K58" s="41"/>
+      <c r="L58" s="41"/>
+      <c r="M58" s="41"/>
+      <c r="N58" s="41"/>
+      <c r="O58" s="41"/>
+      <c r="P58" s="41"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
       <c r="S58" s="8"/>
@@ -15788,37 +15764,37 @@
       <c r="W58" s="8"/>
       <c r="X58" s="8"/>
       <c r="Y58" s="8"/>
-      <c r="Z58" s="20"/>
-      <c r="AA58" s="20"/>
-      <c r="AB58" s="20"/>
-      <c r="AC58" s="20"/>
-      <c r="AD58" s="20"/>
-      <c r="AE58" s="20"/>
-      <c r="AF58" s="20"/>
-      <c r="AG58" s="20"/>
-      <c r="AH58" s="20"/>
-      <c r="AI58" s="20"/>
-      <c r="AJ58" s="20"/>
-      <c r="AK58" s="20"/>
-      <c r="AL58" s="20"/>
-      <c r="AM58" s="20"/>
-      <c r="AN58" s="20"/>
-      <c r="AO58" s="20"/>
-      <c r="AP58" s="20"/>
-      <c r="AQ58" s="20"/>
-      <c r="AR58" s="20"/>
-      <c r="AS58" s="20"/>
-      <c r="AT58" s="20"/>
-      <c r="AU58" s="20"/>
-      <c r="AV58" s="20"/>
-      <c r="AW58" s="20"/>
-      <c r="AX58" s="20"/>
-      <c r="AY58" s="20"/>
-      <c r="AZ58" s="20"/>
-      <c r="BA58" s="20"/>
-      <c r="BB58" s="20"/>
-      <c r="BC58" s="20"/>
-      <c r="BD58" s="19"/>
+      <c r="Z58" s="39"/>
+      <c r="AA58" s="39"/>
+      <c r="AB58" s="39"/>
+      <c r="AC58" s="39"/>
+      <c r="AD58" s="39"/>
+      <c r="AE58" s="39"/>
+      <c r="AF58" s="39"/>
+      <c r="AG58" s="39"/>
+      <c r="AH58" s="39"/>
+      <c r="AI58" s="39"/>
+      <c r="AJ58" s="39"/>
+      <c r="AK58" s="39"/>
+      <c r="AL58" s="39"/>
+      <c r="AM58" s="39"/>
+      <c r="AN58" s="39"/>
+      <c r="AO58" s="39"/>
+      <c r="AP58" s="39"/>
+      <c r="AQ58" s="39"/>
+      <c r="AR58" s="39"/>
+      <c r="AS58" s="39"/>
+      <c r="AT58" s="39"/>
+      <c r="AU58" s="39"/>
+      <c r="AV58" s="39"/>
+      <c r="AW58" s="39"/>
+      <c r="AX58" s="39"/>
+      <c r="AY58" s="39"/>
+      <c r="AZ58" s="39"/>
+      <c r="BA58" s="39"/>
+      <c r="BB58" s="39"/>
+      <c r="BC58" s="39"/>
+      <c r="BD58" s="16"/>
       <c r="BE58" s="8"/>
       <c r="BF58" s="8"/>
       <c r="BG58" s="8"/>
@@ -15863,7 +15839,7 @@
       <c r="CT58" s="8"/>
       <c r="CU58" s="8"/>
     </row>
-    <row r="59" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
@@ -15888,103 +15864,103 @@
       <c r="W59" s="8"/>
       <c r="X59" s="8"/>
       <c r="Y59" s="8"/>
-      <c r="Z59" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA59" s="28"/>
-      <c r="AB59" s="28"/>
-      <c r="AC59" s="28"/>
-      <c r="AD59" s="28"/>
-      <c r="AE59" s="28"/>
-      <c r="AF59" s="28"/>
-      <c r="AG59" s="28"/>
-      <c r="AH59" s="28"/>
-      <c r="AI59" s="28"/>
-      <c r="AJ59" s="28"/>
-      <c r="AK59" s="28"/>
-      <c r="AL59" s="28"/>
-      <c r="AM59" s="28"/>
-      <c r="AN59" s="28"/>
-      <c r="AO59" s="28"/>
-      <c r="AP59" s="28"/>
-      <c r="AQ59" s="28"/>
-      <c r="AR59" s="28"/>
-      <c r="AS59" s="28"/>
-      <c r="AT59" s="28"/>
-      <c r="AU59" s="28"/>
-      <c r="AV59" s="28"/>
-      <c r="AW59" s="28"/>
-      <c r="AX59" s="28"/>
-      <c r="AY59" s="28"/>
-      <c r="AZ59" s="28"/>
-      <c r="BA59" s="28"/>
-      <c r="BB59" s="28"/>
-      <c r="BC59" s="28"/>
-      <c r="BD59" s="14"/>
+      <c r="Z59" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA59" s="33"/>
+      <c r="AB59" s="33"/>
+      <c r="AC59" s="33"/>
+      <c r="AD59" s="33"/>
+      <c r="AE59" s="33"/>
+      <c r="AF59" s="33"/>
+      <c r="AG59" s="33"/>
+      <c r="AH59" s="33"/>
+      <c r="AI59" s="33"/>
+      <c r="AJ59" s="33"/>
+      <c r="AK59" s="33"/>
+      <c r="AL59" s="33"/>
+      <c r="AM59" s="33"/>
+      <c r="AN59" s="33"/>
+      <c r="AO59" s="33"/>
+      <c r="AP59" s="33"/>
+      <c r="AQ59" s="33"/>
+      <c r="AR59" s="33"/>
+      <c r="AS59" s="33"/>
+      <c r="AT59" s="33"/>
+      <c r="AU59" s="33"/>
+      <c r="AV59" s="33"/>
+      <c r="AW59" s="33"/>
+      <c r="AX59" s="33"/>
+      <c r="AY59" s="33"/>
+      <c r="AZ59" s="33"/>
+      <c r="BA59" s="33"/>
+      <c r="BB59" s="33"/>
+      <c r="BC59" s="33"/>
+      <c r="BD59" s="12"/>
       <c r="BE59" s="8"/>
-      <c r="BF59" s="24"/>
-      <c r="BG59" s="24"/>
-      <c r="BH59" s="24"/>
-      <c r="BI59" s="24"/>
-      <c r="BJ59" s="24"/>
-      <c r="BK59" s="24"/>
-      <c r="BL59" s="24"/>
-      <c r="BM59" s="24"/>
-      <c r="BN59" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="BO59" s="29"/>
-      <c r="BP59" s="29"/>
-      <c r="BQ59" s="29"/>
-      <c r="BR59" s="29"/>
-      <c r="BS59" s="29"/>
-      <c r="BT59" s="29"/>
-      <c r="BU59" s="29"/>
-      <c r="BV59" s="29"/>
-      <c r="BW59" s="29"/>
-      <c r="BX59" s="29"/>
-      <c r="BY59" s="29"/>
-      <c r="BZ59" s="29"/>
-      <c r="CA59" s="29"/>
-      <c r="CB59" s="29"/>
-      <c r="CC59" s="29"/>
-      <c r="CD59" s="29"/>
-      <c r="CE59" s="29"/>
-      <c r="CF59" s="29"/>
-      <c r="CG59" s="29"/>
-      <c r="CH59" s="29"/>
-      <c r="CI59" s="29"/>
-      <c r="CJ59" s="29"/>
-      <c r="CK59" s="29"/>
-      <c r="CL59" s="29"/>
-      <c r="CM59" s="29"/>
-      <c r="CN59" s="29"/>
-      <c r="CO59" s="29"/>
-      <c r="CP59" s="29"/>
-      <c r="CQ59" s="29"/>
-      <c r="CR59" s="21"/>
-      <c r="CS59" s="21"/>
-      <c r="CT59" s="21"/>
-      <c r="CU59" s="21"/>
+      <c r="BF59" s="18"/>
+      <c r="BG59" s="18"/>
+      <c r="BH59" s="18"/>
+      <c r="BI59" s="18"/>
+      <c r="BJ59" s="18"/>
+      <c r="BK59" s="18"/>
+      <c r="BL59" s="18"/>
+      <c r="BM59" s="18"/>
+      <c r="BN59" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="BO59" s="30"/>
+      <c r="BP59" s="30"/>
+      <c r="BQ59" s="30"/>
+      <c r="BR59" s="30"/>
+      <c r="BS59" s="30"/>
+      <c r="BT59" s="30"/>
+      <c r="BU59" s="30"/>
+      <c r="BV59" s="30"/>
+      <c r="BW59" s="30"/>
+      <c r="BX59" s="30"/>
+      <c r="BY59" s="30"/>
+      <c r="BZ59" s="30"/>
+      <c r="CA59" s="30"/>
+      <c r="CB59" s="30"/>
+      <c r="CC59" s="30"/>
+      <c r="CD59" s="30"/>
+      <c r="CE59" s="30"/>
+      <c r="CF59" s="30"/>
+      <c r="CG59" s="30"/>
+      <c r="CH59" s="30"/>
+      <c r="CI59" s="30"/>
+      <c r="CJ59" s="30"/>
+      <c r="CK59" s="30"/>
+      <c r="CL59" s="30"/>
+      <c r="CM59" s="30"/>
+      <c r="CN59" s="30"/>
+      <c r="CO59" s="30"/>
+      <c r="CP59" s="30"/>
+      <c r="CQ59" s="30"/>
+      <c r="CR59" s="17"/>
+      <c r="CS59" s="17"/>
+      <c r="CT59" s="17"/>
+      <c r="CU59" s="17"/>
     </row>
-    <row r="60" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="27"/>
-      <c r="J60" s="27"/>
-      <c r="K60" s="27"/>
-      <c r="L60" s="27"/>
-      <c r="M60" s="27"/>
-      <c r="N60" s="27"/>
-      <c r="O60" s="27"/>
-      <c r="P60" s="27"/>
+    <row r="60" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" s="40"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="40"/>
+      <c r="I60" s="40"/>
+      <c r="J60" s="40"/>
+      <c r="K60" s="40"/>
+      <c r="L60" s="40"/>
+      <c r="M60" s="40"/>
+      <c r="N60" s="40"/>
+      <c r="O60" s="40"/>
+      <c r="P60" s="40"/>
       <c r="Q60" s="8"/>
       <c r="R60" s="8"/>
       <c r="S60" s="8"/>
@@ -15994,37 +15970,37 @@
       <c r="W60" s="8"/>
       <c r="X60" s="8"/>
       <c r="Y60" s="8"/>
-      <c r="Z60" s="28"/>
-      <c r="AA60" s="28"/>
-      <c r="AB60" s="28"/>
-      <c r="AC60" s="28"/>
-      <c r="AD60" s="28"/>
-      <c r="AE60" s="28"/>
-      <c r="AF60" s="28"/>
-      <c r="AG60" s="28"/>
-      <c r="AH60" s="28"/>
-      <c r="AI60" s="28"/>
-      <c r="AJ60" s="28"/>
-      <c r="AK60" s="28"/>
-      <c r="AL60" s="28"/>
-      <c r="AM60" s="28"/>
-      <c r="AN60" s="28"/>
-      <c r="AO60" s="28"/>
-      <c r="AP60" s="28"/>
-      <c r="AQ60" s="28"/>
-      <c r="AR60" s="28"/>
-      <c r="AS60" s="28"/>
-      <c r="AT60" s="28"/>
-      <c r="AU60" s="28"/>
-      <c r="AV60" s="28"/>
-      <c r="AW60" s="28"/>
-      <c r="AX60" s="28"/>
-      <c r="AY60" s="28"/>
-      <c r="AZ60" s="28"/>
-      <c r="BA60" s="28"/>
-      <c r="BB60" s="28"/>
-      <c r="BC60" s="28"/>
-      <c r="BD60" s="14"/>
+      <c r="Z60" s="33"/>
+      <c r="AA60" s="33"/>
+      <c r="AB60" s="33"/>
+      <c r="AC60" s="33"/>
+      <c r="AD60" s="33"/>
+      <c r="AE60" s="33"/>
+      <c r="AF60" s="33"/>
+      <c r="AG60" s="33"/>
+      <c r="AH60" s="33"/>
+      <c r="AI60" s="33"/>
+      <c r="AJ60" s="33"/>
+      <c r="AK60" s="33"/>
+      <c r="AL60" s="33"/>
+      <c r="AM60" s="33"/>
+      <c r="AN60" s="33"/>
+      <c r="AO60" s="33"/>
+      <c r="AP60" s="33"/>
+      <c r="AQ60" s="33"/>
+      <c r="AR60" s="33"/>
+      <c r="AS60" s="33"/>
+      <c r="AT60" s="33"/>
+      <c r="AU60" s="33"/>
+      <c r="AV60" s="33"/>
+      <c r="AW60" s="33"/>
+      <c r="AX60" s="33"/>
+      <c r="AY60" s="33"/>
+      <c r="AZ60" s="33"/>
+      <c r="BA60" s="33"/>
+      <c r="BB60" s="33"/>
+      <c r="BC60" s="33"/>
+      <c r="BD60" s="12"/>
       <c r="BE60" s="8"/>
       <c r="BF60" s="8"/>
       <c r="BG60" s="8"/>
@@ -16034,57 +16010,57 @@
       <c r="BK60" s="8"/>
       <c r="BL60" s="8"/>
       <c r="BM60" s="8"/>
-      <c r="BN60" s="22"/>
-      <c r="BO60" s="22"/>
-      <c r="BP60" s="22"/>
-      <c r="BQ60" s="22"/>
-      <c r="BR60" s="22"/>
-      <c r="BS60" s="22"/>
-      <c r="BT60" s="22"/>
-      <c r="BU60" s="22"/>
-      <c r="BV60" s="22"/>
-      <c r="BW60" s="22"/>
-      <c r="BX60" s="22"/>
-      <c r="BY60" s="22"/>
-      <c r="BZ60" s="22"/>
-      <c r="CA60" s="22"/>
-      <c r="CB60" s="22"/>
-      <c r="CC60" s="22"/>
-      <c r="CD60" s="22"/>
-      <c r="CE60" s="22"/>
-      <c r="CF60" s="22"/>
-      <c r="CG60" s="22"/>
-      <c r="CH60" s="22"/>
-      <c r="CI60" s="22"/>
-      <c r="CJ60" s="22"/>
-      <c r="CK60" s="22"/>
-      <c r="CL60" s="22"/>
-      <c r="CM60" s="22"/>
-      <c r="CN60" s="22"/>
-      <c r="CO60" s="22"/>
-      <c r="CP60" s="22"/>
-      <c r="CQ60" s="22"/>
-      <c r="CR60" s="21"/>
-      <c r="CS60" s="21"/>
-      <c r="CT60" s="21"/>
-      <c r="CU60" s="21"/>
+      <c r="BN60" s="31"/>
+      <c r="BO60" s="31"/>
+      <c r="BP60" s="31"/>
+      <c r="BQ60" s="31"/>
+      <c r="BR60" s="31"/>
+      <c r="BS60" s="31"/>
+      <c r="BT60" s="31"/>
+      <c r="BU60" s="31"/>
+      <c r="BV60" s="31"/>
+      <c r="BW60" s="31"/>
+      <c r="BX60" s="31"/>
+      <c r="BY60" s="31"/>
+      <c r="BZ60" s="31"/>
+      <c r="CA60" s="31"/>
+      <c r="CB60" s="31"/>
+      <c r="CC60" s="31"/>
+      <c r="CD60" s="31"/>
+      <c r="CE60" s="31"/>
+      <c r="CF60" s="31"/>
+      <c r="CG60" s="31"/>
+      <c r="CH60" s="31"/>
+      <c r="CI60" s="31"/>
+      <c r="CJ60" s="31"/>
+      <c r="CK60" s="31"/>
+      <c r="CL60" s="31"/>
+      <c r="CM60" s="31"/>
+      <c r="CN60" s="31"/>
+      <c r="CO60" s="31"/>
+      <c r="CP60" s="31"/>
+      <c r="CQ60" s="31"/>
+      <c r="CR60" s="17"/>
+      <c r="CS60" s="17"/>
+      <c r="CT60" s="17"/>
+      <c r="CU60" s="17"/>
     </row>
-    <row r="61" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
-      <c r="N61" s="27"/>
-      <c r="O61" s="27"/>
-      <c r="P61" s="27"/>
+    <row r="61" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="40"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="40"/>
+      <c r="E61" s="40"/>
+      <c r="F61" s="40"/>
+      <c r="G61" s="40"/>
+      <c r="H61" s="40"/>
+      <c r="I61" s="40"/>
+      <c r="J61" s="40"/>
+      <c r="K61" s="40"/>
+      <c r="L61" s="40"/>
+      <c r="M61" s="40"/>
+      <c r="N61" s="40"/>
+      <c r="O61" s="40"/>
+      <c r="P61" s="40"/>
       <c r="Q61" s="8"/>
       <c r="R61" s="8"/>
       <c r="S61" s="8"/>
@@ -16094,37 +16070,37 @@
       <c r="W61" s="8"/>
       <c r="X61" s="8"/>
       <c r="Y61" s="8"/>
-      <c r="Z61" s="28"/>
-      <c r="AA61" s="28"/>
-      <c r="AB61" s="28"/>
-      <c r="AC61" s="28"/>
-      <c r="AD61" s="28"/>
-      <c r="AE61" s="28"/>
-      <c r="AF61" s="28"/>
-      <c r="AG61" s="28"/>
-      <c r="AH61" s="28"/>
-      <c r="AI61" s="28"/>
-      <c r="AJ61" s="28"/>
-      <c r="AK61" s="28"/>
-      <c r="AL61" s="28"/>
-      <c r="AM61" s="28"/>
-      <c r="AN61" s="28"/>
-      <c r="AO61" s="28"/>
-      <c r="AP61" s="28"/>
-      <c r="AQ61" s="28"/>
-      <c r="AR61" s="28"/>
-      <c r="AS61" s="28"/>
-      <c r="AT61" s="28"/>
-      <c r="AU61" s="28"/>
-      <c r="AV61" s="28"/>
-      <c r="AW61" s="28"/>
-      <c r="AX61" s="28"/>
-      <c r="AY61" s="28"/>
-      <c r="AZ61" s="28"/>
-      <c r="BA61" s="28"/>
-      <c r="BB61" s="28"/>
-      <c r="BC61" s="28"/>
-      <c r="BD61" s="14"/>
+      <c r="Z61" s="33"/>
+      <c r="AA61" s="33"/>
+      <c r="AB61" s="33"/>
+      <c r="AC61" s="33"/>
+      <c r="AD61" s="33"/>
+      <c r="AE61" s="33"/>
+      <c r="AF61" s="33"/>
+      <c r="AG61" s="33"/>
+      <c r="AH61" s="33"/>
+      <c r="AI61" s="33"/>
+      <c r="AJ61" s="33"/>
+      <c r="AK61" s="33"/>
+      <c r="AL61" s="33"/>
+      <c r="AM61" s="33"/>
+      <c r="AN61" s="33"/>
+      <c r="AO61" s="33"/>
+      <c r="AP61" s="33"/>
+      <c r="AQ61" s="33"/>
+      <c r="AR61" s="33"/>
+      <c r="AS61" s="33"/>
+      <c r="AT61" s="33"/>
+      <c r="AU61" s="33"/>
+      <c r="AV61" s="33"/>
+      <c r="AW61" s="33"/>
+      <c r="AX61" s="33"/>
+      <c r="AY61" s="33"/>
+      <c r="AZ61" s="33"/>
+      <c r="BA61" s="33"/>
+      <c r="BB61" s="33"/>
+      <c r="BC61" s="33"/>
+      <c r="BD61" s="12"/>
       <c r="BE61" s="8"/>
       <c r="BF61" s="8"/>
       <c r="BG61" s="8"/>
@@ -16134,57 +16110,57 @@
       <c r="BK61" s="8"/>
       <c r="BL61" s="8"/>
       <c r="BM61" s="8"/>
-      <c r="BN61" s="22"/>
-      <c r="BO61" s="22"/>
-      <c r="BP61" s="22"/>
-      <c r="BQ61" s="22"/>
-      <c r="BR61" s="22"/>
-      <c r="BS61" s="22"/>
-      <c r="BT61" s="22"/>
-      <c r="BU61" s="22"/>
-      <c r="BV61" s="22"/>
-      <c r="BW61" s="22"/>
-      <c r="BX61" s="22"/>
-      <c r="BY61" s="22"/>
-      <c r="BZ61" s="22"/>
-      <c r="CA61" s="22"/>
-      <c r="CB61" s="22"/>
-      <c r="CC61" s="22"/>
-      <c r="CD61" s="22"/>
-      <c r="CE61" s="22"/>
-      <c r="CF61" s="22"/>
-      <c r="CG61" s="22"/>
-      <c r="CH61" s="22"/>
-      <c r="CI61" s="22"/>
-      <c r="CJ61" s="22"/>
-      <c r="CK61" s="22"/>
-      <c r="CL61" s="22"/>
-      <c r="CM61" s="22"/>
-      <c r="CN61" s="22"/>
-      <c r="CO61" s="22"/>
-      <c r="CP61" s="22"/>
-      <c r="CQ61" s="22"/>
-      <c r="CR61" s="21"/>
-      <c r="CS61" s="21"/>
-      <c r="CT61" s="21"/>
-      <c r="CU61" s="21"/>
+      <c r="BN61" s="31"/>
+      <c r="BO61" s="31"/>
+      <c r="BP61" s="31"/>
+      <c r="BQ61" s="31"/>
+      <c r="BR61" s="31"/>
+      <c r="BS61" s="31"/>
+      <c r="BT61" s="31"/>
+      <c r="BU61" s="31"/>
+      <c r="BV61" s="31"/>
+      <c r="BW61" s="31"/>
+      <c r="BX61" s="31"/>
+      <c r="BY61" s="31"/>
+      <c r="BZ61" s="31"/>
+      <c r="CA61" s="31"/>
+      <c r="CB61" s="31"/>
+      <c r="CC61" s="31"/>
+      <c r="CD61" s="31"/>
+      <c r="CE61" s="31"/>
+      <c r="CF61" s="31"/>
+      <c r="CG61" s="31"/>
+      <c r="CH61" s="31"/>
+      <c r="CI61" s="31"/>
+      <c r="CJ61" s="31"/>
+      <c r="CK61" s="31"/>
+      <c r="CL61" s="31"/>
+      <c r="CM61" s="31"/>
+      <c r="CN61" s="31"/>
+      <c r="CO61" s="31"/>
+      <c r="CP61" s="31"/>
+      <c r="CQ61" s="31"/>
+      <c r="CR61" s="17"/>
+      <c r="CS61" s="17"/>
+      <c r="CT61" s="17"/>
+      <c r="CU61" s="17"/>
     </row>
-    <row r="62" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="27"/>
-      <c r="C62" s="27"/>
-      <c r="D62" s="27"/>
-      <c r="E62" s="27"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="27"/>
-      <c r="H62" s="27"/>
-      <c r="I62" s="27"/>
-      <c r="J62" s="27"/>
-      <c r="K62" s="27"/>
-      <c r="L62" s="27"/>
-      <c r="M62" s="27"/>
-      <c r="N62" s="27"/>
-      <c r="O62" s="27"/>
-      <c r="P62" s="27"/>
+    <row r="62" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="40"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
+      <c r="F62" s="40"/>
+      <c r="G62" s="40"/>
+      <c r="H62" s="40"/>
+      <c r="I62" s="40"/>
+      <c r="J62" s="40"/>
+      <c r="K62" s="40"/>
+      <c r="L62" s="40"/>
+      <c r="M62" s="40"/>
+      <c r="N62" s="40"/>
+      <c r="O62" s="40"/>
+      <c r="P62" s="40"/>
       <c r="Q62" s="8"/>
       <c r="R62" s="8"/>
       <c r="S62" s="8"/>
@@ -16194,39 +16170,39 @@
       <c r="W62" s="8"/>
       <c r="X62" s="8"/>
       <c r="Y62" s="8"/>
-      <c r="Z62" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA62" s="16"/>
-      <c r="AB62" s="16"/>
-      <c r="AC62" s="16"/>
-      <c r="AD62" s="16"/>
-      <c r="AE62" s="16"/>
-      <c r="AF62" s="16"/>
-      <c r="AG62" s="16"/>
-      <c r="AH62" s="16"/>
-      <c r="AI62" s="16"/>
-      <c r="AJ62" s="16"/>
-      <c r="AK62" s="16"/>
-      <c r="AL62" s="16"/>
-      <c r="AM62" s="16"/>
-      <c r="AN62" s="16"/>
-      <c r="AO62" s="16"/>
-      <c r="AP62" s="16"/>
-      <c r="AQ62" s="16"/>
-      <c r="AR62" s="16"/>
-      <c r="AS62" s="16"/>
-      <c r="AT62" s="16"/>
-      <c r="AU62" s="16"/>
-      <c r="AV62" s="16"/>
-      <c r="AW62" s="16"/>
-      <c r="AX62" s="16"/>
-      <c r="AY62" s="16"/>
-      <c r="AZ62" s="16"/>
-      <c r="BA62" s="16"/>
-      <c r="BB62" s="16"/>
-      <c r="BC62" s="16"/>
-      <c r="BD62" s="26"/>
+      <c r="Z62" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA62" s="34"/>
+      <c r="AB62" s="34"/>
+      <c r="AC62" s="34"/>
+      <c r="AD62" s="34"/>
+      <c r="AE62" s="34"/>
+      <c r="AF62" s="34"/>
+      <c r="AG62" s="34"/>
+      <c r="AH62" s="34"/>
+      <c r="AI62" s="34"/>
+      <c r="AJ62" s="34"/>
+      <c r="AK62" s="34"/>
+      <c r="AL62" s="34"/>
+      <c r="AM62" s="34"/>
+      <c r="AN62" s="34"/>
+      <c r="AO62" s="34"/>
+      <c r="AP62" s="34"/>
+      <c r="AQ62" s="34"/>
+      <c r="AR62" s="34"/>
+      <c r="AS62" s="34"/>
+      <c r="AT62" s="34"/>
+      <c r="AU62" s="34"/>
+      <c r="AV62" s="34"/>
+      <c r="AW62" s="34"/>
+      <c r="AX62" s="34"/>
+      <c r="AY62" s="34"/>
+      <c r="AZ62" s="34"/>
+      <c r="BA62" s="34"/>
+      <c r="BB62" s="34"/>
+      <c r="BC62" s="34"/>
+      <c r="BD62" s="14"/>
       <c r="BE62" s="8"/>
       <c r="BF62" s="8"/>
       <c r="BG62" s="8"/>
@@ -16236,61 +16212,61 @@
       <c r="BK62" s="8"/>
       <c r="BL62" s="8"/>
       <c r="BM62" s="8"/>
-      <c r="BN62" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="BO62" s="18"/>
-      <c r="BP62" s="18"/>
-      <c r="BQ62" s="18"/>
-      <c r="BR62" s="18"/>
-      <c r="BS62" s="18"/>
-      <c r="BT62" s="18"/>
-      <c r="BU62" s="18"/>
-      <c r="BV62" s="18"/>
-      <c r="BW62" s="18"/>
-      <c r="BX62" s="18"/>
-      <c r="BY62" s="18"/>
-      <c r="BZ62" s="18"/>
-      <c r="CA62" s="18"/>
-      <c r="CB62" s="18"/>
-      <c r="CC62" s="18"/>
-      <c r="CD62" s="18"/>
-      <c r="CE62" s="18"/>
-      <c r="CF62" s="18"/>
-      <c r="CG62" s="18"/>
-      <c r="CH62" s="18"/>
-      <c r="CI62" s="18"/>
-      <c r="CJ62" s="18"/>
-      <c r="CK62" s="18"/>
-      <c r="CL62" s="18"/>
-      <c r="CM62" s="18"/>
-      <c r="CN62" s="18"/>
-      <c r="CO62" s="18"/>
-      <c r="CP62" s="18"/>
-      <c r="CQ62" s="18"/>
-      <c r="CR62" s="17"/>
-      <c r="CS62" s="17"/>
-      <c r="CT62" s="17"/>
-      <c r="CU62" s="17"/>
+      <c r="BN62" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="BO62" s="32"/>
+      <c r="BP62" s="32"/>
+      <c r="BQ62" s="32"/>
+      <c r="BR62" s="32"/>
+      <c r="BS62" s="32"/>
+      <c r="BT62" s="32"/>
+      <c r="BU62" s="32"/>
+      <c r="BV62" s="32"/>
+      <c r="BW62" s="32"/>
+      <c r="BX62" s="32"/>
+      <c r="BY62" s="32"/>
+      <c r="BZ62" s="32"/>
+      <c r="CA62" s="32"/>
+      <c r="CB62" s="32"/>
+      <c r="CC62" s="32"/>
+      <c r="CD62" s="32"/>
+      <c r="CE62" s="32"/>
+      <c r="CF62" s="32"/>
+      <c r="CG62" s="32"/>
+      <c r="CH62" s="32"/>
+      <c r="CI62" s="32"/>
+      <c r="CJ62" s="32"/>
+      <c r="CK62" s="32"/>
+      <c r="CL62" s="32"/>
+      <c r="CM62" s="32"/>
+      <c r="CN62" s="32"/>
+      <c r="CO62" s="32"/>
+      <c r="CP62" s="32"/>
+      <c r="CQ62" s="32"/>
+      <c r="CR62" s="15"/>
+      <c r="CS62" s="15"/>
+      <c r="CT62" s="15"/>
+      <c r="CU62" s="15"/>
     </row>
-    <row r="63" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
-      <c r="H63" s="25"/>
-      <c r="I63" s="25"/>
-      <c r="J63" s="25"/>
-      <c r="K63" s="25"/>
-      <c r="L63" s="25"/>
-      <c r="M63" s="25"/>
-      <c r="N63" s="25"/>
-      <c r="O63" s="25"/>
-      <c r="P63" s="25"/>
+    <row r="63" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" s="42"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="G63" s="42"/>
+      <c r="H63" s="42"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="42"/>
+      <c r="K63" s="42"/>
+      <c r="L63" s="42"/>
+      <c r="M63" s="42"/>
+      <c r="N63" s="42"/>
+      <c r="O63" s="42"/>
+      <c r="P63" s="42"/>
       <c r="Q63" s="8"/>
       <c r="R63" s="8"/>
       <c r="S63" s="8"/>
@@ -16300,37 +16276,37 @@
       <c r="W63" s="8"/>
       <c r="X63" s="8"/>
       <c r="Y63" s="8"/>
-      <c r="Z63" s="16"/>
-      <c r="AA63" s="16"/>
-      <c r="AB63" s="16"/>
-      <c r="AC63" s="16"/>
-      <c r="AD63" s="16"/>
-      <c r="AE63" s="16"/>
-      <c r="AF63" s="16"/>
-      <c r="AG63" s="16"/>
-      <c r="AH63" s="16"/>
-      <c r="AI63" s="16"/>
-      <c r="AJ63" s="16"/>
-      <c r="AK63" s="16"/>
-      <c r="AL63" s="16"/>
-      <c r="AM63" s="16"/>
-      <c r="AN63" s="16"/>
-      <c r="AO63" s="16"/>
-      <c r="AP63" s="16"/>
-      <c r="AQ63" s="16"/>
-      <c r="AR63" s="16"/>
-      <c r="AS63" s="16"/>
-      <c r="AT63" s="16"/>
-      <c r="AU63" s="16"/>
-      <c r="AV63" s="16"/>
-      <c r="AW63" s="16"/>
-      <c r="AX63" s="16"/>
-      <c r="AY63" s="16"/>
-      <c r="AZ63" s="16"/>
-      <c r="BA63" s="16"/>
-      <c r="BB63" s="16"/>
-      <c r="BC63" s="16"/>
-      <c r="BD63" s="26"/>
+      <c r="Z63" s="34"/>
+      <c r="AA63" s="34"/>
+      <c r="AB63" s="34"/>
+      <c r="AC63" s="34"/>
+      <c r="AD63" s="34"/>
+      <c r="AE63" s="34"/>
+      <c r="AF63" s="34"/>
+      <c r="AG63" s="34"/>
+      <c r="AH63" s="34"/>
+      <c r="AI63" s="34"/>
+      <c r="AJ63" s="34"/>
+      <c r="AK63" s="34"/>
+      <c r="AL63" s="34"/>
+      <c r="AM63" s="34"/>
+      <c r="AN63" s="34"/>
+      <c r="AO63" s="34"/>
+      <c r="AP63" s="34"/>
+      <c r="AQ63" s="34"/>
+      <c r="AR63" s="34"/>
+      <c r="AS63" s="34"/>
+      <c r="AT63" s="34"/>
+      <c r="AU63" s="34"/>
+      <c r="AV63" s="34"/>
+      <c r="AW63" s="34"/>
+      <c r="AX63" s="34"/>
+      <c r="AY63" s="34"/>
+      <c r="AZ63" s="34"/>
+      <c r="BA63" s="34"/>
+      <c r="BB63" s="34"/>
+      <c r="BC63" s="34"/>
+      <c r="BD63" s="14"/>
       <c r="BE63" s="8"/>
       <c r="BF63" s="8"/>
       <c r="BG63" s="8"/>
@@ -16340,57 +16316,57 @@
       <c r="BK63" s="8"/>
       <c r="BL63" s="8"/>
       <c r="BM63" s="8"/>
-      <c r="BN63" s="18"/>
-      <c r="BO63" s="18"/>
-      <c r="BP63" s="18"/>
-      <c r="BQ63" s="18"/>
-      <c r="BR63" s="18"/>
-      <c r="BS63" s="18"/>
-      <c r="BT63" s="18"/>
-      <c r="BU63" s="18"/>
-      <c r="BV63" s="18"/>
-      <c r="BW63" s="18"/>
-      <c r="BX63" s="18"/>
-      <c r="BY63" s="18"/>
-      <c r="BZ63" s="18"/>
-      <c r="CA63" s="18"/>
-      <c r="CB63" s="18"/>
-      <c r="CC63" s="18"/>
-      <c r="CD63" s="18"/>
-      <c r="CE63" s="18"/>
-      <c r="CF63" s="18"/>
-      <c r="CG63" s="18"/>
-      <c r="CH63" s="18"/>
-      <c r="CI63" s="18"/>
-      <c r="CJ63" s="18"/>
-      <c r="CK63" s="18"/>
-      <c r="CL63" s="18"/>
-      <c r="CM63" s="18"/>
-      <c r="CN63" s="18"/>
-      <c r="CO63" s="18"/>
-      <c r="CP63" s="18"/>
-      <c r="CQ63" s="18"/>
-      <c r="CR63" s="17"/>
-      <c r="CS63" s="17"/>
-      <c r="CT63" s="17"/>
-      <c r="CU63" s="17"/>
+      <c r="BN63" s="32"/>
+      <c r="BO63" s="32"/>
+      <c r="BP63" s="32"/>
+      <c r="BQ63" s="32"/>
+      <c r="BR63" s="32"/>
+      <c r="BS63" s="32"/>
+      <c r="BT63" s="32"/>
+      <c r="BU63" s="32"/>
+      <c r="BV63" s="32"/>
+      <c r="BW63" s="32"/>
+      <c r="BX63" s="32"/>
+      <c r="BY63" s="32"/>
+      <c r="BZ63" s="32"/>
+      <c r="CA63" s="32"/>
+      <c r="CB63" s="32"/>
+      <c r="CC63" s="32"/>
+      <c r="CD63" s="32"/>
+      <c r="CE63" s="32"/>
+      <c r="CF63" s="32"/>
+      <c r="CG63" s="32"/>
+      <c r="CH63" s="32"/>
+      <c r="CI63" s="32"/>
+      <c r="CJ63" s="32"/>
+      <c r="CK63" s="32"/>
+      <c r="CL63" s="32"/>
+      <c r="CM63" s="32"/>
+      <c r="CN63" s="32"/>
+      <c r="CO63" s="32"/>
+      <c r="CP63" s="32"/>
+      <c r="CQ63" s="32"/>
+      <c r="CR63" s="15"/>
+      <c r="CS63" s="15"/>
+      <c r="CT63" s="15"/>
+      <c r="CU63" s="15"/>
     </row>
-    <row r="64" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
-      <c r="H64" s="25"/>
-      <c r="I64" s="25"/>
-      <c r="J64" s="25"/>
-      <c r="K64" s="25"/>
-      <c r="L64" s="25"/>
-      <c r="M64" s="25"/>
-      <c r="N64" s="25"/>
-      <c r="O64" s="25"/>
-      <c r="P64" s="25"/>
+    <row r="64" spans="2:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="42"/>
+      <c r="C64" s="42"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="42"/>
+      <c r="H64" s="42"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="42"/>
+      <c r="K64" s="42"/>
+      <c r="L64" s="42"/>
+      <c r="M64" s="42"/>
+      <c r="N64" s="42"/>
+      <c r="O64" s="42"/>
+      <c r="P64" s="42"/>
       <c r="Q64" s="8"/>
       <c r="R64" s="8"/>
       <c r="S64" s="8"/>
@@ -16475,48 +16451,48 @@
       <c r="CT64" s="8"/>
       <c r="CU64" s="8"/>
     </row>
-    <row r="65" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R65" s="24"/>
-      <c r="S65" s="24"/>
-      <c r="T65" s="24"/>
-      <c r="U65" s="24"/>
-      <c r="V65" s="24"/>
-      <c r="W65" s="24"/>
-      <c r="X65" s="24"/>
-      <c r="Y65" s="24"/>
-      <c r="Z65" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA65" s="23"/>
-      <c r="AB65" s="23"/>
-      <c r="AC65" s="23"/>
-      <c r="AD65" s="23"/>
-      <c r="AE65" s="23"/>
-      <c r="AF65" s="23"/>
-      <c r="AG65" s="23"/>
-      <c r="AH65" s="23"/>
-      <c r="AI65" s="23"/>
-      <c r="AJ65" s="23"/>
-      <c r="AK65" s="23"/>
-      <c r="AL65" s="23"/>
-      <c r="AM65" s="23"/>
-      <c r="AN65" s="23"/>
-      <c r="AO65" s="23"/>
-      <c r="AP65" s="23"/>
-      <c r="AQ65" s="23"/>
-      <c r="AR65" s="23"/>
-      <c r="AS65" s="23"/>
-      <c r="AT65" s="23"/>
-      <c r="AU65" s="23"/>
-      <c r="AV65" s="23"/>
-      <c r="AW65" s="23"/>
-      <c r="AX65" s="23"/>
-      <c r="AY65" s="23"/>
-      <c r="AZ65" s="23"/>
-      <c r="BA65" s="23"/>
-      <c r="BB65" s="23"/>
-      <c r="BC65" s="23"/>
-      <c r="BD65" s="19"/>
+    <row r="65" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R65" s="18"/>
+      <c r="S65" s="18"/>
+      <c r="T65" s="18"/>
+      <c r="U65" s="18"/>
+      <c r="V65" s="18"/>
+      <c r="W65" s="18"/>
+      <c r="X65" s="18"/>
+      <c r="Y65" s="18"/>
+      <c r="Z65" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA65" s="38"/>
+      <c r="AB65" s="38"/>
+      <c r="AC65" s="38"/>
+      <c r="AD65" s="38"/>
+      <c r="AE65" s="38"/>
+      <c r="AF65" s="38"/>
+      <c r="AG65" s="38"/>
+      <c r="AH65" s="38"/>
+      <c r="AI65" s="38"/>
+      <c r="AJ65" s="38"/>
+      <c r="AK65" s="38"/>
+      <c r="AL65" s="38"/>
+      <c r="AM65" s="38"/>
+      <c r="AN65" s="38"/>
+      <c r="AO65" s="38"/>
+      <c r="AP65" s="38"/>
+      <c r="AQ65" s="38"/>
+      <c r="AR65" s="38"/>
+      <c r="AS65" s="38"/>
+      <c r="AT65" s="38"/>
+      <c r="AU65" s="38"/>
+      <c r="AV65" s="38"/>
+      <c r="AW65" s="38"/>
+      <c r="AX65" s="38"/>
+      <c r="AY65" s="38"/>
+      <c r="AZ65" s="38"/>
+      <c r="BA65" s="38"/>
+      <c r="BB65" s="38"/>
+      <c r="BC65" s="38"/>
+      <c r="BD65" s="16"/>
       <c r="BE65" s="8"/>
       <c r="BF65" s="8"/>
       <c r="BG65" s="8"/>
@@ -16526,44 +16502,44 @@
       <c r="BK65" s="8"/>
       <c r="BL65" s="8"/>
       <c r="BM65" s="8"/>
-      <c r="BN65" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="BO65" s="22"/>
-      <c r="BP65" s="22"/>
-      <c r="BQ65" s="22"/>
-      <c r="BR65" s="22"/>
-      <c r="BS65" s="22"/>
-      <c r="BT65" s="22"/>
-      <c r="BU65" s="22"/>
-      <c r="BV65" s="22"/>
-      <c r="BW65" s="22"/>
-      <c r="BX65" s="22"/>
-      <c r="BY65" s="22"/>
-      <c r="BZ65" s="22"/>
-      <c r="CA65" s="22"/>
-      <c r="CB65" s="22"/>
-      <c r="CC65" s="22"/>
-      <c r="CD65" s="22"/>
-      <c r="CE65" s="22"/>
-      <c r="CF65" s="22"/>
-      <c r="CG65" s="22"/>
-      <c r="CH65" s="22"/>
-      <c r="CI65" s="22"/>
-      <c r="CJ65" s="22"/>
-      <c r="CK65" s="22"/>
-      <c r="CL65" s="22"/>
-      <c r="CM65" s="22"/>
-      <c r="CN65" s="22"/>
-      <c r="CO65" s="22"/>
-      <c r="CP65" s="22"/>
-      <c r="CQ65" s="22"/>
-      <c r="CR65" s="21"/>
-      <c r="CS65" s="21"/>
-      <c r="CT65" s="21"/>
-      <c r="CU65" s="21"/>
+      <c r="BN65" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO65" s="31"/>
+      <c r="BP65" s="31"/>
+      <c r="BQ65" s="31"/>
+      <c r="BR65" s="31"/>
+      <c r="BS65" s="31"/>
+      <c r="BT65" s="31"/>
+      <c r="BU65" s="31"/>
+      <c r="BV65" s="31"/>
+      <c r="BW65" s="31"/>
+      <c r="BX65" s="31"/>
+      <c r="BY65" s="31"/>
+      <c r="BZ65" s="31"/>
+      <c r="CA65" s="31"/>
+      <c r="CB65" s="31"/>
+      <c r="CC65" s="31"/>
+      <c r="CD65" s="31"/>
+      <c r="CE65" s="31"/>
+      <c r="CF65" s="31"/>
+      <c r="CG65" s="31"/>
+      <c r="CH65" s="31"/>
+      <c r="CI65" s="31"/>
+      <c r="CJ65" s="31"/>
+      <c r="CK65" s="31"/>
+      <c r="CL65" s="31"/>
+      <c r="CM65" s="31"/>
+      <c r="CN65" s="31"/>
+      <c r="CO65" s="31"/>
+      <c r="CP65" s="31"/>
+      <c r="CQ65" s="31"/>
+      <c r="CR65" s="17"/>
+      <c r="CS65" s="17"/>
+      <c r="CT65" s="17"/>
+      <c r="CU65" s="17"/>
     </row>
-    <row r="66" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R66" s="8"/>
       <c r="S66" s="8"/>
       <c r="T66" s="8"/>
@@ -16572,37 +16548,37 @@
       <c r="W66" s="8"/>
       <c r="X66" s="8"/>
       <c r="Y66" s="8"/>
-      <c r="Z66" s="20"/>
-      <c r="AA66" s="20"/>
-      <c r="AB66" s="20"/>
-      <c r="AC66" s="20"/>
-      <c r="AD66" s="20"/>
-      <c r="AE66" s="20"/>
-      <c r="AF66" s="20"/>
-      <c r="AG66" s="20"/>
-      <c r="AH66" s="20"/>
-      <c r="AI66" s="20"/>
-      <c r="AJ66" s="20"/>
-      <c r="AK66" s="20"/>
-      <c r="AL66" s="20"/>
-      <c r="AM66" s="20"/>
-      <c r="AN66" s="20"/>
-      <c r="AO66" s="20"/>
-      <c r="AP66" s="20"/>
-      <c r="AQ66" s="20"/>
-      <c r="AR66" s="20"/>
-      <c r="AS66" s="20"/>
-      <c r="AT66" s="20"/>
-      <c r="AU66" s="20"/>
-      <c r="AV66" s="20"/>
-      <c r="AW66" s="20"/>
-      <c r="AX66" s="20"/>
-      <c r="AY66" s="20"/>
-      <c r="AZ66" s="20"/>
-      <c r="BA66" s="20"/>
-      <c r="BB66" s="20"/>
-      <c r="BC66" s="20"/>
-      <c r="BD66" s="19"/>
+      <c r="Z66" s="39"/>
+      <c r="AA66" s="39"/>
+      <c r="AB66" s="39"/>
+      <c r="AC66" s="39"/>
+      <c r="AD66" s="39"/>
+      <c r="AE66" s="39"/>
+      <c r="AF66" s="39"/>
+      <c r="AG66" s="39"/>
+      <c r="AH66" s="39"/>
+      <c r="AI66" s="39"/>
+      <c r="AJ66" s="39"/>
+      <c r="AK66" s="39"/>
+      <c r="AL66" s="39"/>
+      <c r="AM66" s="39"/>
+      <c r="AN66" s="39"/>
+      <c r="AO66" s="39"/>
+      <c r="AP66" s="39"/>
+      <c r="AQ66" s="39"/>
+      <c r="AR66" s="39"/>
+      <c r="AS66" s="39"/>
+      <c r="AT66" s="39"/>
+      <c r="AU66" s="39"/>
+      <c r="AV66" s="39"/>
+      <c r="AW66" s="39"/>
+      <c r="AX66" s="39"/>
+      <c r="AY66" s="39"/>
+      <c r="AZ66" s="39"/>
+      <c r="BA66" s="39"/>
+      <c r="BB66" s="39"/>
+      <c r="BC66" s="39"/>
+      <c r="BD66" s="16"/>
       <c r="BE66" s="8"/>
       <c r="BF66" s="8"/>
       <c r="BG66" s="8"/>
@@ -16612,42 +16588,42 @@
       <c r="BK66" s="8"/>
       <c r="BL66" s="8"/>
       <c r="BM66" s="8"/>
-      <c r="BN66" s="22"/>
-      <c r="BO66" s="22"/>
-      <c r="BP66" s="22"/>
-      <c r="BQ66" s="22"/>
-      <c r="BR66" s="22"/>
-      <c r="BS66" s="22"/>
-      <c r="BT66" s="22"/>
-      <c r="BU66" s="22"/>
-      <c r="BV66" s="22"/>
-      <c r="BW66" s="22"/>
-      <c r="BX66" s="22"/>
-      <c r="BY66" s="22"/>
-      <c r="BZ66" s="22"/>
-      <c r="CA66" s="22"/>
-      <c r="CB66" s="22"/>
-      <c r="CC66" s="22"/>
-      <c r="CD66" s="22"/>
-      <c r="CE66" s="22"/>
-      <c r="CF66" s="22"/>
-      <c r="CG66" s="22"/>
-      <c r="CH66" s="22"/>
-      <c r="CI66" s="22"/>
-      <c r="CJ66" s="22"/>
-      <c r="CK66" s="22"/>
-      <c r="CL66" s="22"/>
-      <c r="CM66" s="22"/>
-      <c r="CN66" s="22"/>
-      <c r="CO66" s="22"/>
-      <c r="CP66" s="22"/>
-      <c r="CQ66" s="22"/>
-      <c r="CR66" s="21"/>
-      <c r="CS66" s="21"/>
-      <c r="CT66" s="21"/>
-      <c r="CU66" s="21"/>
+      <c r="BN66" s="31"/>
+      <c r="BO66" s="31"/>
+      <c r="BP66" s="31"/>
+      <c r="BQ66" s="31"/>
+      <c r="BR66" s="31"/>
+      <c r="BS66" s="31"/>
+      <c r="BT66" s="31"/>
+      <c r="BU66" s="31"/>
+      <c r="BV66" s="31"/>
+      <c r="BW66" s="31"/>
+      <c r="BX66" s="31"/>
+      <c r="BY66" s="31"/>
+      <c r="BZ66" s="31"/>
+      <c r="CA66" s="31"/>
+      <c r="CB66" s="31"/>
+      <c r="CC66" s="31"/>
+      <c r="CD66" s="31"/>
+      <c r="CE66" s="31"/>
+      <c r="CF66" s="31"/>
+      <c r="CG66" s="31"/>
+      <c r="CH66" s="31"/>
+      <c r="CI66" s="31"/>
+      <c r="CJ66" s="31"/>
+      <c r="CK66" s="31"/>
+      <c r="CL66" s="31"/>
+      <c r="CM66" s="31"/>
+      <c r="CN66" s="31"/>
+      <c r="CO66" s="31"/>
+      <c r="CP66" s="31"/>
+      <c r="CQ66" s="31"/>
+      <c r="CR66" s="17"/>
+      <c r="CS66" s="17"/>
+      <c r="CT66" s="17"/>
+      <c r="CU66" s="17"/>
     </row>
-    <row r="67" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R67" s="8"/>
       <c r="S67" s="8"/>
       <c r="T67" s="8"/>
@@ -16656,37 +16632,37 @@
       <c r="W67" s="8"/>
       <c r="X67" s="8"/>
       <c r="Y67" s="8"/>
-      <c r="Z67" s="20"/>
-      <c r="AA67" s="20"/>
-      <c r="AB67" s="20"/>
-      <c r="AC67" s="20"/>
-      <c r="AD67" s="20"/>
-      <c r="AE67" s="20"/>
-      <c r="AF67" s="20"/>
-      <c r="AG67" s="20"/>
-      <c r="AH67" s="20"/>
-      <c r="AI67" s="20"/>
-      <c r="AJ67" s="20"/>
-      <c r="AK67" s="20"/>
-      <c r="AL67" s="20"/>
-      <c r="AM67" s="20"/>
-      <c r="AN67" s="20"/>
-      <c r="AO67" s="20"/>
-      <c r="AP67" s="20"/>
-      <c r="AQ67" s="20"/>
-      <c r="AR67" s="20"/>
-      <c r="AS67" s="20"/>
-      <c r="AT67" s="20"/>
-      <c r="AU67" s="20"/>
-      <c r="AV67" s="20"/>
-      <c r="AW67" s="20"/>
-      <c r="AX67" s="20"/>
-      <c r="AY67" s="20"/>
-      <c r="AZ67" s="20"/>
-      <c r="BA67" s="20"/>
-      <c r="BB67" s="20"/>
-      <c r="BC67" s="20"/>
-      <c r="BD67" s="19"/>
+      <c r="Z67" s="39"/>
+      <c r="AA67" s="39"/>
+      <c r="AB67" s="39"/>
+      <c r="AC67" s="39"/>
+      <c r="AD67" s="39"/>
+      <c r="AE67" s="39"/>
+      <c r="AF67" s="39"/>
+      <c r="AG67" s="39"/>
+      <c r="AH67" s="39"/>
+      <c r="AI67" s="39"/>
+      <c r="AJ67" s="39"/>
+      <c r="AK67" s="39"/>
+      <c r="AL67" s="39"/>
+      <c r="AM67" s="39"/>
+      <c r="AN67" s="39"/>
+      <c r="AO67" s="39"/>
+      <c r="AP67" s="39"/>
+      <c r="AQ67" s="39"/>
+      <c r="AR67" s="39"/>
+      <c r="AS67" s="39"/>
+      <c r="AT67" s="39"/>
+      <c r="AU67" s="39"/>
+      <c r="AV67" s="39"/>
+      <c r="AW67" s="39"/>
+      <c r="AX67" s="39"/>
+      <c r="AY67" s="39"/>
+      <c r="AZ67" s="39"/>
+      <c r="BA67" s="39"/>
+      <c r="BB67" s="39"/>
+      <c r="BC67" s="39"/>
+      <c r="BD67" s="16"/>
       <c r="BE67" s="8"/>
       <c r="BF67" s="8"/>
       <c r="BG67" s="8"/>
@@ -16696,42 +16672,42 @@
       <c r="BK67" s="8"/>
       <c r="BL67" s="8"/>
       <c r="BM67" s="8"/>
-      <c r="BN67" s="22"/>
-      <c r="BO67" s="22"/>
-      <c r="BP67" s="22"/>
-      <c r="BQ67" s="22"/>
-      <c r="BR67" s="22"/>
-      <c r="BS67" s="22"/>
-      <c r="BT67" s="22"/>
-      <c r="BU67" s="22"/>
-      <c r="BV67" s="22"/>
-      <c r="BW67" s="22"/>
-      <c r="BX67" s="22"/>
-      <c r="BY67" s="22"/>
-      <c r="BZ67" s="22"/>
-      <c r="CA67" s="22"/>
-      <c r="CB67" s="22"/>
-      <c r="CC67" s="22"/>
-      <c r="CD67" s="22"/>
-      <c r="CE67" s="22"/>
-      <c r="CF67" s="22"/>
-      <c r="CG67" s="22"/>
-      <c r="CH67" s="22"/>
-      <c r="CI67" s="22"/>
-      <c r="CJ67" s="22"/>
-      <c r="CK67" s="22"/>
-      <c r="CL67" s="22"/>
-      <c r="CM67" s="22"/>
-      <c r="CN67" s="22"/>
-      <c r="CO67" s="22"/>
-      <c r="CP67" s="22"/>
-      <c r="CQ67" s="22"/>
-      <c r="CR67" s="21"/>
-      <c r="CS67" s="21"/>
-      <c r="CT67" s="21"/>
-      <c r="CU67" s="21"/>
+      <c r="BN67" s="31"/>
+      <c r="BO67" s="31"/>
+      <c r="BP67" s="31"/>
+      <c r="BQ67" s="31"/>
+      <c r="BR67" s="31"/>
+      <c r="BS67" s="31"/>
+      <c r="BT67" s="31"/>
+      <c r="BU67" s="31"/>
+      <c r="BV67" s="31"/>
+      <c r="BW67" s="31"/>
+      <c r="BX67" s="31"/>
+      <c r="BY67" s="31"/>
+      <c r="BZ67" s="31"/>
+      <c r="CA67" s="31"/>
+      <c r="CB67" s="31"/>
+      <c r="CC67" s="31"/>
+      <c r="CD67" s="31"/>
+      <c r="CE67" s="31"/>
+      <c r="CF67" s="31"/>
+      <c r="CG67" s="31"/>
+      <c r="CH67" s="31"/>
+      <c r="CI67" s="31"/>
+      <c r="CJ67" s="31"/>
+      <c r="CK67" s="31"/>
+      <c r="CL67" s="31"/>
+      <c r="CM67" s="31"/>
+      <c r="CN67" s="31"/>
+      <c r="CO67" s="31"/>
+      <c r="CP67" s="31"/>
+      <c r="CQ67" s="31"/>
+      <c r="CR67" s="17"/>
+      <c r="CS67" s="17"/>
+      <c r="CT67" s="17"/>
+      <c r="CU67" s="17"/>
     </row>
-    <row r="68" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R68" s="8"/>
       <c r="S68" s="8"/>
       <c r="T68" s="8"/>
@@ -16740,37 +16716,37 @@
       <c r="W68" s="8"/>
       <c r="X68" s="8"/>
       <c r="Y68" s="8"/>
-      <c r="Z68" s="20"/>
-      <c r="AA68" s="20"/>
-      <c r="AB68" s="20"/>
-      <c r="AC68" s="20"/>
-      <c r="AD68" s="20"/>
-      <c r="AE68" s="20"/>
-      <c r="AF68" s="20"/>
-      <c r="AG68" s="20"/>
-      <c r="AH68" s="20"/>
-      <c r="AI68" s="20"/>
-      <c r="AJ68" s="20"/>
-      <c r="AK68" s="20"/>
-      <c r="AL68" s="20"/>
-      <c r="AM68" s="20"/>
-      <c r="AN68" s="20"/>
-      <c r="AO68" s="20"/>
-      <c r="AP68" s="20"/>
-      <c r="AQ68" s="20"/>
-      <c r="AR68" s="20"/>
-      <c r="AS68" s="20"/>
-      <c r="AT68" s="20"/>
-      <c r="AU68" s="20"/>
-      <c r="AV68" s="20"/>
-      <c r="AW68" s="20"/>
-      <c r="AX68" s="20"/>
-      <c r="AY68" s="20"/>
-      <c r="AZ68" s="20"/>
-      <c r="BA68" s="20"/>
-      <c r="BB68" s="20"/>
-      <c r="BC68" s="20"/>
-      <c r="BD68" s="19"/>
+      <c r="Z68" s="39"/>
+      <c r="AA68" s="39"/>
+      <c r="AB68" s="39"/>
+      <c r="AC68" s="39"/>
+      <c r="AD68" s="39"/>
+      <c r="AE68" s="39"/>
+      <c r="AF68" s="39"/>
+      <c r="AG68" s="39"/>
+      <c r="AH68" s="39"/>
+      <c r="AI68" s="39"/>
+      <c r="AJ68" s="39"/>
+      <c r="AK68" s="39"/>
+      <c r="AL68" s="39"/>
+      <c r="AM68" s="39"/>
+      <c r="AN68" s="39"/>
+      <c r="AO68" s="39"/>
+      <c r="AP68" s="39"/>
+      <c r="AQ68" s="39"/>
+      <c r="AR68" s="39"/>
+      <c r="AS68" s="39"/>
+      <c r="AT68" s="39"/>
+      <c r="AU68" s="39"/>
+      <c r="AV68" s="39"/>
+      <c r="AW68" s="39"/>
+      <c r="AX68" s="39"/>
+      <c r="AY68" s="39"/>
+      <c r="AZ68" s="39"/>
+      <c r="BA68" s="39"/>
+      <c r="BB68" s="39"/>
+      <c r="BC68" s="39"/>
+      <c r="BD68" s="16"/>
       <c r="BE68" s="8"/>
       <c r="BF68" s="8"/>
       <c r="BG68" s="8"/>
@@ -16780,44 +16756,44 @@
       <c r="BK68" s="8"/>
       <c r="BL68" s="8"/>
       <c r="BM68" s="8"/>
-      <c r="BN68" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="BO68" s="18"/>
-      <c r="BP68" s="18"/>
-      <c r="BQ68" s="18"/>
-      <c r="BR68" s="18"/>
-      <c r="BS68" s="18"/>
-      <c r="BT68" s="18"/>
-      <c r="BU68" s="18"/>
-      <c r="BV68" s="18"/>
-      <c r="BW68" s="18"/>
-      <c r="BX68" s="18"/>
-      <c r="BY68" s="18"/>
-      <c r="BZ68" s="18"/>
-      <c r="CA68" s="18"/>
-      <c r="CB68" s="18"/>
-      <c r="CC68" s="18"/>
-      <c r="CD68" s="18"/>
-      <c r="CE68" s="18"/>
-      <c r="CF68" s="18"/>
-      <c r="CG68" s="18"/>
-      <c r="CH68" s="18"/>
-      <c r="CI68" s="18"/>
-      <c r="CJ68" s="18"/>
-      <c r="CK68" s="18"/>
-      <c r="CL68" s="18"/>
-      <c r="CM68" s="18"/>
-      <c r="CN68" s="18"/>
-      <c r="CO68" s="18"/>
-      <c r="CP68" s="18"/>
-      <c r="CQ68" s="18"/>
-      <c r="CR68" s="17"/>
-      <c r="CS68" s="17"/>
-      <c r="CT68" s="17"/>
-      <c r="CU68" s="17"/>
+      <c r="BN68" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="BO68" s="32"/>
+      <c r="BP68" s="32"/>
+      <c r="BQ68" s="32"/>
+      <c r="BR68" s="32"/>
+      <c r="BS68" s="32"/>
+      <c r="BT68" s="32"/>
+      <c r="BU68" s="32"/>
+      <c r="BV68" s="32"/>
+      <c r="BW68" s="32"/>
+      <c r="BX68" s="32"/>
+      <c r="BY68" s="32"/>
+      <c r="BZ68" s="32"/>
+      <c r="CA68" s="32"/>
+      <c r="CB68" s="32"/>
+      <c r="CC68" s="32"/>
+      <c r="CD68" s="32"/>
+      <c r="CE68" s="32"/>
+      <c r="CF68" s="32"/>
+      <c r="CG68" s="32"/>
+      <c r="CH68" s="32"/>
+      <c r="CI68" s="32"/>
+      <c r="CJ68" s="32"/>
+      <c r="CK68" s="32"/>
+      <c r="CL68" s="32"/>
+      <c r="CM68" s="32"/>
+      <c r="CN68" s="32"/>
+      <c r="CO68" s="32"/>
+      <c r="CP68" s="32"/>
+      <c r="CQ68" s="32"/>
+      <c r="CR68" s="15"/>
+      <c r="CS68" s="15"/>
+      <c r="CT68" s="15"/>
+      <c r="CU68" s="15"/>
     </row>
-    <row r="69" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R69" s="8"/>
       <c r="S69" s="8"/>
       <c r="T69" s="8"/>
@@ -16826,37 +16802,37 @@
       <c r="W69" s="8"/>
       <c r="X69" s="8"/>
       <c r="Y69" s="8"/>
-      <c r="Z69" s="20"/>
-      <c r="AA69" s="20"/>
-      <c r="AB69" s="20"/>
-      <c r="AC69" s="20"/>
-      <c r="AD69" s="20"/>
-      <c r="AE69" s="20"/>
-      <c r="AF69" s="20"/>
-      <c r="AG69" s="20"/>
-      <c r="AH69" s="20"/>
-      <c r="AI69" s="20"/>
-      <c r="AJ69" s="20"/>
-      <c r="AK69" s="20"/>
-      <c r="AL69" s="20"/>
-      <c r="AM69" s="20"/>
-      <c r="AN69" s="20"/>
-      <c r="AO69" s="20"/>
-      <c r="AP69" s="20"/>
-      <c r="AQ69" s="20"/>
-      <c r="AR69" s="20"/>
-      <c r="AS69" s="20"/>
-      <c r="AT69" s="20"/>
-      <c r="AU69" s="20"/>
-      <c r="AV69" s="20"/>
-      <c r="AW69" s="20"/>
-      <c r="AX69" s="20"/>
-      <c r="AY69" s="20"/>
-      <c r="AZ69" s="20"/>
-      <c r="BA69" s="20"/>
-      <c r="BB69" s="20"/>
-      <c r="BC69" s="20"/>
-      <c r="BD69" s="19"/>
+      <c r="Z69" s="39"/>
+      <c r="AA69" s="39"/>
+      <c r="AB69" s="39"/>
+      <c r="AC69" s="39"/>
+      <c r="AD69" s="39"/>
+      <c r="AE69" s="39"/>
+      <c r="AF69" s="39"/>
+      <c r="AG69" s="39"/>
+      <c r="AH69" s="39"/>
+      <c r="AI69" s="39"/>
+      <c r="AJ69" s="39"/>
+      <c r="AK69" s="39"/>
+      <c r="AL69" s="39"/>
+      <c r="AM69" s="39"/>
+      <c r="AN69" s="39"/>
+      <c r="AO69" s="39"/>
+      <c r="AP69" s="39"/>
+      <c r="AQ69" s="39"/>
+      <c r="AR69" s="39"/>
+      <c r="AS69" s="39"/>
+      <c r="AT69" s="39"/>
+      <c r="AU69" s="39"/>
+      <c r="AV69" s="39"/>
+      <c r="AW69" s="39"/>
+      <c r="AX69" s="39"/>
+      <c r="AY69" s="39"/>
+      <c r="AZ69" s="39"/>
+      <c r="BA69" s="39"/>
+      <c r="BB69" s="39"/>
+      <c r="BC69" s="39"/>
+      <c r="BD69" s="16"/>
       <c r="BE69" s="8"/>
       <c r="BF69" s="8"/>
       <c r="BG69" s="8"/>
@@ -16866,42 +16842,42 @@
       <c r="BK69" s="8"/>
       <c r="BL69" s="8"/>
       <c r="BM69" s="8"/>
-      <c r="BN69" s="18"/>
-      <c r="BO69" s="18"/>
-      <c r="BP69" s="18"/>
-      <c r="BQ69" s="18"/>
-      <c r="BR69" s="18"/>
-      <c r="BS69" s="18"/>
-      <c r="BT69" s="18"/>
-      <c r="BU69" s="18"/>
-      <c r="BV69" s="18"/>
-      <c r="BW69" s="18"/>
-      <c r="BX69" s="18"/>
-      <c r="BY69" s="18"/>
-      <c r="BZ69" s="18"/>
-      <c r="CA69" s="18"/>
-      <c r="CB69" s="18"/>
-      <c r="CC69" s="18"/>
-      <c r="CD69" s="18"/>
-      <c r="CE69" s="18"/>
-      <c r="CF69" s="18"/>
-      <c r="CG69" s="18"/>
-      <c r="CH69" s="18"/>
-      <c r="CI69" s="18"/>
-      <c r="CJ69" s="18"/>
-      <c r="CK69" s="18"/>
-      <c r="CL69" s="18"/>
-      <c r="CM69" s="18"/>
-      <c r="CN69" s="18"/>
-      <c r="CO69" s="18"/>
-      <c r="CP69" s="18"/>
-      <c r="CQ69" s="18"/>
-      <c r="CR69" s="17"/>
-      <c r="CS69" s="17"/>
-      <c r="CT69" s="17"/>
-      <c r="CU69" s="17"/>
+      <c r="BN69" s="32"/>
+      <c r="BO69" s="32"/>
+      <c r="BP69" s="32"/>
+      <c r="BQ69" s="32"/>
+      <c r="BR69" s="32"/>
+      <c r="BS69" s="32"/>
+      <c r="BT69" s="32"/>
+      <c r="BU69" s="32"/>
+      <c r="BV69" s="32"/>
+      <c r="BW69" s="32"/>
+      <c r="BX69" s="32"/>
+      <c r="BY69" s="32"/>
+      <c r="BZ69" s="32"/>
+      <c r="CA69" s="32"/>
+      <c r="CB69" s="32"/>
+      <c r="CC69" s="32"/>
+      <c r="CD69" s="32"/>
+      <c r="CE69" s="32"/>
+      <c r="CF69" s="32"/>
+      <c r="CG69" s="32"/>
+      <c r="CH69" s="32"/>
+      <c r="CI69" s="32"/>
+      <c r="CJ69" s="32"/>
+      <c r="CK69" s="32"/>
+      <c r="CL69" s="32"/>
+      <c r="CM69" s="32"/>
+      <c r="CN69" s="32"/>
+      <c r="CO69" s="32"/>
+      <c r="CP69" s="32"/>
+      <c r="CQ69" s="32"/>
+      <c r="CR69" s="15"/>
+      <c r="CS69" s="15"/>
+      <c r="CT69" s="15"/>
+      <c r="CU69" s="15"/>
     </row>
-    <row r="70" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R70" s="8"/>
       <c r="S70" s="8"/>
       <c r="T70" s="8"/>
@@ -16985,7 +16961,7 @@
       <c r="CT70" s="8"/>
       <c r="CU70" s="8"/>
     </row>
-    <row r="71" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R71" s="8"/>
       <c r="S71" s="8"/>
       <c r="T71" s="8"/>
@@ -16994,39 +16970,39 @@
       <c r="W71" s="8"/>
       <c r="X71" s="8"/>
       <c r="Y71" s="8"/>
-      <c r="Z71" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA71" s="16"/>
-      <c r="AB71" s="16"/>
-      <c r="AC71" s="16"/>
-      <c r="AD71" s="16"/>
-      <c r="AE71" s="16"/>
-      <c r="AF71" s="16"/>
-      <c r="AG71" s="16"/>
-      <c r="AH71" s="16"/>
-      <c r="AI71" s="16"/>
-      <c r="AJ71" s="16"/>
-      <c r="AK71" s="16"/>
-      <c r="AL71" s="16"/>
-      <c r="AM71" s="16"/>
-      <c r="AN71" s="16"/>
-      <c r="AO71" s="16"/>
-      <c r="AP71" s="16"/>
-      <c r="AQ71" s="16"/>
-      <c r="AR71" s="16"/>
-      <c r="AS71" s="16"/>
-      <c r="AT71" s="16"/>
-      <c r="AU71" s="16"/>
-      <c r="AV71" s="16"/>
-      <c r="AW71" s="16"/>
-      <c r="AX71" s="16"/>
-      <c r="AY71" s="16"/>
-      <c r="AZ71" s="16"/>
-      <c r="BA71" s="16"/>
-      <c r="BB71" s="16"/>
-      <c r="BC71" s="16"/>
-      <c r="BD71" s="15"/>
+      <c r="Z71" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA71" s="34"/>
+      <c r="AB71" s="34"/>
+      <c r="AC71" s="34"/>
+      <c r="AD71" s="34"/>
+      <c r="AE71" s="34"/>
+      <c r="AF71" s="34"/>
+      <c r="AG71" s="34"/>
+      <c r="AH71" s="34"/>
+      <c r="AI71" s="34"/>
+      <c r="AJ71" s="34"/>
+      <c r="AK71" s="34"/>
+      <c r="AL71" s="34"/>
+      <c r="AM71" s="34"/>
+      <c r="AN71" s="34"/>
+      <c r="AO71" s="34"/>
+      <c r="AP71" s="34"/>
+      <c r="AQ71" s="34"/>
+      <c r="AR71" s="34"/>
+      <c r="AS71" s="34"/>
+      <c r="AT71" s="34"/>
+      <c r="AU71" s="34"/>
+      <c r="AV71" s="34"/>
+      <c r="AW71" s="34"/>
+      <c r="AX71" s="34"/>
+      <c r="AY71" s="34"/>
+      <c r="AZ71" s="34"/>
+      <c r="BA71" s="34"/>
+      <c r="BB71" s="34"/>
+      <c r="BC71" s="34"/>
+      <c r="BD71" s="13"/>
       <c r="BE71" s="8"/>
       <c r="BF71" s="8"/>
       <c r="BG71" s="8"/>
@@ -17071,7 +17047,7 @@
       <c r="CT71" s="8"/>
       <c r="CU71" s="8"/>
     </row>
-    <row r="72" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R72" s="8"/>
       <c r="S72" s="8"/>
       <c r="T72" s="8"/>
@@ -17080,37 +17056,37 @@
       <c r="W72" s="8"/>
       <c r="X72" s="8"/>
       <c r="Y72" s="8"/>
-      <c r="Z72" s="16"/>
-      <c r="AA72" s="16"/>
-      <c r="AB72" s="16"/>
-      <c r="AC72" s="16"/>
-      <c r="AD72" s="16"/>
-      <c r="AE72" s="16"/>
-      <c r="AF72" s="16"/>
-      <c r="AG72" s="16"/>
-      <c r="AH72" s="16"/>
-      <c r="AI72" s="16"/>
-      <c r="AJ72" s="16"/>
-      <c r="AK72" s="16"/>
-      <c r="AL72" s="16"/>
-      <c r="AM72" s="16"/>
-      <c r="AN72" s="16"/>
-      <c r="AO72" s="16"/>
-      <c r="AP72" s="16"/>
-      <c r="AQ72" s="16"/>
-      <c r="AR72" s="16"/>
-      <c r="AS72" s="16"/>
-      <c r="AT72" s="16"/>
-      <c r="AU72" s="16"/>
-      <c r="AV72" s="16"/>
-      <c r="AW72" s="16"/>
-      <c r="AX72" s="16"/>
-      <c r="AY72" s="16"/>
-      <c r="AZ72" s="16"/>
-      <c r="BA72" s="16"/>
-      <c r="BB72" s="16"/>
-      <c r="BC72" s="16"/>
-      <c r="BD72" s="15"/>
+      <c r="Z72" s="34"/>
+      <c r="AA72" s="34"/>
+      <c r="AB72" s="34"/>
+      <c r="AC72" s="34"/>
+      <c r="AD72" s="34"/>
+      <c r="AE72" s="34"/>
+      <c r="AF72" s="34"/>
+      <c r="AG72" s="34"/>
+      <c r="AH72" s="34"/>
+      <c r="AI72" s="34"/>
+      <c r="AJ72" s="34"/>
+      <c r="AK72" s="34"/>
+      <c r="AL72" s="34"/>
+      <c r="AM72" s="34"/>
+      <c r="AN72" s="34"/>
+      <c r="AO72" s="34"/>
+      <c r="AP72" s="34"/>
+      <c r="AQ72" s="34"/>
+      <c r="AR72" s="34"/>
+      <c r="AS72" s="34"/>
+      <c r="AT72" s="34"/>
+      <c r="AU72" s="34"/>
+      <c r="AV72" s="34"/>
+      <c r="AW72" s="34"/>
+      <c r="AX72" s="34"/>
+      <c r="AY72" s="34"/>
+      <c r="AZ72" s="34"/>
+      <c r="BA72" s="34"/>
+      <c r="BB72" s="34"/>
+      <c r="BC72" s="34"/>
+      <c r="BD72" s="13"/>
       <c r="BE72" s="8"/>
       <c r="BF72" s="8"/>
       <c r="BG72" s="8"/>
@@ -17155,7 +17131,7 @@
       <c r="CT72" s="8"/>
       <c r="CU72" s="8"/>
     </row>
-    <row r="73" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R73" s="8"/>
       <c r="S73" s="8"/>
       <c r="T73" s="8"/>
@@ -17239,7 +17215,7 @@
       <c r="CT73" s="8"/>
       <c r="CU73" s="8"/>
     </row>
-    <row r="74" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R74" s="8"/>
       <c r="S74" s="8"/>
       <c r="T74" s="8"/>
@@ -17248,37 +17224,37 @@
       <c r="W74" s="8"/>
       <c r="X74" s="8"/>
       <c r="Y74" s="8"/>
-      <c r="Z74" s="14"/>
-      <c r="AA74" s="14"/>
-      <c r="AB74" s="14"/>
-      <c r="AC74" s="14"/>
-      <c r="AD74" s="14"/>
-      <c r="AE74" s="14"/>
-      <c r="AF74" s="14"/>
-      <c r="AG74" s="14"/>
-      <c r="AH74" s="14"/>
-      <c r="AI74" s="14"/>
-      <c r="AJ74" s="14"/>
-      <c r="AK74" s="14"/>
-      <c r="AL74" s="14"/>
-      <c r="AM74" s="14"/>
-      <c r="AN74" s="14"/>
-      <c r="AO74" s="14"/>
-      <c r="AP74" s="14"/>
-      <c r="AQ74" s="14"/>
-      <c r="AR74" s="14"/>
-      <c r="AS74" s="14"/>
-      <c r="AT74" s="14"/>
-      <c r="AU74" s="14"/>
-      <c r="AV74" s="14"/>
-      <c r="AW74" s="14"/>
-      <c r="AX74" s="14"/>
-      <c r="AY74" s="14"/>
-      <c r="AZ74" s="14"/>
-      <c r="BA74" s="14"/>
-      <c r="BB74" s="14"/>
-      <c r="BC74" s="14"/>
-      <c r="BD74" s="14"/>
+      <c r="Z74" s="12"/>
+      <c r="AA74" s="12"/>
+      <c r="AB74" s="12"/>
+      <c r="AC74" s="12"/>
+      <c r="AD74" s="12"/>
+      <c r="AE74" s="12"/>
+      <c r="AF74" s="12"/>
+      <c r="AG74" s="12"/>
+      <c r="AH74" s="12"/>
+      <c r="AI74" s="12"/>
+      <c r="AJ74" s="12"/>
+      <c r="AK74" s="12"/>
+      <c r="AL74" s="12"/>
+      <c r="AM74" s="12"/>
+      <c r="AN74" s="12"/>
+      <c r="AO74" s="12"/>
+      <c r="AP74" s="12"/>
+      <c r="AQ74" s="12"/>
+      <c r="AR74" s="12"/>
+      <c r="AS74" s="12"/>
+      <c r="AT74" s="12"/>
+      <c r="AU74" s="12"/>
+      <c r="AV74" s="12"/>
+      <c r="AW74" s="12"/>
+      <c r="AX74" s="12"/>
+      <c r="AY74" s="12"/>
+      <c r="AZ74" s="12"/>
+      <c r="BA74" s="12"/>
+      <c r="BB74" s="12"/>
+      <c r="BC74" s="12"/>
+      <c r="BD74" s="12"/>
       <c r="BE74" s="8"/>
       <c r="BF74" s="8"/>
       <c r="BG74" s="8"/>
@@ -17323,7 +17299,7 @@
       <c r="CT74" s="8"/>
       <c r="CU74" s="8"/>
     </row>
-    <row r="75" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R75" s="8"/>
       <c r="S75" s="8"/>
       <c r="T75" s="8"/>
@@ -17332,37 +17308,37 @@
       <c r="W75" s="8"/>
       <c r="X75" s="8"/>
       <c r="Y75" s="8"/>
-      <c r="Z75" s="14"/>
-      <c r="AA75" s="14"/>
-      <c r="AB75" s="14"/>
-      <c r="AC75" s="14"/>
-      <c r="AD75" s="14"/>
-      <c r="AE75" s="14"/>
-      <c r="AF75" s="14"/>
-      <c r="AG75" s="14"/>
-      <c r="AH75" s="14"/>
-      <c r="AI75" s="14"/>
-      <c r="AJ75" s="14"/>
-      <c r="AK75" s="14"/>
-      <c r="AL75" s="14"/>
-      <c r="AM75" s="14"/>
-      <c r="AN75" s="14"/>
-      <c r="AO75" s="14"/>
-      <c r="AP75" s="14"/>
-      <c r="AQ75" s="14"/>
-      <c r="AR75" s="14"/>
-      <c r="AS75" s="14"/>
-      <c r="AT75" s="14"/>
-      <c r="AU75" s="14"/>
-      <c r="AV75" s="14"/>
-      <c r="AW75" s="14"/>
-      <c r="AX75" s="14"/>
-      <c r="AY75" s="14"/>
-      <c r="AZ75" s="14"/>
-      <c r="BA75" s="14"/>
-      <c r="BB75" s="14"/>
-      <c r="BC75" s="14"/>
-      <c r="BD75" s="14"/>
+      <c r="Z75" s="12"/>
+      <c r="AA75" s="12"/>
+      <c r="AB75" s="12"/>
+      <c r="AC75" s="12"/>
+      <c r="AD75" s="12"/>
+      <c r="AE75" s="12"/>
+      <c r="AF75" s="12"/>
+      <c r="AG75" s="12"/>
+      <c r="AH75" s="12"/>
+      <c r="AI75" s="12"/>
+      <c r="AJ75" s="12"/>
+      <c r="AK75" s="12"/>
+      <c r="AL75" s="12"/>
+      <c r="AM75" s="12"/>
+      <c r="AN75" s="12"/>
+      <c r="AO75" s="12"/>
+      <c r="AP75" s="12"/>
+      <c r="AQ75" s="12"/>
+      <c r="AR75" s="12"/>
+      <c r="AS75" s="12"/>
+      <c r="AT75" s="12"/>
+      <c r="AU75" s="12"/>
+      <c r="AV75" s="12"/>
+      <c r="AW75" s="12"/>
+      <c r="AX75" s="12"/>
+      <c r="AY75" s="12"/>
+      <c r="AZ75" s="12"/>
+      <c r="BA75" s="12"/>
+      <c r="BB75" s="12"/>
+      <c r="BC75" s="12"/>
+      <c r="BD75" s="12"/>
       <c r="BE75" s="8"/>
       <c r="BF75" s="8"/>
       <c r="BG75" s="8"/>
@@ -17407,7 +17383,7 @@
       <c r="CT75" s="8"/>
       <c r="CU75" s="8"/>
     </row>
-    <row r="76" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R76" s="8"/>
       <c r="S76" s="8"/>
       <c r="T76" s="8"/>
@@ -17416,37 +17392,37 @@
       <c r="W76" s="8"/>
       <c r="X76" s="8"/>
       <c r="Y76" s="8"/>
-      <c r="Z76" s="14"/>
-      <c r="AA76" s="14"/>
-      <c r="AB76" s="14"/>
-      <c r="AC76" s="14"/>
-      <c r="AD76" s="14"/>
-      <c r="AE76" s="14"/>
-      <c r="AF76" s="14"/>
-      <c r="AG76" s="14"/>
-      <c r="AH76" s="14"/>
-      <c r="AI76" s="14"/>
-      <c r="AJ76" s="14"/>
-      <c r="AK76" s="14"/>
-      <c r="AL76" s="14"/>
-      <c r="AM76" s="14"/>
-      <c r="AN76" s="14"/>
-      <c r="AO76" s="14"/>
-      <c r="AP76" s="14"/>
-      <c r="AQ76" s="14"/>
-      <c r="AR76" s="14"/>
-      <c r="AS76" s="14"/>
-      <c r="AT76" s="14"/>
-      <c r="AU76" s="14"/>
-      <c r="AV76" s="14"/>
-      <c r="AW76" s="14"/>
-      <c r="AX76" s="14"/>
-      <c r="AY76" s="14"/>
-      <c r="AZ76" s="14"/>
-      <c r="BA76" s="14"/>
-      <c r="BB76" s="14"/>
-      <c r="BC76" s="14"/>
-      <c r="BD76" s="14"/>
+      <c r="Z76" s="12"/>
+      <c r="AA76" s="12"/>
+      <c r="AB76" s="12"/>
+      <c r="AC76" s="12"/>
+      <c r="AD76" s="12"/>
+      <c r="AE76" s="12"/>
+      <c r="AF76" s="12"/>
+      <c r="AG76" s="12"/>
+      <c r="AH76" s="12"/>
+      <c r="AI76" s="12"/>
+      <c r="AJ76" s="12"/>
+      <c r="AK76" s="12"/>
+      <c r="AL76" s="12"/>
+      <c r="AM76" s="12"/>
+      <c r="AN76" s="12"/>
+      <c r="AO76" s="12"/>
+      <c r="AP76" s="12"/>
+      <c r="AQ76" s="12"/>
+      <c r="AR76" s="12"/>
+      <c r="AS76" s="12"/>
+      <c r="AT76" s="12"/>
+      <c r="AU76" s="12"/>
+      <c r="AV76" s="12"/>
+      <c r="AW76" s="12"/>
+      <c r="AX76" s="12"/>
+      <c r="AY76" s="12"/>
+      <c r="AZ76" s="12"/>
+      <c r="BA76" s="12"/>
+      <c r="BB76" s="12"/>
+      <c r="BC76" s="12"/>
+      <c r="BD76" s="12"/>
       <c r="BE76" s="8"/>
       <c r="BF76" s="8"/>
       <c r="BG76" s="8"/>
@@ -17491,7 +17467,7 @@
       <c r="CT76" s="8"/>
       <c r="CU76" s="8"/>
     </row>
-    <row r="77" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R77" s="8"/>
       <c r="S77" s="8"/>
       <c r="T77" s="8"/>
@@ -17500,39 +17476,39 @@
       <c r="W77" s="8"/>
       <c r="X77" s="8"/>
       <c r="Y77" s="8"/>
-      <c r="Z77" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA77" s="13"/>
-      <c r="AB77" s="13"/>
-      <c r="AC77" s="13"/>
-      <c r="AD77" s="13"/>
-      <c r="AE77" s="13"/>
-      <c r="AF77" s="13"/>
-      <c r="AG77" s="13"/>
-      <c r="AH77" s="13"/>
-      <c r="AI77" s="13"/>
-      <c r="AJ77" s="13"/>
-      <c r="AK77" s="13"/>
-      <c r="AL77" s="13"/>
-      <c r="AM77" s="13"/>
-      <c r="AN77" s="13"/>
-      <c r="AO77" s="13"/>
-      <c r="AP77" s="13"/>
-      <c r="AQ77" s="13"/>
-      <c r="AR77" s="13"/>
-      <c r="AS77" s="13"/>
-      <c r="AT77" s="13"/>
-      <c r="AU77" s="13"/>
-      <c r="AV77" s="13"/>
-      <c r="AW77" s="13"/>
-      <c r="AX77" s="13"/>
-      <c r="AY77" s="13"/>
-      <c r="AZ77" s="13"/>
-      <c r="BA77" s="13"/>
-      <c r="BB77" s="13"/>
-      <c r="BC77" s="13"/>
-      <c r="BD77" s="12"/>
+      <c r="Z77" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA77" s="44"/>
+      <c r="AB77" s="44"/>
+      <c r="AC77" s="44"/>
+      <c r="AD77" s="44"/>
+      <c r="AE77" s="44"/>
+      <c r="AF77" s="44"/>
+      <c r="AG77" s="44"/>
+      <c r="AH77" s="44"/>
+      <c r="AI77" s="44"/>
+      <c r="AJ77" s="44"/>
+      <c r="AK77" s="44"/>
+      <c r="AL77" s="44"/>
+      <c r="AM77" s="44"/>
+      <c r="AN77" s="44"/>
+      <c r="AO77" s="44"/>
+      <c r="AP77" s="44"/>
+      <c r="AQ77" s="44"/>
+      <c r="AR77" s="44"/>
+      <c r="AS77" s="44"/>
+      <c r="AT77" s="44"/>
+      <c r="AU77" s="44"/>
+      <c r="AV77" s="44"/>
+      <c r="AW77" s="44"/>
+      <c r="AX77" s="44"/>
+      <c r="AY77" s="44"/>
+      <c r="AZ77" s="44"/>
+      <c r="BA77" s="44"/>
+      <c r="BB77" s="44"/>
+      <c r="BC77" s="44"/>
+      <c r="BD77" s="11"/>
       <c r="BE77" s="8"/>
       <c r="BF77" s="8"/>
       <c r="BG77" s="8"/>
@@ -17577,7 +17553,7 @@
       <c r="CT77" s="8"/>
       <c r="CU77" s="8"/>
     </row>
-    <row r="78" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R78" s="8"/>
       <c r="S78" s="8"/>
       <c r="T78" s="8"/>
@@ -17586,37 +17562,37 @@
       <c r="W78" s="8"/>
       <c r="X78" s="8"/>
       <c r="Y78" s="8"/>
-      <c r="Z78" s="13"/>
-      <c r="AA78" s="13"/>
-      <c r="AB78" s="13"/>
-      <c r="AC78" s="13"/>
-      <c r="AD78" s="13"/>
-      <c r="AE78" s="13"/>
-      <c r="AF78" s="13"/>
-      <c r="AG78" s="13"/>
-      <c r="AH78" s="13"/>
-      <c r="AI78" s="13"/>
-      <c r="AJ78" s="13"/>
-      <c r="AK78" s="13"/>
-      <c r="AL78" s="13"/>
-      <c r="AM78" s="13"/>
-      <c r="AN78" s="13"/>
-      <c r="AO78" s="13"/>
-      <c r="AP78" s="13"/>
-      <c r="AQ78" s="13"/>
-      <c r="AR78" s="13"/>
-      <c r="AS78" s="13"/>
-      <c r="AT78" s="13"/>
-      <c r="AU78" s="13"/>
-      <c r="AV78" s="13"/>
-      <c r="AW78" s="13"/>
-      <c r="AX78" s="13"/>
-      <c r="AY78" s="13"/>
-      <c r="AZ78" s="13"/>
-      <c r="BA78" s="13"/>
-      <c r="BB78" s="13"/>
-      <c r="BC78" s="13"/>
-      <c r="BD78" s="12"/>
+      <c r="Z78" s="44"/>
+      <c r="AA78" s="44"/>
+      <c r="AB78" s="44"/>
+      <c r="AC78" s="44"/>
+      <c r="AD78" s="44"/>
+      <c r="AE78" s="44"/>
+      <c r="AF78" s="44"/>
+      <c r="AG78" s="44"/>
+      <c r="AH78" s="44"/>
+      <c r="AI78" s="44"/>
+      <c r="AJ78" s="44"/>
+      <c r="AK78" s="44"/>
+      <c r="AL78" s="44"/>
+      <c r="AM78" s="44"/>
+      <c r="AN78" s="44"/>
+      <c r="AO78" s="44"/>
+      <c r="AP78" s="44"/>
+      <c r="AQ78" s="44"/>
+      <c r="AR78" s="44"/>
+      <c r="AS78" s="44"/>
+      <c r="AT78" s="44"/>
+      <c r="AU78" s="44"/>
+      <c r="AV78" s="44"/>
+      <c r="AW78" s="44"/>
+      <c r="AX78" s="44"/>
+      <c r="AY78" s="44"/>
+      <c r="AZ78" s="44"/>
+      <c r="BA78" s="44"/>
+      <c r="BB78" s="44"/>
+      <c r="BC78" s="44"/>
+      <c r="BD78" s="11"/>
       <c r="BE78" s="8"/>
       <c r="BF78" s="8"/>
       <c r="BG78" s="8"/>
@@ -17661,7 +17637,7 @@
       <c r="CT78" s="8"/>
       <c r="CU78" s="8"/>
     </row>
-    <row r="79" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R79" s="8"/>
       <c r="S79" s="8"/>
       <c r="T79" s="8"/>
@@ -17670,37 +17646,37 @@
       <c r="W79" s="8"/>
       <c r="X79" s="8"/>
       <c r="Y79" s="8"/>
-      <c r="Z79" s="13"/>
-      <c r="AA79" s="13"/>
-      <c r="AB79" s="13"/>
-      <c r="AC79" s="13"/>
-      <c r="AD79" s="13"/>
-      <c r="AE79" s="13"/>
-      <c r="AF79" s="13"/>
-      <c r="AG79" s="13"/>
-      <c r="AH79" s="13"/>
-      <c r="AI79" s="13"/>
-      <c r="AJ79" s="13"/>
-      <c r="AK79" s="13"/>
-      <c r="AL79" s="13"/>
-      <c r="AM79" s="13"/>
-      <c r="AN79" s="13"/>
-      <c r="AO79" s="13"/>
-      <c r="AP79" s="13"/>
-      <c r="AQ79" s="13"/>
-      <c r="AR79" s="13"/>
-      <c r="AS79" s="13"/>
-      <c r="AT79" s="13"/>
-      <c r="AU79" s="13"/>
-      <c r="AV79" s="13"/>
-      <c r="AW79" s="13"/>
-      <c r="AX79" s="13"/>
-      <c r="AY79" s="13"/>
-      <c r="AZ79" s="13"/>
-      <c r="BA79" s="13"/>
-      <c r="BB79" s="13"/>
-      <c r="BC79" s="13"/>
-      <c r="BD79" s="12"/>
+      <c r="Z79" s="44"/>
+      <c r="AA79" s="44"/>
+      <c r="AB79" s="44"/>
+      <c r="AC79" s="44"/>
+      <c r="AD79" s="44"/>
+      <c r="AE79" s="44"/>
+      <c r="AF79" s="44"/>
+      <c r="AG79" s="44"/>
+      <c r="AH79" s="44"/>
+      <c r="AI79" s="44"/>
+      <c r="AJ79" s="44"/>
+      <c r="AK79" s="44"/>
+      <c r="AL79" s="44"/>
+      <c r="AM79" s="44"/>
+      <c r="AN79" s="44"/>
+      <c r="AO79" s="44"/>
+      <c r="AP79" s="44"/>
+      <c r="AQ79" s="44"/>
+      <c r="AR79" s="44"/>
+      <c r="AS79" s="44"/>
+      <c r="AT79" s="44"/>
+      <c r="AU79" s="44"/>
+      <c r="AV79" s="44"/>
+      <c r="AW79" s="44"/>
+      <c r="AX79" s="44"/>
+      <c r="AY79" s="44"/>
+      <c r="AZ79" s="44"/>
+      <c r="BA79" s="44"/>
+      <c r="BB79" s="44"/>
+      <c r="BC79" s="44"/>
+      <c r="BD79" s="11"/>
       <c r="BE79" s="8"/>
       <c r="BF79" s="8"/>
       <c r="BG79" s="8"/>
@@ -17745,7 +17721,7 @@
       <c r="CT79" s="8"/>
       <c r="CU79" s="8"/>
     </row>
-    <row r="80" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="18:99" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R80" s="8"/>
       <c r="S80" s="8"/>
       <c r="T80" s="8"/>
@@ -17754,37 +17730,37 @@
       <c r="W80" s="8"/>
       <c r="X80" s="8"/>
       <c r="Y80" s="8"/>
-      <c r="Z80" s="13"/>
-      <c r="AA80" s="13"/>
-      <c r="AB80" s="13"/>
-      <c r="AC80" s="13"/>
-      <c r="AD80" s="13"/>
-      <c r="AE80" s="13"/>
-      <c r="AF80" s="13"/>
-      <c r="AG80" s="13"/>
-      <c r="AH80" s="13"/>
-      <c r="AI80" s="13"/>
-      <c r="AJ80" s="13"/>
-      <c r="AK80" s="13"/>
-      <c r="AL80" s="13"/>
-      <c r="AM80" s="13"/>
-      <c r="AN80" s="13"/>
-      <c r="AO80" s="13"/>
-      <c r="AP80" s="13"/>
-      <c r="AQ80" s="13"/>
-      <c r="AR80" s="13"/>
-      <c r="AS80" s="13"/>
-      <c r="AT80" s="13"/>
-      <c r="AU80" s="13"/>
-      <c r="AV80" s="13"/>
-      <c r="AW80" s="13"/>
-      <c r="AX80" s="13"/>
-      <c r="AY80" s="13"/>
-      <c r="AZ80" s="13"/>
-      <c r="BA80" s="13"/>
-      <c r="BB80" s="13"/>
-      <c r="BC80" s="13"/>
-      <c r="BD80" s="12"/>
+      <c r="Z80" s="44"/>
+      <c r="AA80" s="44"/>
+      <c r="AB80" s="44"/>
+      <c r="AC80" s="44"/>
+      <c r="AD80" s="44"/>
+      <c r="AE80" s="44"/>
+      <c r="AF80" s="44"/>
+      <c r="AG80" s="44"/>
+      <c r="AH80" s="44"/>
+      <c r="AI80" s="44"/>
+      <c r="AJ80" s="44"/>
+      <c r="AK80" s="44"/>
+      <c r="AL80" s="44"/>
+      <c r="AM80" s="44"/>
+      <c r="AN80" s="44"/>
+      <c r="AO80" s="44"/>
+      <c r="AP80" s="44"/>
+      <c r="AQ80" s="44"/>
+      <c r="AR80" s="44"/>
+      <c r="AS80" s="44"/>
+      <c r="AT80" s="44"/>
+      <c r="AU80" s="44"/>
+      <c r="AV80" s="44"/>
+      <c r="AW80" s="44"/>
+      <c r="AX80" s="44"/>
+      <c r="AY80" s="44"/>
+      <c r="AZ80" s="44"/>
+      <c r="BA80" s="44"/>
+      <c r="BB80" s="44"/>
+      <c r="BC80" s="44"/>
+      <c r="BD80" s="11"/>
       <c r="BE80" s="8"/>
       <c r="BF80" s="8"/>
       <c r="BG80" s="8"/>
@@ -17829,396 +17805,374 @@
       <c r="CT80" s="8"/>
       <c r="CU80" s="8"/>
     </row>
-    <row r="81" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z81" s="13"/>
-      <c r="AA81" s="13"/>
-      <c r="AB81" s="13"/>
-      <c r="AC81" s="13"/>
-      <c r="AD81" s="13"/>
-      <c r="AE81" s="13"/>
-      <c r="AF81" s="13"/>
-      <c r="AG81" s="13"/>
-      <c r="AH81" s="13"/>
-      <c r="AI81" s="13"/>
-      <c r="AJ81" s="13"/>
-      <c r="AK81" s="13"/>
-      <c r="AL81" s="13"/>
-      <c r="AM81" s="13"/>
-      <c r="AN81" s="13"/>
-      <c r="AO81" s="13"/>
-      <c r="AP81" s="13"/>
-      <c r="AQ81" s="13"/>
-      <c r="AR81" s="13"/>
-      <c r="AS81" s="13"/>
-      <c r="AT81" s="13"/>
-      <c r="AU81" s="13"/>
-      <c r="AV81" s="13"/>
-      <c r="AW81" s="13"/>
-      <c r="AX81" s="13"/>
-      <c r="AY81" s="13"/>
-      <c r="AZ81" s="13"/>
-      <c r="BA81" s="13"/>
-      <c r="BB81" s="13"/>
-      <c r="BC81" s="13"/>
-      <c r="BD81" s="12"/>
-      <c r="CV81"/>
-      <c r="CW81"/>
+    <row r="81" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z81" s="44"/>
+      <c r="AA81" s="44"/>
+      <c r="AB81" s="44"/>
+      <c r="AC81" s="44"/>
+      <c r="AD81" s="44"/>
+      <c r="AE81" s="44"/>
+      <c r="AF81" s="44"/>
+      <c r="AG81" s="44"/>
+      <c r="AH81" s="44"/>
+      <c r="AI81" s="44"/>
+      <c r="AJ81" s="44"/>
+      <c r="AK81" s="44"/>
+      <c r="AL81" s="44"/>
+      <c r="AM81" s="44"/>
+      <c r="AN81" s="44"/>
+      <c r="AO81" s="44"/>
+      <c r="AP81" s="44"/>
+      <c r="AQ81" s="44"/>
+      <c r="AR81" s="44"/>
+      <c r="AS81" s="44"/>
+      <c r="AT81" s="44"/>
+      <c r="AU81" s="44"/>
+      <c r="AV81" s="44"/>
+      <c r="AW81" s="44"/>
+      <c r="AX81" s="44"/>
+      <c r="AY81" s="44"/>
+      <c r="AZ81" s="44"/>
+      <c r="BA81" s="44"/>
+      <c r="BB81" s="44"/>
+      <c r="BC81" s="44"/>
+      <c r="BD81" s="11"/>
     </row>
-    <row r="82" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z82" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA82" s="13"/>
-      <c r="AB82" s="13"/>
-      <c r="AC82" s="13"/>
-      <c r="AD82" s="13"/>
-      <c r="AE82" s="13"/>
-      <c r="AF82" s="13"/>
-      <c r="AG82" s="13"/>
-      <c r="AH82" s="13"/>
-      <c r="AI82" s="13"/>
-      <c r="AJ82" s="13"/>
-      <c r="AK82" s="13"/>
-      <c r="AL82" s="13"/>
-      <c r="AM82" s="13"/>
-      <c r="AN82" s="13"/>
-      <c r="AO82" s="13"/>
-      <c r="AP82" s="13"/>
-      <c r="AQ82" s="13"/>
-      <c r="AR82" s="13"/>
-      <c r="AS82" s="13"/>
-      <c r="AT82" s="13"/>
-      <c r="AU82" s="13"/>
-      <c r="AV82" s="13"/>
-      <c r="AW82" s="13"/>
-      <c r="AX82" s="13"/>
-      <c r="AY82" s="13"/>
-      <c r="AZ82" s="13"/>
-      <c r="BA82" s="13"/>
-      <c r="BB82" s="13"/>
-      <c r="BC82" s="13"/>
-      <c r="BD82" s="12"/>
-      <c r="CV82"/>
-      <c r="CW82"/>
+    <row r="82" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z82" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA82" s="44"/>
+      <c r="AB82" s="44"/>
+      <c r="AC82" s="44"/>
+      <c r="AD82" s="44"/>
+      <c r="AE82" s="44"/>
+      <c r="AF82" s="44"/>
+      <c r="AG82" s="44"/>
+      <c r="AH82" s="44"/>
+      <c r="AI82" s="44"/>
+      <c r="AJ82" s="44"/>
+      <c r="AK82" s="44"/>
+      <c r="AL82" s="44"/>
+      <c r="AM82" s="44"/>
+      <c r="AN82" s="44"/>
+      <c r="AO82" s="44"/>
+      <c r="AP82" s="44"/>
+      <c r="AQ82" s="44"/>
+      <c r="AR82" s="44"/>
+      <c r="AS82" s="44"/>
+      <c r="AT82" s="44"/>
+      <c r="AU82" s="44"/>
+      <c r="AV82" s="44"/>
+      <c r="AW82" s="44"/>
+      <c r="AX82" s="44"/>
+      <c r="AY82" s="44"/>
+      <c r="AZ82" s="44"/>
+      <c r="BA82" s="44"/>
+      <c r="BB82" s="44"/>
+      <c r="BC82" s="44"/>
+      <c r="BD82" s="11"/>
     </row>
-    <row r="83" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z83" s="13"/>
-      <c r="AA83" s="13"/>
-      <c r="AB83" s="13"/>
-      <c r="AC83" s="13"/>
-      <c r="AD83" s="13"/>
-      <c r="AE83" s="13"/>
-      <c r="AF83" s="13"/>
-      <c r="AG83" s="13"/>
-      <c r="AH83" s="13"/>
-      <c r="AI83" s="13"/>
-      <c r="AJ83" s="13"/>
-      <c r="AK83" s="13"/>
-      <c r="AL83" s="13"/>
-      <c r="AM83" s="13"/>
-      <c r="AN83" s="13"/>
-      <c r="AO83" s="13"/>
-      <c r="AP83" s="13"/>
-      <c r="AQ83" s="13"/>
-      <c r="AR83" s="13"/>
-      <c r="AS83" s="13"/>
-      <c r="AT83" s="13"/>
-      <c r="AU83" s="13"/>
-      <c r="AV83" s="13"/>
-      <c r="AW83" s="13"/>
-      <c r="AX83" s="13"/>
-      <c r="AY83" s="13"/>
-      <c r="AZ83" s="13"/>
-      <c r="BA83" s="13"/>
-      <c r="BB83" s="13"/>
-      <c r="BC83" s="13"/>
-      <c r="BD83" s="12"/>
-      <c r="CV83"/>
-      <c r="CW83"/>
+    <row r="83" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z83" s="44"/>
+      <c r="AA83" s="44"/>
+      <c r="AB83" s="44"/>
+      <c r="AC83" s="44"/>
+      <c r="AD83" s="44"/>
+      <c r="AE83" s="44"/>
+      <c r="AF83" s="44"/>
+      <c r="AG83" s="44"/>
+      <c r="AH83" s="44"/>
+      <c r="AI83" s="44"/>
+      <c r="AJ83" s="44"/>
+      <c r="AK83" s="44"/>
+      <c r="AL83" s="44"/>
+      <c r="AM83" s="44"/>
+      <c r="AN83" s="44"/>
+      <c r="AO83" s="44"/>
+      <c r="AP83" s="44"/>
+      <c r="AQ83" s="44"/>
+      <c r="AR83" s="44"/>
+      <c r="AS83" s="44"/>
+      <c r="AT83" s="44"/>
+      <c r="AU83" s="44"/>
+      <c r="AV83" s="44"/>
+      <c r="AW83" s="44"/>
+      <c r="AX83" s="44"/>
+      <c r="AY83" s="44"/>
+      <c r="AZ83" s="44"/>
+      <c r="BA83" s="44"/>
+      <c r="BB83" s="44"/>
+      <c r="BC83" s="44"/>
+      <c r="BD83" s="11"/>
     </row>
-    <row r="84" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z84" s="13"/>
-      <c r="AA84" s="13"/>
-      <c r="AB84" s="13"/>
-      <c r="AC84" s="13"/>
-      <c r="AD84" s="13"/>
-      <c r="AE84" s="13"/>
-      <c r="AF84" s="13"/>
-      <c r="AG84" s="13"/>
-      <c r="AH84" s="13"/>
-      <c r="AI84" s="13"/>
-      <c r="AJ84" s="13"/>
-      <c r="AK84" s="13"/>
-      <c r="AL84" s="13"/>
-      <c r="AM84" s="13"/>
-      <c r="AN84" s="13"/>
-      <c r="AO84" s="13"/>
-      <c r="AP84" s="13"/>
-      <c r="AQ84" s="13"/>
-      <c r="AR84" s="13"/>
-      <c r="AS84" s="13"/>
-      <c r="AT84" s="13"/>
-      <c r="AU84" s="13"/>
-      <c r="AV84" s="13"/>
-      <c r="AW84" s="13"/>
-      <c r="AX84" s="13"/>
-      <c r="AY84" s="13"/>
-      <c r="AZ84" s="13"/>
-      <c r="BA84" s="13"/>
-      <c r="BB84" s="13"/>
-      <c r="BC84" s="13"/>
-      <c r="BD84" s="12"/>
-      <c r="CV84"/>
-      <c r="CW84"/>
+    <row r="84" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z84" s="44"/>
+      <c r="AA84" s="44"/>
+      <c r="AB84" s="44"/>
+      <c r="AC84" s="44"/>
+      <c r="AD84" s="44"/>
+      <c r="AE84" s="44"/>
+      <c r="AF84" s="44"/>
+      <c r="AG84" s="44"/>
+      <c r="AH84" s="44"/>
+      <c r="AI84" s="44"/>
+      <c r="AJ84" s="44"/>
+      <c r="AK84" s="44"/>
+      <c r="AL84" s="44"/>
+      <c r="AM84" s="44"/>
+      <c r="AN84" s="44"/>
+      <c r="AO84" s="44"/>
+      <c r="AP84" s="44"/>
+      <c r="AQ84" s="44"/>
+      <c r="AR84" s="44"/>
+      <c r="AS84" s="44"/>
+      <c r="AT84" s="44"/>
+      <c r="AU84" s="44"/>
+      <c r="AV84" s="44"/>
+      <c r="AW84" s="44"/>
+      <c r="AX84" s="44"/>
+      <c r="AY84" s="44"/>
+      <c r="AZ84" s="44"/>
+      <c r="BA84" s="44"/>
+      <c r="BB84" s="44"/>
+      <c r="BC84" s="44"/>
+      <c r="BD84" s="11"/>
     </row>
-    <row r="85" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z85" s="13"/>
-      <c r="AA85" s="13"/>
-      <c r="AB85" s="13"/>
-      <c r="AC85" s="13"/>
-      <c r="AD85" s="13"/>
-      <c r="AE85" s="13"/>
-      <c r="AF85" s="13"/>
-      <c r="AG85" s="13"/>
-      <c r="AH85" s="13"/>
-      <c r="AI85" s="13"/>
-      <c r="AJ85" s="13"/>
-      <c r="AK85" s="13"/>
-      <c r="AL85" s="13"/>
-      <c r="AM85" s="13"/>
-      <c r="AN85" s="13"/>
-      <c r="AO85" s="13"/>
-      <c r="AP85" s="13"/>
-      <c r="AQ85" s="13"/>
-      <c r="AR85" s="13"/>
-      <c r="AS85" s="13"/>
-      <c r="AT85" s="13"/>
-      <c r="AU85" s="13"/>
-      <c r="AV85" s="13"/>
-      <c r="AW85" s="13"/>
-      <c r="AX85" s="13"/>
-      <c r="AY85" s="13"/>
-      <c r="AZ85" s="13"/>
-      <c r="BA85" s="13"/>
-      <c r="BB85" s="13"/>
-      <c r="BC85" s="13"/>
-      <c r="BD85" s="12"/>
-      <c r="CV85"/>
-      <c r="CW85"/>
+    <row r="85" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z85" s="44"/>
+      <c r="AA85" s="44"/>
+      <c r="AB85" s="44"/>
+      <c r="AC85" s="44"/>
+      <c r="AD85" s="44"/>
+      <c r="AE85" s="44"/>
+      <c r="AF85" s="44"/>
+      <c r="AG85" s="44"/>
+      <c r="AH85" s="44"/>
+      <c r="AI85" s="44"/>
+      <c r="AJ85" s="44"/>
+      <c r="AK85" s="44"/>
+      <c r="AL85" s="44"/>
+      <c r="AM85" s="44"/>
+      <c r="AN85" s="44"/>
+      <c r="AO85" s="44"/>
+      <c r="AP85" s="44"/>
+      <c r="AQ85" s="44"/>
+      <c r="AR85" s="44"/>
+      <c r="AS85" s="44"/>
+      <c r="AT85" s="44"/>
+      <c r="AU85" s="44"/>
+      <c r="AV85" s="44"/>
+      <c r="AW85" s="44"/>
+      <c r="AX85" s="44"/>
+      <c r="AY85" s="44"/>
+      <c r="AZ85" s="44"/>
+      <c r="BA85" s="44"/>
+      <c r="BB85" s="44"/>
+      <c r="BC85" s="44"/>
+      <c r="BD85" s="11"/>
     </row>
-    <row r="86" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z86" s="13"/>
-      <c r="AA86" s="13"/>
-      <c r="AB86" s="13"/>
-      <c r="AC86" s="13"/>
-      <c r="AD86" s="13"/>
-      <c r="AE86" s="13"/>
-      <c r="AF86" s="13"/>
-      <c r="AG86" s="13"/>
-      <c r="AH86" s="13"/>
-      <c r="AI86" s="13"/>
-      <c r="AJ86" s="13"/>
-      <c r="AK86" s="13"/>
-      <c r="AL86" s="13"/>
-      <c r="AM86" s="13"/>
-      <c r="AN86" s="13"/>
-      <c r="AO86" s="13"/>
-      <c r="AP86" s="13"/>
-      <c r="AQ86" s="13"/>
-      <c r="AR86" s="13"/>
-      <c r="AS86" s="13"/>
-      <c r="AT86" s="13"/>
-      <c r="AU86" s="13"/>
-      <c r="AV86" s="13"/>
-      <c r="AW86" s="13"/>
-      <c r="AX86" s="13"/>
-      <c r="AY86" s="13"/>
-      <c r="AZ86" s="13"/>
-      <c r="BA86" s="13"/>
-      <c r="BB86" s="13"/>
-      <c r="BC86" s="13"/>
-      <c r="BD86" s="12"/>
-      <c r="CV86"/>
-      <c r="CW86"/>
+    <row r="86" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z86" s="44"/>
+      <c r="AA86" s="44"/>
+      <c r="AB86" s="44"/>
+      <c r="AC86" s="44"/>
+      <c r="AD86" s="44"/>
+      <c r="AE86" s="44"/>
+      <c r="AF86" s="44"/>
+      <c r="AG86" s="44"/>
+      <c r="AH86" s="44"/>
+      <c r="AI86" s="44"/>
+      <c r="AJ86" s="44"/>
+      <c r="AK86" s="44"/>
+      <c r="AL86" s="44"/>
+      <c r="AM86" s="44"/>
+      <c r="AN86" s="44"/>
+      <c r="AO86" s="44"/>
+      <c r="AP86" s="44"/>
+      <c r="AQ86" s="44"/>
+      <c r="AR86" s="44"/>
+      <c r="AS86" s="44"/>
+      <c r="AT86" s="44"/>
+      <c r="AU86" s="44"/>
+      <c r="AV86" s="44"/>
+      <c r="AW86" s="44"/>
+      <c r="AX86" s="44"/>
+      <c r="AY86" s="44"/>
+      <c r="AZ86" s="44"/>
+      <c r="BA86" s="44"/>
+      <c r="BB86" s="44"/>
+      <c r="BC86" s="44"/>
+      <c r="BD86" s="11"/>
     </row>
-    <row r="87" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z87" s="13"/>
-      <c r="AA87" s="13"/>
-      <c r="AB87" s="13"/>
-      <c r="AC87" s="13"/>
-      <c r="AD87" s="13"/>
-      <c r="AE87" s="13"/>
-      <c r="AF87" s="13"/>
-      <c r="AG87" s="13"/>
-      <c r="AH87" s="13"/>
-      <c r="AI87" s="13"/>
-      <c r="AJ87" s="13"/>
-      <c r="AK87" s="13"/>
-      <c r="AL87" s="13"/>
-      <c r="AM87" s="13"/>
-      <c r="AN87" s="13"/>
-      <c r="AO87" s="13"/>
-      <c r="AP87" s="13"/>
-      <c r="AQ87" s="13"/>
-      <c r="AR87" s="13"/>
-      <c r="AS87" s="13"/>
-      <c r="AT87" s="13"/>
-      <c r="AU87" s="13"/>
-      <c r="AV87" s="13"/>
-      <c r="AW87" s="13"/>
-      <c r="AX87" s="13"/>
-      <c r="AY87" s="13"/>
-      <c r="AZ87" s="13"/>
-      <c r="BA87" s="13"/>
-      <c r="BB87" s="13"/>
-      <c r="BC87" s="13"/>
-      <c r="BD87" s="12"/>
-      <c r="CV87"/>
-      <c r="CW87"/>
+    <row r="87" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z87" s="44"/>
+      <c r="AA87" s="44"/>
+      <c r="AB87" s="44"/>
+      <c r="AC87" s="44"/>
+      <c r="AD87" s="44"/>
+      <c r="AE87" s="44"/>
+      <c r="AF87" s="44"/>
+      <c r="AG87" s="44"/>
+      <c r="AH87" s="44"/>
+      <c r="AI87" s="44"/>
+      <c r="AJ87" s="44"/>
+      <c r="AK87" s="44"/>
+      <c r="AL87" s="44"/>
+      <c r="AM87" s="44"/>
+      <c r="AN87" s="44"/>
+      <c r="AO87" s="44"/>
+      <c r="AP87" s="44"/>
+      <c r="AQ87" s="44"/>
+      <c r="AR87" s="44"/>
+      <c r="AS87" s="44"/>
+      <c r="AT87" s="44"/>
+      <c r="AU87" s="44"/>
+      <c r="AV87" s="44"/>
+      <c r="AW87" s="44"/>
+      <c r="AX87" s="44"/>
+      <c r="AY87" s="44"/>
+      <c r="AZ87" s="44"/>
+      <c r="BA87" s="44"/>
+      <c r="BB87" s="44"/>
+      <c r="BC87" s="44"/>
+      <c r="BD87" s="11"/>
     </row>
-    <row r="88" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z88" s="13"/>
-      <c r="AA88" s="13"/>
-      <c r="AB88" s="13"/>
-      <c r="AC88" s="13"/>
-      <c r="AD88" s="13"/>
-      <c r="AE88" s="13"/>
-      <c r="AF88" s="13"/>
-      <c r="AG88" s="13"/>
-      <c r="AH88" s="13"/>
-      <c r="AI88" s="13"/>
-      <c r="AJ88" s="13"/>
-      <c r="AK88" s="13"/>
-      <c r="AL88" s="13"/>
-      <c r="AM88" s="13"/>
-      <c r="AN88" s="13"/>
-      <c r="AO88" s="13"/>
-      <c r="AP88" s="13"/>
-      <c r="AQ88" s="13"/>
-      <c r="AR88" s="13"/>
-      <c r="AS88" s="13"/>
-      <c r="AT88" s="13"/>
-      <c r="AU88" s="13"/>
-      <c r="AV88" s="13"/>
-      <c r="AW88" s="13"/>
-      <c r="AX88" s="13"/>
-      <c r="AY88" s="13"/>
-      <c r="AZ88" s="13"/>
-      <c r="BA88" s="13"/>
-      <c r="BB88" s="13"/>
-      <c r="BC88" s="13"/>
-      <c r="BD88" s="12"/>
-      <c r="CV88"/>
-      <c r="CW88"/>
+    <row r="88" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z88" s="44"/>
+      <c r="AA88" s="44"/>
+      <c r="AB88" s="44"/>
+      <c r="AC88" s="44"/>
+      <c r="AD88" s="44"/>
+      <c r="AE88" s="44"/>
+      <c r="AF88" s="44"/>
+      <c r="AG88" s="44"/>
+      <c r="AH88" s="44"/>
+      <c r="AI88" s="44"/>
+      <c r="AJ88" s="44"/>
+      <c r="AK88" s="44"/>
+      <c r="AL88" s="44"/>
+      <c r="AM88" s="44"/>
+      <c r="AN88" s="44"/>
+      <c r="AO88" s="44"/>
+      <c r="AP88" s="44"/>
+      <c r="AQ88" s="44"/>
+      <c r="AR88" s="44"/>
+      <c r="AS88" s="44"/>
+      <c r="AT88" s="44"/>
+      <c r="AU88" s="44"/>
+      <c r="AV88" s="44"/>
+      <c r="AW88" s="44"/>
+      <c r="AX88" s="44"/>
+      <c r="AY88" s="44"/>
+      <c r="AZ88" s="44"/>
+      <c r="BA88" s="44"/>
+      <c r="BB88" s="44"/>
+      <c r="BC88" s="44"/>
+      <c r="BD88" s="11"/>
     </row>
-    <row r="89" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z89" s="13"/>
-      <c r="AA89" s="13"/>
-      <c r="AB89" s="13"/>
-      <c r="AC89" s="13"/>
-      <c r="AD89" s="13"/>
-      <c r="AE89" s="13"/>
-      <c r="AF89" s="13"/>
-      <c r="AG89" s="13"/>
-      <c r="AH89" s="13"/>
-      <c r="AI89" s="13"/>
-      <c r="AJ89" s="13"/>
-      <c r="AK89" s="13"/>
-      <c r="AL89" s="13"/>
-      <c r="AM89" s="13"/>
-      <c r="AN89" s="13"/>
-      <c r="AO89" s="13"/>
-      <c r="AP89" s="13"/>
-      <c r="AQ89" s="13"/>
-      <c r="AR89" s="13"/>
-      <c r="AS89" s="13"/>
-      <c r="AT89" s="13"/>
-      <c r="AU89" s="13"/>
-      <c r="AV89" s="13"/>
-      <c r="AW89" s="13"/>
-      <c r="AX89" s="13"/>
-      <c r="AY89" s="13"/>
-      <c r="AZ89" s="13"/>
-      <c r="BA89" s="13"/>
-      <c r="BB89" s="13"/>
-      <c r="BC89" s="13"/>
-      <c r="BD89" s="12"/>
-      <c r="CV89"/>
-      <c r="CW89"/>
+    <row r="89" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z89" s="44"/>
+      <c r="AA89" s="44"/>
+      <c r="AB89" s="44"/>
+      <c r="AC89" s="44"/>
+      <c r="AD89" s="44"/>
+      <c r="AE89" s="44"/>
+      <c r="AF89" s="44"/>
+      <c r="AG89" s="44"/>
+      <c r="AH89" s="44"/>
+      <c r="AI89" s="44"/>
+      <c r="AJ89" s="44"/>
+      <c r="AK89" s="44"/>
+      <c r="AL89" s="44"/>
+      <c r="AM89" s="44"/>
+      <c r="AN89" s="44"/>
+      <c r="AO89" s="44"/>
+      <c r="AP89" s="44"/>
+      <c r="AQ89" s="44"/>
+      <c r="AR89" s="44"/>
+      <c r="AS89" s="44"/>
+      <c r="AT89" s="44"/>
+      <c r="AU89" s="44"/>
+      <c r="AV89" s="44"/>
+      <c r="AW89" s="44"/>
+      <c r="AX89" s="44"/>
+      <c r="AY89" s="44"/>
+      <c r="AZ89" s="44"/>
+      <c r="BA89" s="44"/>
+      <c r="BB89" s="44"/>
+      <c r="BC89" s="44"/>
+      <c r="BD89" s="11"/>
     </row>
-    <row r="90" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z90" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA90" s="11"/>
-      <c r="AB90" s="11"/>
-      <c r="AC90" s="11"/>
-      <c r="AD90" s="11"/>
-      <c r="AE90" s="11"/>
-      <c r="AF90" s="11"/>
-      <c r="AG90" s="11"/>
-      <c r="AH90" s="11"/>
-      <c r="AI90" s="11"/>
-      <c r="AJ90" s="11"/>
-      <c r="AK90" s="11"/>
-      <c r="AL90" s="11"/>
-      <c r="AM90" s="11"/>
-      <c r="AN90" s="11"/>
-      <c r="AO90" s="11"/>
-      <c r="AP90" s="11"/>
-      <c r="AQ90" s="11"/>
-      <c r="AR90" s="11"/>
-      <c r="AS90" s="11"/>
-      <c r="AT90" s="11"/>
-      <c r="AU90" s="11"/>
-      <c r="AV90" s="11"/>
-      <c r="AW90" s="11"/>
-      <c r="AX90" s="11"/>
-      <c r="AY90" s="11"/>
-      <c r="AZ90" s="11"/>
-      <c r="BA90" s="11"/>
-      <c r="BB90" s="11"/>
-      <c r="BC90" s="11"/>
+    <row r="90" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z90" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA90" s="43"/>
+      <c r="AB90" s="43"/>
+      <c r="AC90" s="43"/>
+      <c r="AD90" s="43"/>
+      <c r="AE90" s="43"/>
+      <c r="AF90" s="43"/>
+      <c r="AG90" s="43"/>
+      <c r="AH90" s="43"/>
+      <c r="AI90" s="43"/>
+      <c r="AJ90" s="43"/>
+      <c r="AK90" s="43"/>
+      <c r="AL90" s="43"/>
+      <c r="AM90" s="43"/>
+      <c r="AN90" s="43"/>
+      <c r="AO90" s="43"/>
+      <c r="AP90" s="43"/>
+      <c r="AQ90" s="43"/>
+      <c r="AR90" s="43"/>
+      <c r="AS90" s="43"/>
+      <c r="AT90" s="43"/>
+      <c r="AU90" s="43"/>
+      <c r="AV90" s="43"/>
+      <c r="AW90" s="43"/>
+      <c r="AX90" s="43"/>
+      <c r="AY90" s="43"/>
+      <c r="AZ90" s="43"/>
+      <c r="BA90" s="43"/>
+      <c r="BB90" s="43"/>
+      <c r="BC90" s="43"/>
       <c r="BD90" s="10"/>
-      <c r="CV90"/>
-      <c r="CW90"/>
     </row>
-    <row r="91" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Z91" s="11"/>
-      <c r="AA91" s="11"/>
-      <c r="AB91" s="11"/>
-      <c r="AC91" s="11"/>
-      <c r="AD91" s="11"/>
-      <c r="AE91" s="11"/>
-      <c r="AF91" s="11"/>
-      <c r="AG91" s="11"/>
-      <c r="AH91" s="11"/>
-      <c r="AI91" s="11"/>
-      <c r="AJ91" s="11"/>
-      <c r="AK91" s="11"/>
-      <c r="AL91" s="11"/>
-      <c r="AM91" s="11"/>
-      <c r="AN91" s="11"/>
-      <c r="AO91" s="11"/>
-      <c r="AP91" s="11"/>
-      <c r="AQ91" s="11"/>
-      <c r="AR91" s="11"/>
-      <c r="AS91" s="11"/>
-      <c r="AT91" s="11"/>
-      <c r="AU91" s="11"/>
-      <c r="AV91" s="11"/>
-      <c r="AW91" s="11"/>
-      <c r="AX91" s="11"/>
-      <c r="AY91" s="11"/>
-      <c r="AZ91" s="11"/>
-      <c r="BA91" s="11"/>
-      <c r="BB91" s="11"/>
-      <c r="BC91" s="11"/>
+    <row r="91" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z91" s="43"/>
+      <c r="AA91" s="43"/>
+      <c r="AB91" s="43"/>
+      <c r="AC91" s="43"/>
+      <c r="AD91" s="43"/>
+      <c r="AE91" s="43"/>
+      <c r="AF91" s="43"/>
+      <c r="AG91" s="43"/>
+      <c r="AH91" s="43"/>
+      <c r="AI91" s="43"/>
+      <c r="AJ91" s="43"/>
+      <c r="AK91" s="43"/>
+      <c r="AL91" s="43"/>
+      <c r="AM91" s="43"/>
+      <c r="AN91" s="43"/>
+      <c r="AO91" s="43"/>
+      <c r="AP91" s="43"/>
+      <c r="AQ91" s="43"/>
+      <c r="AR91" s="43"/>
+      <c r="AS91" s="43"/>
+      <c r="AT91" s="43"/>
+      <c r="AU91" s="43"/>
+      <c r="AV91" s="43"/>
+      <c r="AW91" s="43"/>
+      <c r="AX91" s="43"/>
+      <c r="AY91" s="43"/>
+      <c r="AZ91" s="43"/>
+      <c r="BA91" s="43"/>
+      <c r="BB91" s="43"/>
+      <c r="BC91" s="43"/>
       <c r="BD91" s="10"/>
-      <c r="CV91"/>
-      <c r="CW91"/>
     </row>
-    <row r="92" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Z92" s="9"/>
       <c r="AA92" s="9"/>
       <c r="AB92" s="9"/>
@@ -18250,10 +18204,8 @@
       <c r="BB92" s="9"/>
       <c r="BC92" s="9"/>
       <c r="BD92" s="9"/>
-      <c r="CV92"/>
-      <c r="CW92"/>
     </row>
-    <row r="93" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Z93" s="9"/>
       <c r="AA93" s="9"/>
       <c r="AB93" s="9"/>
@@ -18285,10 +18237,8 @@
       <c r="BB93" s="9"/>
       <c r="BC93" s="9"/>
       <c r="BD93" s="9"/>
-      <c r="CV93"/>
-      <c r="CW93"/>
     </row>
-    <row r="94" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Z94" s="9"/>
       <c r="AA94" s="9"/>
       <c r="AB94" s="9"/>
@@ -18320,10 +18270,8 @@
       <c r="BB94" s="9"/>
       <c r="BC94" s="9"/>
       <c r="BD94" s="9"/>
-      <c r="CV94"/>
-      <c r="CW94"/>
     </row>
-    <row r="95" spans="26:101" s="8" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="26:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Z95" s="9"/>
       <c r="AA95" s="9"/>
       <c r="AB95" s="9"/>
@@ -18355,43 +18303,9 @@
       <c r="BB95" s="9"/>
       <c r="BC95" s="9"/>
       <c r="BD95" s="9"/>
-      <c r="CV95"/>
-      <c r="CW95"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="Z2:BC3"/>
-    <mergeCell ref="Z4:BC6"/>
-    <mergeCell ref="R5:W7"/>
-    <mergeCell ref="BF5:BK7"/>
-    <mergeCell ref="Z9:BC13"/>
-    <mergeCell ref="BN9:CQ11"/>
-    <mergeCell ref="BN12:CQ13"/>
-    <mergeCell ref="Z14:BC16"/>
-    <mergeCell ref="Z17:BC18"/>
-    <mergeCell ref="Z21:BC22"/>
-    <mergeCell ref="Z23:BC24"/>
-    <mergeCell ref="Z26:BC27"/>
-    <mergeCell ref="Z32:BC36"/>
-    <mergeCell ref="BN34:CQ36"/>
-    <mergeCell ref="Z37:BC39"/>
-    <mergeCell ref="BN37:CQ38"/>
-    <mergeCell ref="Z40:BC41"/>
-    <mergeCell ref="BN40:CQ42"/>
-    <mergeCell ref="Z43:BC47"/>
-    <mergeCell ref="BN43:CQ44"/>
-    <mergeCell ref="Z48:BC50"/>
-    <mergeCell ref="B51:P52"/>
-    <mergeCell ref="Z51:BC52"/>
-    <mergeCell ref="B54:P56"/>
-    <mergeCell ref="Z54:BC58"/>
-    <mergeCell ref="B57:P58"/>
-    <mergeCell ref="Z59:BC61"/>
-    <mergeCell ref="BN59:CQ61"/>
-    <mergeCell ref="B60:P62"/>
-    <mergeCell ref="Z62:BC63"/>
-    <mergeCell ref="BN62:CQ63"/>
-    <mergeCell ref="B63:P64"/>
     <mergeCell ref="Z90:BC91"/>
     <mergeCell ref="Z65:BC69"/>
     <mergeCell ref="BN65:CQ67"/>
@@ -18399,6 +18313,38 @@
     <mergeCell ref="Z71:BC72"/>
     <mergeCell ref="Z77:BC81"/>
     <mergeCell ref="Z82:BC89"/>
+    <mergeCell ref="Z59:BC61"/>
+    <mergeCell ref="BN59:CQ61"/>
+    <mergeCell ref="B60:P62"/>
+    <mergeCell ref="Z62:BC63"/>
+    <mergeCell ref="BN62:CQ63"/>
+    <mergeCell ref="B63:P64"/>
+    <mergeCell ref="B51:P52"/>
+    <mergeCell ref="Z51:BC52"/>
+    <mergeCell ref="B54:P56"/>
+    <mergeCell ref="Z54:BC58"/>
+    <mergeCell ref="B57:P58"/>
+    <mergeCell ref="Z40:BC41"/>
+    <mergeCell ref="BN40:CQ42"/>
+    <mergeCell ref="Z43:BC47"/>
+    <mergeCell ref="BN43:CQ44"/>
+    <mergeCell ref="Z48:BC50"/>
+    <mergeCell ref="Z23:BC24"/>
+    <mergeCell ref="Z26:BC27"/>
+    <mergeCell ref="Z32:BC36"/>
+    <mergeCell ref="BN34:CQ36"/>
+    <mergeCell ref="Z37:BC39"/>
+    <mergeCell ref="BN37:CQ38"/>
+    <mergeCell ref="BN9:CQ11"/>
+    <mergeCell ref="BN12:CQ13"/>
+    <mergeCell ref="Z14:BC16"/>
+    <mergeCell ref="Z17:BC18"/>
+    <mergeCell ref="Z21:BC22"/>
+    <mergeCell ref="Z2:BC3"/>
+    <mergeCell ref="Z4:BC6"/>
+    <mergeCell ref="R5:W7"/>
+    <mergeCell ref="BF5:BK7"/>
+    <mergeCell ref="Z9:BC13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B63" r:id="rId1" xr:uid="{E94F4EDE-1E77-43A3-A953-3FB4805E383B}"/>
@@ -18428,23 +18374,532 @@
   <sheetPr codeName="Arkusz1">
     <tabColor rgb="FFEEEE22"/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:H26"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="2.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="2" spans="1:8" ht="128.25" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="42.75" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="45"/>
+      <c r="B3" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47">
+        <f>Dolnośląskie!$C$5</f>
+        <v>6962</v>
+      </c>
+      <c r="E3" s="47">
+        <f>Dolnośląskie!$D$5</f>
+        <v>4756</v>
+      </c>
+      <c r="H3" s="47">
+        <f>Dolnośląskie!$E$5</f>
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="42.75" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="45"/>
+      <c r="B4" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="F4" s="47">
+        <f>Lubelskie!$B$5</f>
+        <v>7491</v>
+      </c>
+      <c r="G4" s="47">
+        <f>Lubelskie!$C$5</f>
+        <v>1583</v>
+      </c>
+      <c r="H4" s="47">
+        <f>Lubelskie!$D$5</f>
+        <v>3679</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="42.75" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="45"/>
+      <c r="B5" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="48">
+        <f>Świętokrzyskie!$B$5</f>
+        <v>4500</v>
+      </c>
+      <c r="D5" s="47">
+        <f>Świętokrzyskie!$C$5</f>
+        <v>6031</v>
+      </c>
+      <c r="E5" s="47">
+        <f>Świętokrzyskie!$E$5</f>
+        <v>7271</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="47">
+        <f>SUM(C3:C5)</f>
+        <v>4500</v>
+      </c>
+      <c r="D6" s="47">
+        <f>SUM(D3:D5)</f>
+        <v>12993</v>
+      </c>
+      <c r="E6" s="47">
+        <f>SUM(E3:E5)</f>
+        <v>12027</v>
+      </c>
+      <c r="F6" s="47">
+        <f>SUM(F3:F5)</f>
+        <v>7491</v>
+      </c>
+      <c r="G6" s="47">
+        <f>SUM(G3:G5)</f>
+        <v>1583</v>
+      </c>
+      <c r="H6" s="47">
+        <f>SUM(H3:H5)</f>
+        <v>4797</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="47">
+        <f>Dolnośląskie!$B$6</f>
+        <v>969</v>
+      </c>
+      <c r="D7" s="47">
+        <f>Dolnośląskie!$C$6</f>
+        <v>8052</v>
+      </c>
+      <c r="E7" s="47">
+        <f>Dolnośląskie!$D$6</f>
+        <v>6161</v>
+      </c>
+      <c r="H7" s="47">
+        <f>Dolnośląskie!$E$6</f>
+        <v>6589</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="47">
+        <f>Lubelskie!$B$6</f>
+        <v>3303</v>
+      </c>
+      <c r="G8" s="47">
+        <f>Lubelskie!$C$6</f>
+        <v>6088</v>
+      </c>
+      <c r="H8" s="47">
+        <f>Lubelskie!$D$6</f>
+        <v>4338</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="47">
+        <f>Świętokrzyskie!$B$6</f>
+        <v>4470</v>
+      </c>
+      <c r="D9" s="47">
+        <f>Świętokrzyskie!$C$6</f>
+        <v>4154</v>
+      </c>
+      <c r="E9" s="47">
+        <f>Świętokrzyskie!$E$6</f>
+        <v>2527</v>
+      </c>
+      <c r="G9" s="47">
+        <f>Świętokrzyskie!$D$6</f>
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="47">
+        <f>SUM(C7:C9)</f>
+        <v>5439</v>
+      </c>
+      <c r="D10" s="47">
+        <f>SUM(D7:D9)</f>
+        <v>12206</v>
+      </c>
+      <c r="E10" s="47">
+        <f>SUM(E7:E9)</f>
+        <v>8688</v>
+      </c>
+      <c r="F10" s="47">
+        <f>SUM(F7:F9)</f>
+        <v>3303</v>
+      </c>
+      <c r="G10" s="47">
+        <f>SUM(G7:G9)</f>
+        <v>8209</v>
+      </c>
+      <c r="H10" s="47">
+        <f>SUM(H7:H9)</f>
+        <v>10927</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="47">
+        <f>Dolnośląskie!$B$7</f>
+        <v>4694</v>
+      </c>
+      <c r="D11" s="47">
+        <f>Dolnośląskie!$C$7</f>
+        <v>1924</v>
+      </c>
+      <c r="E11" s="47">
+        <f>Dolnośląskie!$D$7</f>
+        <v>4633</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="47">
+        <f>Lubelskie!$B$7</f>
+        <v>1856</v>
+      </c>
+      <c r="G12" s="47">
+        <f>Lubelskie!$C$7</f>
+        <v>4346</v>
+      </c>
+      <c r="H12" s="47">
+        <f>Lubelskie!$D$7</f>
+        <v>3553</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="47">
+        <f>Świętokrzyskie!$B$7</f>
+        <v>1873</v>
+      </c>
+      <c r="D13" s="47">
+        <f>Świętokrzyskie!$C$7</f>
+        <v>6388</v>
+      </c>
+      <c r="E13" s="47">
+        <f>Świętokrzyskie!$E$7</f>
+        <v>3125</v>
+      </c>
+      <c r="G13" s="47">
+        <f>Świętokrzyskie!$D$7</f>
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="47">
+        <f>SUM(C11:C13)</f>
+        <v>6567</v>
+      </c>
+      <c r="D14" s="47">
+        <f>SUM(D11:D13)</f>
+        <v>8312</v>
+      </c>
+      <c r="E14" s="47">
+        <f>SUM(E11:E13)</f>
+        <v>7758</v>
+      </c>
+      <c r="F14" s="47">
+        <f>SUM(F11:F13)</f>
+        <v>1856</v>
+      </c>
+      <c r="G14" s="47">
+        <f>SUM(G11:G13)</f>
+        <v>5903</v>
+      </c>
+      <c r="H14" s="47">
+        <f>SUM(H11:H13)</f>
+        <v>3553</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="47">
+        <f>Dolnośląskie!$B$8</f>
+        <v>3807</v>
+      </c>
+      <c r="D15" s="47">
+        <f>Dolnośląskie!$C$8</f>
+        <v>2261</v>
+      </c>
+      <c r="E15" s="47">
+        <f>Dolnośląskie!$D$8</f>
+        <v>4252</v>
+      </c>
+      <c r="H15" s="47">
+        <f>Dolnośląskie!$E$8</f>
+        <v>7094</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="47">
+        <f>SUM(C15)</f>
+        <v>3807</v>
+      </c>
+      <c r="D16" s="47">
+        <f>SUM(D15)</f>
+        <v>2261</v>
+      </c>
+      <c r="E16" s="47">
+        <f>SUM(E15)</f>
+        <v>4252</v>
+      </c>
+      <c r="H16" s="47">
+        <f>SUM(H15)</f>
+        <v>7094</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="47">
+        <f>Dolnośląskie!$B$9</f>
+        <v>1952</v>
+      </c>
+      <c r="D17" s="47">
+        <f>Dolnośląskie!$C$9</f>
+        <v>3740</v>
+      </c>
+      <c r="E17" s="47">
+        <f>Dolnośląskie!$D$9</f>
+        <v>5982</v>
+      </c>
+      <c r="H17" s="47">
+        <f>Dolnośląskie!$E$9</f>
+        <v>6530</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="47">
+        <f>SUM(C17)</f>
+        <v>1952</v>
+      </c>
+      <c r="D18" s="47">
+        <f>SUM(D17)</f>
+        <v>3740</v>
+      </c>
+      <c r="E18" s="47">
+        <f>SUM(E17)</f>
+        <v>5982</v>
+      </c>
+      <c r="H18" s="47">
+        <f>SUM(H17)</f>
+        <v>6530</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="47">
+        <f>Dolnośląskie!$B$10</f>
+        <v>1191</v>
+      </c>
+      <c r="D19" s="47">
+        <f>Dolnośląskie!$C$10</f>
+        <v>8177</v>
+      </c>
+      <c r="E19" s="47">
+        <f>Dolnośląskie!$D$10</f>
+        <v>4159</v>
+      </c>
+      <c r="H19" s="47">
+        <f>Dolnośląskie!$E$10</f>
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="47">
+        <f>SUM(C19)</f>
+        <v>1191</v>
+      </c>
+      <c r="D20" s="47">
+        <f>SUM(D19)</f>
+        <v>8177</v>
+      </c>
+      <c r="E20" s="47">
+        <f>SUM(E19)</f>
+        <v>4159</v>
+      </c>
+      <c r="H20" s="47">
+        <f>SUM(H19)</f>
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="47">
+        <f>Lubelskie!$B$8</f>
+        <v>7679</v>
+      </c>
+      <c r="G21" s="47">
+        <f>Lubelskie!$C$8</f>
+        <v>5473</v>
+      </c>
+      <c r="H21" s="47">
+        <f>Lubelskie!$D$8</f>
+        <v>4667</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="47">
+        <f>SUM(F21)</f>
+        <v>7679</v>
+      </c>
+      <c r="G22" s="47">
+        <f>SUM(G21)</f>
+        <v>5473</v>
+      </c>
+      <c r="H22" s="47">
+        <f>SUM(H21)</f>
+        <v>4667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" s="47">
+        <f>Lubelskie!$C$9</f>
+        <v>8148</v>
+      </c>
+      <c r="H23" s="47">
+        <f>Lubelskie!$D$9</f>
+        <v>3385</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="47">
+        <f>SUM(G23)</f>
+        <v>8148</v>
+      </c>
+      <c r="H24" s="47">
+        <f>SUM(H23)</f>
+        <v>3385</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="47">
+        <f>Świętokrzyskie!$B$8</f>
+        <v>7808</v>
+      </c>
+      <c r="D25" s="47">
+        <f>Świętokrzyskie!$C$8</f>
+        <v>1386</v>
+      </c>
+      <c r="E25" s="47">
+        <f>Świętokrzyskie!$E$8</f>
+        <v>5155</v>
+      </c>
+      <c r="G25" s="47">
+        <f>Świętokrzyskie!$D$8</f>
+        <v>8229</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="47">
+        <f>SUM(C25)</f>
+        <v>7808</v>
+      </c>
+      <c r="D26" s="47">
+        <f>SUM(D25)</f>
+        <v>1386</v>
+      </c>
+      <c r="E26" s="47">
+        <f>SUM(E25)</f>
+        <v>5155</v>
+      </c>
+      <c r="G26" s="47">
+        <f>SUM(G25)</f>
+        <v>8229</v>
       </c>
     </row>
   </sheetData>
+  <dataConsolidate leftLabels="1" topLabels="1" link="1">
+    <dataRefs count="3">
+      <dataRef ref="A4:E10" sheet="Dolnośląskie"/>
+      <dataRef ref="A4:D9" sheet="Lubelskie"/>
+      <dataRef ref="A4:E8" sheet="Świętokrzyskie"/>
+    </dataRefs>
+  </dataConsolidate>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -18456,14 +18911,14 @@
     <tabColor rgb="FF2EA3F2"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="11.44140625" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="11.42578125" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -18472,7 +18927,7 @@
       </c>
       <c r="C1" s="5"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>16</v>
       </c>
@@ -18483,7 +18938,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
@@ -18494,13 +18949,13 @@
         <v>6</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -18516,7 +18971,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
@@ -18534,7 +18989,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
@@ -18550,7 +19005,7 @@
       <c r="E7" s="3"/>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>15</v>
       </c>
@@ -18568,7 +19023,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>13</v>
       </c>
@@ -18586,7 +19041,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>12</v>
       </c>
@@ -18604,10 +19059,10 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G12" s="4"/>
     </row>
   </sheetData>
@@ -18622,26 +19077,26 @@
     <tabColor rgb="FF2EA3F2"/>
   </sheetPr>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="2"/>
-    <col min="7" max="7" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="2"/>
+    <col min="7" max="7" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>16</v>
       </c>
@@ -18652,7 +19107,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
@@ -18666,10 +19121,10 @@
         <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -18688,7 +19143,7 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
@@ -18709,7 +19164,7 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
@@ -18730,7 +19185,7 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
@@ -18763,16 +19218,16 @@
     <tabColor rgb="FF2EA3F2"/>
   </sheetPr>
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="2"/>
-    <col min="6" max="6" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="2"/>
+    <col min="6" max="6" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -18780,7 +19235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>16</v>
       </c>
@@ -18790,12 +19245,12 @@
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>8</v>
@@ -18804,7 +19259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -18823,7 +19278,7 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
@@ -18842,7 +19297,7 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
@@ -18861,9 +19316,9 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3">
         <v>7679</v>
@@ -18880,9 +19335,9 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3">
